--- a/Assets/Data/Amstrad CPC 664/MC0005A/Data CPC 664 MC0005A.xlsx
+++ b/Assets/Data/Amstrad CPC 664/MC0005A/Data CPC 664 MC0005A.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbewe\RetroComputing\CRT\Data\Amstrad CPC 664\MC0005A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbewe\AppData\Local\Classic-Repair-Toolbox\Data\Amstrad CPC 664\MC0005A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B48ADE-BBE0-4AC4-A520-DC2E9EB686E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31483DDF-384B-42F0-A9B3-0EB6C6A29365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Board schematics" sheetId="5" r:id="rId1"/>
@@ -442,16 +442,10 @@
     <t>74LS244</t>
   </si>
   <si>
-    <t>Commodore shared files/Component local files/74LS244.pdf</t>
-  </si>
-  <si>
     <t>IC114</t>
   </si>
   <si>
     <t>74LS373</t>
-  </si>
-  <si>
-    <t>Commodore shared files/Component local files/74LS373.pdf</t>
   </si>
   <si>
     <t>IC103</t>
@@ -933,6 +927,87 @@
   </si>
   <si>
     <t>https://www.cpcwiki.eu/index.php/Main_Page</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/CPC664_PCB_Bottom.png</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/CPC664_Schematic_Main.png</t>
+  </si>
+  <si>
+    <t>Amstrad CPC 664/MC0005A/CPC664_Schematic_Disk_Interface.png</t>
+  </si>
+  <si>
+    <t>BUFFER</t>
+  </si>
+  <si>
+    <t>OR</t>
+  </si>
+  <si>
+    <t>NAND</t>
+  </si>
+  <si>
+    <t>NOT</t>
+  </si>
+  <si>
+    <t>DRAM</t>
+  </si>
+  <si>
+    <t>OS + BASIC</t>
+  </si>
+  <si>
+    <t>BCD2DEC</t>
+  </si>
+  <si>
+    <t>BCD TO Decimal Decoder</t>
+  </si>
+  <si>
+    <t>BIOS and BASIC ROM for CPC664</t>
+  </si>
+  <si>
+    <t>IC201</t>
+  </si>
+  <si>
+    <t>IC202</t>
+  </si>
+  <si>
+    <t>IC203</t>
+  </si>
+  <si>
+    <t>IC204</t>
+  </si>
+  <si>
+    <t>IC205</t>
+  </si>
+  <si>
+    <t>IC206</t>
+  </si>
+  <si>
+    <t>IC207</t>
+  </si>
+  <si>
+    <t>IC208</t>
+  </si>
+  <si>
+    <t>IC209</t>
+  </si>
+  <si>
+    <t>IC210</t>
+  </si>
+  <si>
+    <t>IC211</t>
+  </si>
+  <si>
+    <t>IC212</t>
+  </si>
+  <si>
+    <t>IC213</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component local files/74LS244.PDF</t>
+  </si>
+  <si>
+    <t>Commodore shared files/Component local files/74LS373.PDF</t>
   </si>
   <si>
     <r>
@@ -947,83 +1022,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>2026-March-12</t>
+      <t>2026-March-26</t>
     </r>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/CPC664_PCB_Bottom.png</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/CPC664_Schematic_Main.png</t>
-  </si>
-  <si>
-    <t>Amstrad CPC 664/MC0005A/CPC664_Schematic_Disk_Interface.png</t>
-  </si>
-  <si>
-    <t>BUFFER</t>
-  </si>
-  <si>
-    <t>OR</t>
-  </si>
-  <si>
-    <t>NAND</t>
-  </si>
-  <si>
-    <t>NOT</t>
-  </si>
-  <si>
-    <t>DRAM</t>
-  </si>
-  <si>
-    <t>OS + BASIC</t>
-  </si>
-  <si>
-    <t>BCD2DEC</t>
-  </si>
-  <si>
-    <t>BCD TO Decimal Decoder</t>
-  </si>
-  <si>
-    <t>BIOS and BASIC ROM for CPC664</t>
-  </si>
-  <si>
-    <t>IC201</t>
-  </si>
-  <si>
-    <t>IC202</t>
-  </si>
-  <si>
-    <t>IC203</t>
-  </si>
-  <si>
-    <t>IC204</t>
-  </si>
-  <si>
-    <t>IC205</t>
-  </si>
-  <si>
-    <t>IC206</t>
-  </si>
-  <si>
-    <t>IC207</t>
-  </si>
-  <si>
-    <t>IC208</t>
-  </si>
-  <si>
-    <t>IC209</t>
-  </si>
-  <si>
-    <t>IC210</t>
-  </si>
-  <si>
-    <t>IC211</t>
-  </si>
-  <si>
-    <t>IC212</t>
-  </si>
-  <si>
-    <t>IC213</t>
   </si>
 </sst>
 </file>
@@ -1158,7 +1158,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1316,9 +1316,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1659,7 +1656,7 @@
     </row>
     <row r="3" spans="1:6" s="8" customFormat="1" ht="21">
       <c r="A3" s="8" t="s">
-        <v>270</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1671,7 +1668,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="17" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -1730,10 +1727,10 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="33" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>9</v>
@@ -1750,10 +1747,10 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="33" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C11" s="33" t="s">
         <v>9</v>
@@ -1773,7 +1770,7 @@
         <v>74</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>9</v>
@@ -1793,7 +1790,7 @@
         <v>75</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>9</v>
@@ -1897,7 +1894,7 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="17" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -1957,7 +1954,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="17" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2004,22 +2001,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="9" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2044,10 +2041,10 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C11" s="1">
         <v>40022</v>
@@ -2059,67 +2056,67 @@
         <v>24</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="9" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G13" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="9" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2164,42 +2161,42 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="C17" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G17" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="D18" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2227,13 +2224,13 @@
         <v>94</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>95</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>24</v>
@@ -2241,36 +2238,36 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="D21" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G21" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="D22" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>24</v>
@@ -2281,7 +2278,7 @@
         <v>107</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>108</v>
@@ -2304,7 +2301,7 @@
         <v>92</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>24</v>
@@ -2318,7 +2315,7 @@
         <v>97</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C25" s="1">
         <v>4164</v>
@@ -2330,7 +2327,7 @@
         <v>24</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2338,7 +2335,7 @@
         <v>99</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C26" s="1">
         <v>4164</v>
@@ -2350,7 +2347,7 @@
         <v>24</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2358,7 +2355,7 @@
         <v>100</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C27" s="1">
         <v>4164</v>
@@ -2370,7 +2367,7 @@
         <v>24</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2378,7 +2375,7 @@
         <v>101</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C28" s="1">
         <v>4164</v>
@@ -2390,7 +2387,7 @@
         <v>24</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2398,7 +2395,7 @@
         <v>102</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C29" s="1">
         <v>4164</v>
@@ -2410,7 +2407,7 @@
         <v>24</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2418,7 +2415,7 @@
         <v>103</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C30" s="1">
         <v>4164</v>
@@ -2430,7 +2427,7 @@
         <v>24</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2438,7 +2435,7 @@
         <v>104</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C31" s="1">
         <v>4164</v>
@@ -2450,7 +2447,7 @@
         <v>24</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2458,7 +2455,7 @@
         <v>105</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C32" s="1">
         <v>4164</v>
@@ -2470,21 +2467,21 @@
         <v>24</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>24</v>
@@ -2492,19 +2489,19 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="E34" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -3377,7 +3374,7 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="17" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="24"/>
@@ -3438,31 +3435,31 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G9" s="44" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="I9" s="9"/>
     </row>
     <row r="10" spans="1:9" ht="30">
       <c r="A10" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G10" s="44" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="135">
@@ -3475,10 +3472,10 @@
         <v>26</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G11" s="44" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="30">
@@ -3488,21 +3485,21 @@
       <c r="B12" s="50"/>
       <c r="C12" s="52"/>
       <c r="D12" s="41" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E12" s="41" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F12" s="41" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G12" s="53" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="41" customFormat="1">
       <c r="A13" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="28"/>
@@ -3511,75 +3508,75 @@
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G13" s="44"/>
     </row>
     <row r="14" spans="1:9" ht="60">
       <c r="A14" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G14" s="44" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="30">
       <c r="A15" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G15" s="44" t="s">
         <v>197</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="G15" s="44" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="60">
       <c r="A16" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G16" s="44" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="30">
       <c r="A17" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="G17" s="44" t="s">
         <v>197</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="G17" s="44" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="75">
@@ -3592,10 +3589,10 @@
         <v>26</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G19" s="44" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="30">
@@ -3607,16 +3604,16 @@
         <v>14</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G20" s="44" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -3629,46 +3626,46 @@
         <v>26</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="60">
       <c r="A22" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G22" s="44" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="30">
       <c r="A23" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G23" s="44" t="s">
         <v>197</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G23" s="44" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -3681,7 +3678,7 @@
         <v>26</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G25" s="1"/>
     </row>
@@ -3695,46 +3692,46 @@
         <v>26</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="67.5" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G27" s="44" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="30">
       <c r="A28" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G28" s="44" t="s">
         <v>197</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="G28" s="44" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -3745,7 +3742,7 @@
         <v>26</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="150">
@@ -3758,10 +3755,10 @@
         <v>26</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G31" s="44" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="30">
@@ -3773,16 +3770,16 @@
         <v>4</v>
       </c>
       <c r="D32" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="G32" s="44" t="s">
         <v>180</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="G32" s="44" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -3794,16 +3791,16 @@
         <v>13</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G33" s="44" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="30">
@@ -3815,16 +3812,16 @@
         <v>14</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G34" s="44" t="s">
         <v>183</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="G34" s="44" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -3836,16 +3833,16 @@
         <v>19</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G35" s="44" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -3857,16 +3854,16 @@
         <v>24</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G36" s="44" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="60">
@@ -3880,10 +3877,10 @@
       </c>
       <c r="E37" s="41"/>
       <c r="F37" s="41" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G37" s="53" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -3895,16 +3892,16 @@
         <v>3</v>
       </c>
       <c r="D38" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="E38" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="F38" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="G38" s="53" t="s">
         <v>217</v>
-      </c>
-      <c r="E38" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="F38" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="G38" s="53" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -3916,16 +3913,16 @@
         <v>4</v>
       </c>
       <c r="D39" s="41" t="s">
+        <v>212</v>
+      </c>
+      <c r="E39" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="F39" s="41" t="s">
         <v>214</v>
       </c>
-      <c r="E39" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="F39" s="41" t="s">
-        <v>216</v>
-      </c>
       <c r="G39" s="53" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -3937,16 +3934,16 @@
         <v>15</v>
       </c>
       <c r="D40" s="41" t="s">
+        <v>209</v>
+      </c>
+      <c r="E40" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="F40" s="41" t="s">
         <v>211</v>
       </c>
-      <c r="E40" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="F40" s="41" t="s">
-        <v>213</v>
-      </c>
       <c r="G40" s="53" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="75">
@@ -3956,16 +3953,16 @@
       <c r="B41" s="50"/>
       <c r="C41" s="52"/>
       <c r="D41" s="41" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E41" s="41" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F41" s="41" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G41" s="53" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="60">
@@ -3979,10 +3976,10 @@
       </c>
       <c r="E42" s="41"/>
       <c r="F42" s="41" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G42" s="53" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3994,16 +3991,16 @@
         <v>3</v>
       </c>
       <c r="D43" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="E43" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="F43" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="G43" s="53" t="s">
         <v>217</v>
-      </c>
-      <c r="E43" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="F43" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="G43" s="53" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -4015,16 +4012,16 @@
         <v>4</v>
       </c>
       <c r="D44" s="41" t="s">
+        <v>212</v>
+      </c>
+      <c r="E44" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="F44" s="41" t="s">
         <v>214</v>
       </c>
-      <c r="E44" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="F44" s="41" t="s">
-        <v>216</v>
-      </c>
       <c r="G44" s="53" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -4036,16 +4033,16 @@
         <v>15</v>
       </c>
       <c r="D45" s="41" t="s">
+        <v>209</v>
+      </c>
+      <c r="E45" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="F45" s="41" t="s">
         <v>211</v>
       </c>
-      <c r="E45" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="F45" s="41" t="s">
-        <v>213</v>
-      </c>
       <c r="G45" s="53" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="75">
@@ -4055,16 +4052,16 @@
       <c r="B46" s="50"/>
       <c r="C46" s="52"/>
       <c r="D46" s="41" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E46" s="41" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F46" s="41" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G46" s="53" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="60">
@@ -4078,10 +4075,10 @@
       </c>
       <c r="E47" s="41"/>
       <c r="F47" s="41" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G47" s="53" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -4093,16 +4090,16 @@
         <v>3</v>
       </c>
       <c r="D48" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="E48" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="F48" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="G48" s="53" t="s">
         <v>217</v>
-      </c>
-      <c r="E48" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="F48" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="G48" s="53" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -4114,16 +4111,16 @@
         <v>4</v>
       </c>
       <c r="D49" s="41" t="s">
+        <v>212</v>
+      </c>
+      <c r="E49" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="F49" s="41" t="s">
         <v>214</v>
       </c>
-      <c r="E49" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="F49" s="41" t="s">
-        <v>216</v>
-      </c>
       <c r="G49" s="53" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -4135,16 +4132,16 @@
         <v>15</v>
       </c>
       <c r="D50" s="41" t="s">
+        <v>209</v>
+      </c>
+      <c r="E50" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="F50" s="41" t="s">
         <v>211</v>
       </c>
-      <c r="E50" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="F50" s="41" t="s">
-        <v>213</v>
-      </c>
       <c r="G50" s="53" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="75">
@@ -4154,16 +4151,16 @@
       <c r="B51" s="50"/>
       <c r="C51" s="52"/>
       <c r="D51" s="41" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E51" s="41" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F51" s="41" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G51" s="53" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="60">
@@ -4177,10 +4174,10 @@
       </c>
       <c r="E52" s="41"/>
       <c r="F52" s="41" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G52" s="53" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -4192,16 +4189,16 @@
         <v>3</v>
       </c>
       <c r="D53" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="E53" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="F53" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="G53" s="53" t="s">
         <v>217</v>
-      </c>
-      <c r="E53" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="F53" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="G53" s="53" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -4213,16 +4210,16 @@
         <v>4</v>
       </c>
       <c r="D54" s="41" t="s">
+        <v>212</v>
+      </c>
+      <c r="E54" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="F54" s="41" t="s">
         <v>214</v>
       </c>
-      <c r="E54" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="F54" s="41" t="s">
-        <v>216</v>
-      </c>
       <c r="G54" s="53" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -4234,16 +4231,16 @@
         <v>15</v>
       </c>
       <c r="D55" s="41" t="s">
+        <v>209</v>
+      </c>
+      <c r="E55" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="F55" s="41" t="s">
         <v>211</v>
       </c>
-      <c r="E55" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="F55" s="41" t="s">
-        <v>213</v>
-      </c>
       <c r="G55" s="53" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="75">
@@ -4253,16 +4250,16 @@
       <c r="B56" s="50"/>
       <c r="C56" s="52"/>
       <c r="D56" s="41" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E56" s="41" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F56" s="41" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G56" s="53" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="60">
@@ -4276,10 +4273,10 @@
       </c>
       <c r="E57" s="41"/>
       <c r="F57" s="41" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G57" s="53" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -4291,16 +4288,16 @@
         <v>3</v>
       </c>
       <c r="D58" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="E58" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="F58" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="G58" s="53" t="s">
         <v>217</v>
-      </c>
-      <c r="E58" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="F58" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="G58" s="53" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -4312,16 +4309,16 @@
         <v>4</v>
       </c>
       <c r="D59" s="41" t="s">
+        <v>212</v>
+      </c>
+      <c r="E59" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="F59" s="41" t="s">
         <v>214</v>
       </c>
-      <c r="E59" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="F59" s="41" t="s">
-        <v>216</v>
-      </c>
       <c r="G59" s="53" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -4333,16 +4330,16 @@
         <v>15</v>
       </c>
       <c r="D60" s="41" t="s">
+        <v>209</v>
+      </c>
+      <c r="E60" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="F60" s="41" t="s">
         <v>211</v>
       </c>
-      <c r="E60" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="F60" s="41" t="s">
-        <v>213</v>
-      </c>
       <c r="G60" s="53" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="75">
@@ -4352,16 +4349,16 @@
       <c r="B61" s="50"/>
       <c r="C61" s="52"/>
       <c r="D61" s="41" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E61" s="41" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F61" s="41" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G61" s="53" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="60">
@@ -4375,10 +4372,10 @@
       </c>
       <c r="E62" s="41"/>
       <c r="F62" s="41" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G62" s="53" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -4390,16 +4387,16 @@
         <v>3</v>
       </c>
       <c r="D63" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="E63" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="F63" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="G63" s="53" t="s">
         <v>217</v>
-      </c>
-      <c r="E63" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="F63" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="G63" s="53" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -4411,16 +4408,16 @@
         <v>4</v>
       </c>
       <c r="D64" s="41" t="s">
+        <v>212</v>
+      </c>
+      <c r="E64" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="F64" s="41" t="s">
         <v>214</v>
       </c>
-      <c r="E64" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="F64" s="41" t="s">
-        <v>216</v>
-      </c>
       <c r="G64" s="53" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -4432,16 +4429,16 @@
         <v>15</v>
       </c>
       <c r="D65" s="41" t="s">
+        <v>209</v>
+      </c>
+      <c r="E65" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="F65" s="41" t="s">
         <v>211</v>
       </c>
-      <c r="E65" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="F65" s="41" t="s">
-        <v>213</v>
-      </c>
       <c r="G65" s="53" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="75">
@@ -4451,16 +4448,16 @@
       <c r="B66" s="50"/>
       <c r="C66" s="52"/>
       <c r="D66" s="41" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E66" s="41" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F66" s="41" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G66" s="53" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="60">
@@ -4474,10 +4471,10 @@
       </c>
       <c r="E67" s="41"/>
       <c r="F67" s="41" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G67" s="53" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -4489,16 +4486,16 @@
         <v>3</v>
       </c>
       <c r="D68" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="E68" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="F68" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="G68" s="53" t="s">
         <v>217</v>
-      </c>
-      <c r="E68" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="F68" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="G68" s="53" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -4510,16 +4507,16 @@
         <v>4</v>
       </c>
       <c r="D69" s="41" t="s">
+        <v>212</v>
+      </c>
+      <c r="E69" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="F69" s="41" t="s">
         <v>214</v>
       </c>
-      <c r="E69" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="F69" s="41" t="s">
-        <v>216</v>
-      </c>
       <c r="G69" s="53" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -4531,16 +4528,16 @@
         <v>15</v>
       </c>
       <c r="D70" s="41" t="s">
+        <v>209</v>
+      </c>
+      <c r="E70" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="F70" s="41" t="s">
         <v>211</v>
       </c>
-      <c r="E70" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="F70" s="41" t="s">
-        <v>213</v>
-      </c>
       <c r="G70" s="53" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="75">
@@ -4550,16 +4547,16 @@
       <c r="B71" s="50"/>
       <c r="C71" s="52"/>
       <c r="D71" s="41" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E71" s="41" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F71" s="41" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G71" s="53" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="60">
@@ -4573,10 +4570,10 @@
       </c>
       <c r="E72" s="41"/>
       <c r="F72" s="41" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G72" s="53" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -4588,16 +4585,16 @@
         <v>3</v>
       </c>
       <c r="D73" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="E73" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="F73" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="G73" s="53" t="s">
         <v>217</v>
-      </c>
-      <c r="E73" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="F73" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="G73" s="53" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -4609,16 +4606,16 @@
         <v>4</v>
       </c>
       <c r="D74" s="41" t="s">
+        <v>212</v>
+      </c>
+      <c r="E74" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="F74" s="41" t="s">
         <v>214</v>
       </c>
-      <c r="E74" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="F74" s="41" t="s">
-        <v>216</v>
-      </c>
       <c r="G74" s="53" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -4630,16 +4627,16 @@
         <v>15</v>
       </c>
       <c r="D75" s="41" t="s">
+        <v>209</v>
+      </c>
+      <c r="E75" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="F75" s="41" t="s">
         <v>211</v>
       </c>
-      <c r="E75" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="F75" s="41" t="s">
-        <v>213</v>
-      </c>
       <c r="G75" s="53" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="75">
@@ -4649,35 +4646,35 @@
       <c r="B76" s="50"/>
       <c r="C76" s="52"/>
       <c r="D76" s="41" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E76" s="41" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F76" s="41" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G76" s="53" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="60">
       <c r="A77" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G77" s="44" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="51" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B78"/>
       <c r="C78" s="1"/>
@@ -4686,39 +4683,39 @@
       </c>
       <c r="E78"/>
       <c r="F78" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G78" s="40"/>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C80" s="28">
         <v>1</v>
       </c>
       <c r="D80" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F80" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="E80" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="G80" s="44" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="173" spans="5:5">
@@ -6408,7 +6405,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="17" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B4" s="35"/>
       <c r="C4" s="35"/>
@@ -6472,721 +6469,721 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B9" s="55" t="s">
-        <v>142</v>
-      </c>
-      <c r="C9" s="55">
+        <v>145</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="C9" s="12">
         <v>656</v>
       </c>
-      <c r="D9" s="55">
+      <c r="D9" s="12">
         <v>582</v>
       </c>
-      <c r="E9" s="55">
+      <c r="E9" s="12">
         <v>94</v>
       </c>
-      <c r="F9" s="55">
+      <c r="F9" s="12">
         <v>196</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B10" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="B10" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="55">
+      <c r="C10" s="12">
         <v>610</v>
       </c>
-      <c r="D10" s="55">
+      <c r="D10" s="12">
         <v>272</v>
       </c>
-      <c r="E10" s="55">
+      <c r="E10" s="12">
         <v>145</v>
       </c>
-      <c r="F10" s="55">
+      <c r="F10" s="12">
         <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B11" s="55" t="s">
-        <v>113</v>
-      </c>
-      <c r="C11" s="55">
+        <v>145</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" s="12">
         <v>1240</v>
       </c>
-      <c r="D11" s="55">
+      <c r="D11" s="12">
         <v>1293</v>
       </c>
-      <c r="E11" s="55">
+      <c r="E11" s="12">
         <v>158</v>
       </c>
-      <c r="F11" s="55">
+      <c r="F11" s="12">
         <v>291</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B12" s="55" t="s">
-        <v>117</v>
-      </c>
-      <c r="C12" s="55">
+        <v>145</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C12" s="12">
         <v>1911</v>
       </c>
-      <c r="D12" s="55">
+      <c r="D12" s="12">
         <v>444</v>
       </c>
-      <c r="E12" s="55">
+      <c r="E12" s="12">
         <v>76</v>
       </c>
-      <c r="F12" s="55">
+      <c r="F12" s="12">
         <v>114</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B13" s="55" t="s">
-        <v>118</v>
-      </c>
-      <c r="C13" s="55">
+        <v>145</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="12">
         <v>2103</v>
       </c>
-      <c r="D13" s="55">
+      <c r="D13" s="12">
         <v>662</v>
       </c>
-      <c r="E13" s="55">
+      <c r="E13" s="12">
         <v>75</v>
       </c>
-      <c r="F13" s="55">
+      <c r="F13" s="12">
         <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B14" s="55" t="s">
-        <v>154</v>
-      </c>
-      <c r="C14" s="55">
+        <v>145</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="C14" s="12">
         <v>1248</v>
       </c>
-      <c r="D14" s="55">
+      <c r="D14" s="12">
         <v>867</v>
       </c>
-      <c r="E14" s="55">
+      <c r="E14" s="12">
         <v>99</v>
       </c>
-      <c r="F14" s="55">
+      <c r="F14" s="12">
         <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B15" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="B15" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="55">
+      <c r="C15" s="12">
         <v>269</v>
       </c>
-      <c r="D15" s="55">
+      <c r="D15" s="12">
         <v>276</v>
       </c>
-      <c r="E15" s="55">
+      <c r="E15" s="12">
         <v>190</v>
       </c>
-      <c r="F15" s="55">
+      <c r="F15" s="12">
         <v>834</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B16" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="B16" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="55">
+      <c r="C16" s="12">
         <v>2396</v>
       </c>
-      <c r="D16" s="55">
+      <c r="D16" s="12">
         <v>327</v>
       </c>
-      <c r="E16" s="55">
+      <c r="E16" s="12">
         <v>193</v>
       </c>
-      <c r="F16" s="55">
+      <c r="F16" s="12">
         <v>561</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B17" s="55" t="s">
-        <v>119</v>
-      </c>
-      <c r="C17" s="55">
+        <v>145</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C17" s="12">
         <v>1820</v>
       </c>
-      <c r="D17" s="55">
+      <c r="D17" s="12">
         <v>337</v>
       </c>
-      <c r="E17" s="55">
+      <c r="E17" s="12">
         <v>71</v>
       </c>
-      <c r="F17" s="55">
+      <c r="F17" s="12">
         <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B18" s="55" t="s">
-        <v>137</v>
-      </c>
-      <c r="C18" s="55">
+        <v>145</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="C18" s="12">
         <v>315</v>
       </c>
-      <c r="D18" s="55">
+      <c r="D18" s="12">
         <v>1186</v>
       </c>
-      <c r="E18" s="55">
+      <c r="E18" s="12">
         <v>57</v>
       </c>
-      <c r="F18" s="55">
+      <c r="F18" s="12">
         <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B19" s="55" t="s">
-        <v>137</v>
-      </c>
-      <c r="C19" s="55">
+        <v>145</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="C19" s="12">
         <v>451</v>
       </c>
-      <c r="D19" s="55">
+      <c r="D19" s="12">
         <v>1188</v>
       </c>
-      <c r="E19" s="55">
+      <c r="E19" s="12">
         <v>61</v>
       </c>
-      <c r="F19" s="55">
+      <c r="F19" s="12">
         <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B20" s="55" t="s">
-        <v>137</v>
-      </c>
-      <c r="C20" s="55">
+        <v>145</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="C20" s="12">
         <v>1392</v>
       </c>
-      <c r="D20" s="55">
+      <c r="D20" s="12">
         <v>875</v>
       </c>
-      <c r="E20" s="55">
+      <c r="E20" s="12">
         <v>62</v>
       </c>
-      <c r="F20" s="55">
+      <c r="F20" s="12">
         <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B21" s="55" t="s">
-        <v>137</v>
-      </c>
-      <c r="C21" s="55">
+        <v>145</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="C21" s="12">
         <v>2627</v>
       </c>
-      <c r="D21" s="55">
+      <c r="D21" s="12">
         <v>814</v>
       </c>
-      <c r="E21" s="55">
+      <c r="E21" s="12">
         <v>63</v>
       </c>
-      <c r="F21" s="55">
+      <c r="F21" s="12">
         <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B22" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="55">
+      <c r="C22" s="12">
         <v>269</v>
       </c>
-      <c r="D22" s="55">
+      <c r="D22" s="12">
         <v>1299</v>
       </c>
-      <c r="E22" s="55">
+      <c r="E22" s="12">
         <v>193</v>
       </c>
-      <c r="F22" s="55">
+      <c r="F22" s="12">
         <v>549</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B23" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="B23" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="C23" s="55">
+      <c r="C23" s="12">
         <v>500</v>
       </c>
-      <c r="D23" s="55">
+      <c r="D23" s="12">
         <v>1870</v>
       </c>
-      <c r="E23" s="55">
+      <c r="E23" s="12">
         <v>40</v>
       </c>
-      <c r="F23" s="55">
+      <c r="F23" s="12">
         <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B24" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="B24" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="C24" s="55">
+      <c r="C24" s="12">
         <v>501</v>
       </c>
-      <c r="D24" s="55">
+      <c r="D24" s="12">
         <v>1910</v>
       </c>
-      <c r="E24" s="55">
+      <c r="E24" s="12">
         <v>38</v>
       </c>
-      <c r="F24" s="55">
+      <c r="F24" s="12">
         <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B25" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="B25" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="C25" s="55">
+      <c r="C25" s="12">
         <v>1217</v>
       </c>
-      <c r="D25" s="55">
+      <c r="D25" s="12">
         <v>1098</v>
       </c>
-      <c r="E25" s="55">
+      <c r="E25" s="12">
         <v>41</v>
       </c>
-      <c r="F25" s="55">
+      <c r="F25" s="12">
         <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B26" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="B26" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="C26" s="55">
+      <c r="C26" s="12">
         <v>2148</v>
       </c>
-      <c r="D26" s="55">
+      <c r="D26" s="12">
         <v>1467</v>
       </c>
-      <c r="E26" s="55">
+      <c r="E26" s="12">
         <v>41</v>
       </c>
-      <c r="F26" s="55">
+      <c r="F26" s="12">
         <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B27" s="55" t="s">
-        <v>120</v>
-      </c>
-      <c r="C27" s="55">
+        <v>145</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C27" s="12">
         <v>2008</v>
       </c>
-      <c r="D27" s="55">
+      <c r="D27" s="12">
         <v>551</v>
       </c>
-      <c r="E27" s="55">
+      <c r="E27" s="12">
         <v>75</v>
       </c>
-      <c r="F27" s="55">
+      <c r="F27" s="12">
         <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B28" s="55" t="s">
-        <v>110</v>
-      </c>
-      <c r="C28" s="55">
+        <v>145</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C28" s="12">
         <v>1816</v>
       </c>
-      <c r="D28" s="55">
+      <c r="D28" s="12">
         <v>1510</v>
       </c>
-      <c r="E28" s="55">
+      <c r="E28" s="12">
         <v>90</v>
       </c>
-      <c r="F28" s="55">
+      <c r="F28" s="12">
         <v>169</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B29" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="B29" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="C29" s="55">
+      <c r="C29" s="12">
         <v>1813</v>
       </c>
-      <c r="D29" s="55">
+      <c r="D29" s="12">
         <v>1272</v>
       </c>
-      <c r="E29" s="55">
+      <c r="E29" s="12">
         <v>97</v>
       </c>
-      <c r="F29" s="55">
+      <c r="F29" s="12">
         <v>156</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B30" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="B30" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="C30" s="55">
+      <c r="C30" s="12">
         <v>2894</v>
       </c>
-      <c r="D30" s="55">
+      <c r="D30" s="12">
         <v>1033</v>
       </c>
-      <c r="E30" s="55">
+      <c r="E30" s="12">
         <v>164</v>
       </c>
-      <c r="F30" s="55">
+      <c r="F30" s="12">
         <v>934</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B31" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="B31" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="C31" s="55">
+      <c r="C31" s="12">
         <v>1733</v>
       </c>
-      <c r="D31" s="55">
+      <c r="D31" s="12">
         <v>886</v>
       </c>
-      <c r="E31" s="55">
+      <c r="E31" s="12">
         <v>341</v>
       </c>
-      <c r="F31" s="55">
+      <c r="F31" s="12">
         <v>312</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B32" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="B32" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="C32" s="55">
+      <c r="C32" s="12">
         <v>1735</v>
       </c>
-      <c r="D32" s="55">
+      <c r="D32" s="12">
         <v>886</v>
       </c>
-      <c r="E32" s="55">
+      <c r="E32" s="12">
         <v>337</v>
       </c>
-      <c r="F32" s="55">
+      <c r="F32" s="12">
         <v>310</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B33" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="B33" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="C33" s="55">
+      <c r="C33" s="12">
         <v>1733</v>
       </c>
-      <c r="D33" s="55">
+      <c r="D33" s="12">
         <v>886</v>
       </c>
-      <c r="E33" s="55">
+      <c r="E33" s="12">
         <v>339</v>
       </c>
-      <c r="F33" s="55">
+      <c r="F33" s="12">
         <v>312</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B34" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="B34" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="C34" s="55">
+      <c r="C34" s="12">
         <v>1737</v>
       </c>
-      <c r="D34" s="55">
+      <c r="D34" s="12">
         <v>886</v>
       </c>
-      <c r="E34" s="55">
+      <c r="E34" s="12">
         <v>337</v>
       </c>
-      <c r="F34" s="55">
+      <c r="F34" s="12">
         <v>310</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B35" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="B35" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="C35" s="55">
+      <c r="C35" s="12">
         <v>1733</v>
       </c>
-      <c r="D35" s="55">
+      <c r="D35" s="12">
         <v>886</v>
       </c>
-      <c r="E35" s="55">
+      <c r="E35" s="12">
         <v>339</v>
       </c>
-      <c r="F35" s="55">
+      <c r="F35" s="12">
         <v>312</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B36" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="B36" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="C36" s="55">
+      <c r="C36" s="12">
         <v>1730</v>
       </c>
-      <c r="D36" s="55">
+      <c r="D36" s="12">
         <v>884</v>
       </c>
-      <c r="E36" s="55">
+      <c r="E36" s="12">
         <v>344</v>
       </c>
-      <c r="F36" s="55">
+      <c r="F36" s="12">
         <v>312</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B37" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="B37" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="C37" s="55">
+      <c r="C37" s="12">
         <v>1733</v>
       </c>
-      <c r="D37" s="55">
+      <c r="D37" s="12">
         <v>888</v>
       </c>
-      <c r="E37" s="55">
+      <c r="E37" s="12">
         <v>342</v>
       </c>
-      <c r="F37" s="55">
+      <c r="F37" s="12">
         <v>310</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B38" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="B38" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="C38" s="55">
+      <c r="C38" s="12">
         <v>1733</v>
       </c>
-      <c r="D38" s="55">
+      <c r="D38" s="12">
         <v>886</v>
       </c>
-      <c r="E38" s="55">
+      <c r="E38" s="12">
         <v>341</v>
       </c>
-      <c r="F38" s="55">
+      <c r="F38" s="12">
         <v>312</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B39" s="55" t="s">
-        <v>148</v>
-      </c>
-      <c r="C39" s="55">
+        <v>145</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C39" s="12">
         <v>1426</v>
       </c>
-      <c r="D39" s="55">
+      <c r="D39" s="12">
         <v>1791</v>
       </c>
-      <c r="E39" s="55">
+      <c r="E39" s="12">
         <v>45</v>
       </c>
-      <c r="F39" s="55">
+      <c r="F39" s="12">
         <v>43</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B40" s="55" t="s">
-        <v>148</v>
-      </c>
-      <c r="C40" s="55">
+        <v>145</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C40" s="12">
         <v>1591</v>
       </c>
-      <c r="D40" s="55">
+      <c r="D40" s="12">
         <v>1791</v>
       </c>
-      <c r="E40" s="55">
+      <c r="E40" s="12">
         <v>43</v>
       </c>
-      <c r="F40" s="55">
+      <c r="F40" s="12">
         <v>45</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B41" s="55" t="s">
-        <v>148</v>
-      </c>
-      <c r="C41" s="55">
+        <v>145</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C41" s="12">
         <v>1985</v>
       </c>
-      <c r="D41" s="55">
+      <c r="D41" s="12">
         <v>1751</v>
       </c>
-      <c r="E41" s="55">
+      <c r="E41" s="12">
         <v>47</v>
       </c>
-      <c r="F41" s="55">
+      <c r="F41" s="12">
         <v>42</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B42" s="55" t="s">
-        <v>148</v>
-      </c>
-      <c r="C42" s="55">
+        <v>145</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C42" s="12">
         <v>231</v>
       </c>
-      <c r="D42" s="55">
+      <c r="D42" s="12">
         <v>1176</v>
       </c>
-      <c r="E42" s="55">
+      <c r="E42" s="12">
         <v>41</v>
       </c>
-      <c r="F42" s="55">
+      <c r="F42" s="12">
         <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C43" s="12">
         <v>147</v>
       </c>
-      <c r="B43" s="55" t="s">
-        <v>148</v>
-      </c>
-      <c r="C43" s="55">
-        <v>147</v>
-      </c>
-      <c r="D43" s="55">
+      <c r="D43" s="12">
         <v>1177</v>
       </c>
-      <c r="E43" s="55">
+      <c r="E43" s="12">
         <v>41</v>
       </c>
-      <c r="F43" s="55">
+      <c r="F43" s="12">
         <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="B44" s="55" t="s">
-        <v>167</v>
-      </c>
-      <c r="C44" s="55">
+        <v>145</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="C44" s="12">
         <v>1416</v>
       </c>
-      <c r="D44" s="55">
+      <c r="D44" s="12">
         <v>1857</v>
       </c>
-      <c r="E44" s="55">
+      <c r="E44" s="12">
         <v>105</v>
       </c>
-      <c r="F44" s="55">
+      <c r="F44" s="12">
         <v>54</v>
       </c>
     </row>
@@ -7194,19 +7191,19 @@
       <c r="A45" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B45" s="56" t="s">
-        <v>142</v>
-      </c>
-      <c r="C45" s="56">
+      <c r="B45" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="C45" s="12">
         <v>62</v>
       </c>
-      <c r="D45" s="56">
+      <c r="D45" s="12">
         <v>384</v>
       </c>
-      <c r="E45" s="56">
+      <c r="E45" s="12">
         <v>74</v>
       </c>
-      <c r="F45" s="56">
+      <c r="F45" s="12">
         <v>34</v>
       </c>
     </row>
@@ -7214,19 +7211,19 @@
       <c r="A46" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B46" s="56" t="s">
+      <c r="B46" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="C46" s="56">
+      <c r="C46" s="12">
         <v>162</v>
       </c>
-      <c r="D46" s="56">
+      <c r="D46" s="12">
         <v>230</v>
       </c>
-      <c r="E46" s="56">
+      <c r="E46" s="12">
         <v>121</v>
       </c>
-      <c r="F46" s="56">
+      <c r="F46" s="12">
         <v>51</v>
       </c>
     </row>
@@ -7234,19 +7231,19 @@
       <c r="A47" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B47" s="56" t="s">
-        <v>113</v>
-      </c>
-      <c r="C47" s="56">
+      <c r="B47" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C47" s="12">
         <v>162</v>
       </c>
-      <c r="D47" s="56">
+      <c r="D47" s="12">
         <v>333</v>
       </c>
-      <c r="E47" s="56">
+      <c r="E47" s="12">
         <v>120</v>
       </c>
-      <c r="F47" s="56">
+      <c r="F47" s="12">
         <v>57</v>
       </c>
     </row>
@@ -7254,19 +7251,19 @@
       <c r="A48" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B48" s="56" t="s">
-        <v>117</v>
-      </c>
-      <c r="C48" s="56">
+      <c r="B48" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C48" s="12">
         <v>160</v>
       </c>
-      <c r="D48" s="56">
+      <c r="D48" s="12">
         <v>441</v>
       </c>
-      <c r="E48" s="56">
+      <c r="E48" s="12">
         <v>73</v>
       </c>
-      <c r="F48" s="56">
+      <c r="F48" s="12">
         <v>34</v>
       </c>
     </row>
@@ -7274,19 +7271,19 @@
       <c r="A49" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B49" s="56" t="s">
-        <v>118</v>
-      </c>
-      <c r="C49" s="56">
+      <c r="B49" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C49" s="12">
         <v>285</v>
       </c>
-      <c r="D49" s="56">
+      <c r="D49" s="12">
         <v>442</v>
       </c>
-      <c r="E49" s="56">
+      <c r="E49" s="12">
         <v>72</v>
       </c>
-      <c r="F49" s="56">
+      <c r="F49" s="12">
         <v>33</v>
       </c>
     </row>
@@ -7294,19 +7291,19 @@
       <c r="A50" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B50" s="56" t="s">
-        <v>154</v>
-      </c>
-      <c r="C50" s="56">
+      <c r="B50" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="C50" s="12">
         <v>359</v>
       </c>
-      <c r="D50" s="56">
+      <c r="D50" s="12">
         <v>174</v>
       </c>
-      <c r="E50" s="56">
+      <c r="E50" s="12">
         <v>86</v>
       </c>
-      <c r="F50" s="56">
+      <c r="F50" s="12">
         <v>33</v>
       </c>
     </row>
@@ -7314,19 +7311,19 @@
       <c r="A51" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B51" s="56" t="s">
+      <c r="B51" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="C51" s="56">
+      <c r="C51" s="12">
         <v>349</v>
       </c>
-      <c r="D51" s="56">
+      <c r="D51" s="12">
         <v>226</v>
       </c>
-      <c r="E51" s="56">
+      <c r="E51" s="12">
         <v>169</v>
       </c>
-      <c r="F51" s="56">
+      <c r="F51" s="12">
         <v>57</v>
       </c>
     </row>
@@ -7334,19 +7331,19 @@
       <c r="A52" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B52" s="56" t="s">
+      <c r="B52" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C52" s="56">
+      <c r="C52" s="12">
         <v>349</v>
       </c>
-      <c r="D52" s="56">
+      <c r="D52" s="12">
         <v>335</v>
       </c>
-      <c r="E52" s="56">
+      <c r="E52" s="12">
         <v>168</v>
       </c>
-      <c r="F52" s="56">
+      <c r="F52" s="12">
         <v>54</v>
       </c>
     </row>
@@ -7354,19 +7351,19 @@
       <c r="A53" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B53" s="56" t="s">
-        <v>119</v>
-      </c>
-      <c r="C53" s="56">
+      <c r="B53" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C53" s="12">
         <v>407</v>
       </c>
-      <c r="D53" s="56">
+      <c r="D53" s="12">
         <v>441</v>
       </c>
-      <c r="E53" s="56">
+      <c r="E53" s="12">
         <v>71</v>
       </c>
-      <c r="F53" s="56">
+      <c r="F53" s="12">
         <v>32</v>
       </c>
     </row>
@@ -7374,19 +7371,19 @@
       <c r="A54" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B54" s="56" t="s">
-        <v>137</v>
-      </c>
-      <c r="C54" s="56">
+      <c r="B54" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="C54" s="12">
         <v>611</v>
       </c>
-      <c r="D54" s="56">
+      <c r="D54" s="12">
         <v>471</v>
       </c>
-      <c r="E54" s="56">
+      <c r="E54" s="12">
         <v>63</v>
       </c>
-      <c r="F54" s="56">
+      <c r="F54" s="12">
         <v>34</v>
       </c>
     </row>
@@ -7394,19 +7391,19 @@
       <c r="A55" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B55" s="56" t="s">
+      <c r="B55" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="C55" s="56">
+      <c r="C55" s="12">
         <v>636</v>
       </c>
-      <c r="D55" s="56">
+      <c r="D55" s="12">
         <v>343</v>
       </c>
-      <c r="E55" s="56">
+      <c r="E55" s="12">
         <v>170</v>
       </c>
-      <c r="F55" s="56">
+      <c r="F55" s="12">
         <v>53</v>
       </c>
     </row>
@@ -7414,19 +7411,19 @@
       <c r="A56" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B56" s="56" t="s">
+      <c r="B56" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="C56" s="56">
+      <c r="C56" s="12">
         <v>610</v>
       </c>
-      <c r="D56" s="56">
+      <c r="D56" s="12">
         <v>183</v>
       </c>
-      <c r="E56" s="56">
+      <c r="E56" s="12">
         <v>63</v>
       </c>
-      <c r="F56" s="56">
+      <c r="F56" s="12">
         <v>31</v>
       </c>
     </row>
@@ -7434,19 +7431,19 @@
       <c r="A57" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B57" s="56" t="s">
-        <v>120</v>
-      </c>
-      <c r="C57" s="56">
+      <c r="B57" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C57" s="12">
         <v>702</v>
       </c>
-      <c r="D57" s="56">
+      <c r="D57" s="12">
         <v>469</v>
       </c>
-      <c r="E57" s="56">
+      <c r="E57" s="12">
         <v>70</v>
       </c>
-      <c r="F57" s="56">
+      <c r="F57" s="12">
         <v>33</v>
       </c>
     </row>
@@ -7454,19 +7451,19 @@
       <c r="A58" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B58" s="56" t="s">
-        <v>110</v>
-      </c>
-      <c r="C58" s="56">
+      <c r="B58" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C58" s="12">
         <v>901</v>
       </c>
-      <c r="D58" s="56">
+      <c r="D58" s="12">
         <v>347</v>
       </c>
-      <c r="E58" s="56">
+      <c r="E58" s="12">
         <v>38</v>
       </c>
-      <c r="F58" s="56">
+      <c r="F58" s="12">
         <v>80</v>
       </c>
     </row>
@@ -7474,19 +7471,19 @@
       <c r="A59" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B59" s="56" t="s">
+      <c r="B59" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="C59" s="56">
+      <c r="C59" s="12">
         <v>962</v>
       </c>
-      <c r="D59" s="56">
+      <c r="D59" s="12">
         <v>349</v>
       </c>
-      <c r="E59" s="56">
+      <c r="E59" s="12">
         <v>34</v>
       </c>
-      <c r="F59" s="56">
+      <c r="F59" s="12">
         <v>78</v>
       </c>
     </row>
@@ -7494,19 +7491,19 @@
       <c r="A60" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B60" s="56" t="s">
+      <c r="B60" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="C60" s="56">
+      <c r="C60" s="12">
         <v>1227</v>
       </c>
-      <c r="D60" s="56">
+      <c r="D60" s="12">
         <v>361</v>
       </c>
-      <c r="E60" s="56">
+      <c r="E60" s="12">
         <v>58</v>
       </c>
-      <c r="F60" s="56">
+      <c r="F60" s="12">
         <v>157</v>
       </c>
     </row>
@@ -7514,19 +7511,19 @@
       <c r="A61" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B61" s="56" t="s">
+      <c r="B61" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="C61" s="56">
+      <c r="C61" s="12">
         <v>1079</v>
       </c>
-      <c r="D61" s="56">
+      <c r="D61" s="12">
         <v>452</v>
       </c>
-      <c r="E61" s="56">
+      <c r="E61" s="12">
         <v>35</v>
       </c>
-      <c r="F61" s="56">
+      <c r="F61" s="12">
         <v>59</v>
       </c>
     </row>
@@ -7534,19 +7531,19 @@
       <c r="A62" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B62" s="56" t="s">
+      <c r="B62" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="C62" s="56">
+      <c r="C62" s="12">
         <v>1019</v>
       </c>
-      <c r="D62" s="56">
+      <c r="D62" s="12">
         <v>453</v>
       </c>
-      <c r="E62" s="56">
+      <c r="E62" s="12">
         <v>35</v>
       </c>
-      <c r="F62" s="56">
+      <c r="F62" s="12">
         <v>61</v>
       </c>
     </row>
@@ -7554,19 +7551,19 @@
       <c r="A63" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B63" s="56" t="s">
+      <c r="B63" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="C63" s="56">
+      <c r="C63" s="12">
         <v>964</v>
       </c>
-      <c r="D63" s="56">
+      <c r="D63" s="12">
         <v>451</v>
       </c>
-      <c r="E63" s="56">
+      <c r="E63" s="12">
         <v>30</v>
       </c>
-      <c r="F63" s="56">
+      <c r="F63" s="12">
         <v>64</v>
       </c>
     </row>
@@ -7574,19 +7571,19 @@
       <c r="A64" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B64" s="56" t="s">
+      <c r="B64" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="C64" s="56">
+      <c r="C64" s="12">
         <v>901</v>
       </c>
-      <c r="D64" s="56">
+      <c r="D64" s="12">
         <v>451</v>
       </c>
-      <c r="E64" s="56">
+      <c r="E64" s="12">
         <v>35</v>
       </c>
-      <c r="F64" s="56">
+      <c r="F64" s="12">
         <v>65</v>
       </c>
     </row>
@@ -7594,19 +7591,19 @@
       <c r="A65" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B65" s="56" t="s">
+      <c r="B65" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="C65" s="56">
+      <c r="C65" s="12">
         <v>1138</v>
       </c>
-      <c r="D65" s="56">
+      <c r="D65" s="12">
         <v>451</v>
       </c>
-      <c r="E65" s="56">
+      <c r="E65" s="12">
         <v>35</v>
       </c>
-      <c r="F65" s="56">
+      <c r="F65" s="12">
         <v>62</v>
       </c>
     </row>
@@ -7614,19 +7611,19 @@
       <c r="A66" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B66" s="56" t="s">
+      <c r="B66" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="C66" s="56">
+      <c r="C66" s="12">
         <v>1139</v>
       </c>
-      <c r="D66" s="56">
+      <c r="D66" s="12">
         <v>351</v>
       </c>
-      <c r="E66" s="56">
+      <c r="E66" s="12">
         <v>34</v>
       </c>
-      <c r="F66" s="56">
+      <c r="F66" s="12">
         <v>63</v>
       </c>
     </row>
@@ -7634,19 +7631,19 @@
       <c r="A67" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B67" s="56" t="s">
+      <c r="B67" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="C67" s="56">
+      <c r="C67" s="12">
         <v>1079</v>
       </c>
-      <c r="D67" s="56">
+      <c r="D67" s="12">
         <v>349</v>
       </c>
-      <c r="E67" s="56">
+      <c r="E67" s="12">
         <v>37</v>
       </c>
-      <c r="F67" s="56">
+      <c r="F67" s="12">
         <v>63</v>
       </c>
     </row>
@@ -7654,19 +7651,19 @@
       <c r="A68" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B68" s="56" t="s">
+      <c r="B68" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="C68" s="56">
+      <c r="C68" s="12">
         <v>1022</v>
       </c>
-      <c r="D68" s="56">
+      <c r="D68" s="12">
         <v>348</v>
       </c>
-      <c r="E68" s="56">
+      <c r="E68" s="12">
         <v>33</v>
       </c>
-      <c r="F68" s="56">
+      <c r="F68" s="12">
         <v>68</v>
       </c>
     </row>
@@ -7674,19 +7671,19 @@
       <c r="A69" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B69" s="56" t="s">
-        <v>148</v>
-      </c>
-      <c r="C69" s="56">
+      <c r="B69" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C69" s="12">
         <v>1306</v>
       </c>
-      <c r="D69" s="56">
+      <c r="D69" s="12">
         <v>476</v>
       </c>
-      <c r="E69" s="56">
+      <c r="E69" s="12">
         <v>61</v>
       </c>
-      <c r="F69" s="56">
+      <c r="F69" s="12">
         <v>27</v>
       </c>
     </row>
@@ -7694,19 +7691,19 @@
       <c r="A70" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B70" s="56" t="s">
-        <v>283</v>
-      </c>
-      <c r="C70" s="56">
+      <c r="B70" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="C70" s="12">
         <v>1288</v>
       </c>
-      <c r="D70" s="56">
+      <c r="D70" s="12">
         <v>229</v>
       </c>
-      <c r="E70" s="56">
+      <c r="E70" s="12">
         <v>174</v>
       </c>
-      <c r="F70" s="56">
+      <c r="F70" s="12">
         <v>59</v>
       </c>
     </row>
@@ -7714,19 +7711,19 @@
       <c r="A71" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B71" s="56" t="s">
-        <v>284</v>
-      </c>
-      <c r="C71" s="56">
+      <c r="B71" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="C71" s="12">
         <v>1473</v>
       </c>
-      <c r="D71" s="56">
+      <c r="D71" s="12">
         <v>275</v>
       </c>
-      <c r="E71" s="56">
+      <c r="E71" s="12">
         <v>36</v>
       </c>
-      <c r="F71" s="56">
+      <c r="F71" s="12">
         <v>31</v>
       </c>
     </row>
@@ -7734,19 +7731,19 @@
       <c r="A72" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B72" s="56" t="s">
-        <v>285</v>
-      </c>
-      <c r="C72" s="56">
+      <c r="B72" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="C72" s="12">
         <v>1215</v>
       </c>
-      <c r="D72" s="56">
+      <c r="D72" s="12">
         <v>185</v>
       </c>
-      <c r="E72" s="56">
+      <c r="E72" s="12">
         <v>79</v>
       </c>
-      <c r="F72" s="56">
+      <c r="F72" s="12">
         <v>33</v>
       </c>
     </row>
@@ -7754,19 +7751,19 @@
       <c r="A73" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B73" s="56" t="s">
-        <v>286</v>
-      </c>
-      <c r="C73" s="56">
+      <c r="B73" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="C73" s="12">
         <v>697</v>
       </c>
-      <c r="D73" s="56">
+      <c r="D73" s="12">
         <v>184</v>
       </c>
-      <c r="E73" s="56">
+      <c r="E73" s="12">
         <v>125</v>
       </c>
-      <c r="F73" s="56">
+      <c r="F73" s="12">
         <v>52</v>
       </c>
     </row>
@@ -7774,19 +7771,19 @@
       <c r="A74" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B74" s="56" t="s">
-        <v>287</v>
-      </c>
-      <c r="C74" s="56">
+      <c r="B74" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="C74" s="12">
         <v>1048</v>
       </c>
-      <c r="D74" s="56">
+      <c r="D74" s="12">
         <v>271</v>
       </c>
-      <c r="E74" s="56">
+      <c r="E74" s="12">
         <v>64</v>
       </c>
-      <c r="F74" s="56">
+      <c r="F74" s="12">
         <v>34</v>
       </c>
     </row>
@@ -7794,19 +7791,19 @@
       <c r="A75" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B75" s="56" t="s">
-        <v>288</v>
-      </c>
-      <c r="C75" s="56">
+      <c r="B75" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="C75" s="12">
         <v>1313</v>
       </c>
-      <c r="D75" s="56">
+      <c r="D75" s="12">
         <v>190</v>
       </c>
-      <c r="E75" s="56">
+      <c r="E75" s="12">
         <v>59</v>
       </c>
-      <c r="F75" s="56">
+      <c r="F75" s="12">
         <v>27</v>
       </c>
     </row>
@@ -7814,19 +7811,19 @@
       <c r="A76" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B76" s="56" t="s">
-        <v>289</v>
-      </c>
-      <c r="C76" s="56">
+      <c r="B76" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="C76" s="12">
         <v>890</v>
       </c>
-      <c r="D76" s="56">
+      <c r="D76" s="12">
         <v>269</v>
       </c>
-      <c r="E76" s="56">
+      <c r="E76" s="12">
         <v>63</v>
       </c>
-      <c r="F76" s="56">
+      <c r="F76" s="12">
         <v>33</v>
       </c>
     </row>
@@ -7834,19 +7831,19 @@
       <c r="A77" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B77" s="56" t="s">
-        <v>290</v>
-      </c>
-      <c r="C77" s="56">
+      <c r="B77" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="C77" s="12">
         <v>1393</v>
       </c>
-      <c r="D77" s="56">
+      <c r="D77" s="12">
         <v>191</v>
       </c>
-      <c r="E77" s="56">
+      <c r="E77" s="12">
         <v>65</v>
       </c>
-      <c r="F77" s="56">
+      <c r="F77" s="12">
         <v>30</v>
       </c>
     </row>
@@ -7854,19 +7851,19 @@
       <c r="A78" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B78" s="56" t="s">
-        <v>291</v>
-      </c>
-      <c r="C78" s="56">
+      <c r="B78" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="C78" s="12">
         <v>970</v>
       </c>
-      <c r="D78" s="56">
+      <c r="D78" s="12">
         <v>213</v>
       </c>
-      <c r="E78" s="56">
+      <c r="E78" s="12">
         <v>63</v>
       </c>
-      <c r="F78" s="56">
+      <c r="F78" s="12">
         <v>31</v>
       </c>
     </row>
@@ -7874,19 +7871,19 @@
       <c r="A79" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B79" s="56" t="s">
-        <v>292</v>
-      </c>
-      <c r="C79" s="56">
+      <c r="B79" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="C79" s="12">
         <v>969</v>
       </c>
-      <c r="D79" s="56">
+      <c r="D79" s="12">
         <v>271</v>
       </c>
-      <c r="E79" s="56">
+      <c r="E79" s="12">
         <v>63</v>
       </c>
-      <c r="F79" s="56">
+      <c r="F79" s="12">
         <v>30</v>
       </c>
     </row>
@@ -7894,19 +7891,19 @@
       <c r="A80" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B80" s="56" t="s">
-        <v>293</v>
-      </c>
-      <c r="C80" s="56">
+      <c r="B80" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C80" s="12">
         <v>889</v>
       </c>
-      <c r="D80" s="56">
+      <c r="D80" s="12">
         <v>213</v>
       </c>
-      <c r="E80" s="56">
+      <c r="E80" s="12">
         <v>63</v>
       </c>
-      <c r="F80" s="56">
+      <c r="F80" s="12">
         <v>31</v>
       </c>
     </row>
@@ -7914,19 +7911,19 @@
       <c r="A81" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B81" s="56" t="s">
-        <v>294</v>
-      </c>
-      <c r="C81" s="56">
+      <c r="B81" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="C81" s="12">
         <v>1051</v>
       </c>
-      <c r="D81" s="56">
+      <c r="D81" s="12">
         <v>213</v>
       </c>
-      <c r="E81" s="56">
+      <c r="E81" s="12">
         <v>60</v>
       </c>
-      <c r="F81" s="56">
+      <c r="F81" s="12">
         <v>32</v>
       </c>
     </row>
@@ -7934,19 +7931,19 @@
       <c r="A82" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B82" s="56" t="s">
-        <v>295</v>
-      </c>
-      <c r="C82" s="56">
+      <c r="B82" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="C82" s="12">
         <v>1217</v>
       </c>
-      <c r="D82" s="56">
+      <c r="D82" s="12">
         <v>273</v>
       </c>
-      <c r="E82" s="56">
+      <c r="E82" s="12">
         <v>60</v>
       </c>
-      <c r="F82" s="56">
+      <c r="F82" s="12">
         <v>30</v>
       </c>
     </row>
@@ -7954,19 +7951,19 @@
       <c r="A83" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B83" s="56" t="s">
-        <v>167</v>
-      </c>
-      <c r="C83" s="56">
+      <c r="B83" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="C83" s="12">
         <v>1305</v>
       </c>
-      <c r="D83" s="56">
+      <c r="D83" s="12">
         <v>444</v>
       </c>
-      <c r="E83" s="56">
+      <c r="E83" s="12">
         <v>53</v>
       </c>
-      <c r="F83" s="56">
+      <c r="F83" s="12">
         <v>29</v>
       </c>
     </row>
@@ -7974,19 +7971,19 @@
       <c r="A84" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="B84" s="57" t="s">
-        <v>142</v>
-      </c>
-      <c r="C84" s="57">
+      <c r="B84" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="C84" s="12">
         <v>1466</v>
       </c>
-      <c r="D84" s="57">
+      <c r="D84" s="12">
         <v>364</v>
       </c>
-      <c r="E84" s="57">
+      <c r="E84" s="12">
         <v>70</v>
       </c>
-      <c r="F84" s="57">
+      <c r="F84" s="12">
         <v>35</v>
       </c>
     </row>
@@ -7994,19 +7991,19 @@
       <c r="A85" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="B85" s="57" t="s">
+      <c r="B85" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="C85" s="57">
+      <c r="C85" s="12">
         <v>1308</v>
       </c>
-      <c r="D85" s="57">
+      <c r="D85" s="12">
         <v>196</v>
       </c>
-      <c r="E85" s="57">
+      <c r="E85" s="12">
         <v>125</v>
       </c>
-      <c r="F85" s="57">
+      <c r="F85" s="12">
         <v>59</v>
       </c>
     </row>
@@ -8014,19 +8011,19 @@
       <c r="A86" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="B86" s="57" t="s">
-        <v>113</v>
-      </c>
-      <c r="C86" s="57">
+      <c r="B86" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C86" s="12">
         <v>1309</v>
       </c>
-      <c r="D86" s="57">
+      <c r="D86" s="12">
         <v>309</v>
       </c>
-      <c r="E86" s="57">
+      <c r="E86" s="12">
         <v>121</v>
       </c>
-      <c r="F86" s="57">
+      <c r="F86" s="12">
         <v>59</v>
       </c>
     </row>
@@ -8034,19 +8031,19 @@
       <c r="A87" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="B87" s="57" t="s">
-        <v>117</v>
-      </c>
-      <c r="C87" s="57">
+      <c r="B87" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C87" s="12">
         <v>1364</v>
       </c>
-      <c r="D87" s="57">
+      <c r="D87" s="12">
         <v>425</v>
       </c>
-      <c r="E87" s="57">
+      <c r="E87" s="12">
         <v>70</v>
       </c>
-      <c r="F87" s="57">
+      <c r="F87" s="12">
         <v>37</v>
       </c>
     </row>
@@ -8054,19 +8051,19 @@
       <c r="A88" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="B88" s="57" t="s">
-        <v>118</v>
-      </c>
-      <c r="C88" s="57">
+      <c r="B88" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C88" s="12">
         <v>1238</v>
       </c>
-      <c r="D88" s="57">
+      <c r="D88" s="12">
         <v>426</v>
       </c>
-      <c r="E88" s="57">
+      <c r="E88" s="12">
         <v>73</v>
       </c>
-      <c r="F88" s="57">
+      <c r="F88" s="12">
         <v>37</v>
       </c>
     </row>
@@ -8074,19 +8071,19 @@
       <c r="A89" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="B89" s="57" t="s">
-        <v>154</v>
-      </c>
-      <c r="C89" s="57">
+      <c r="B89" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="C89" s="12">
         <v>1142</v>
       </c>
-      <c r="D89" s="57">
+      <c r="D89" s="12">
         <v>135</v>
       </c>
-      <c r="E89" s="57">
+      <c r="E89" s="12">
         <v>91</v>
       </c>
-      <c r="F89" s="57">
+      <c r="F89" s="12">
         <v>38</v>
       </c>
     </row>
@@ -8094,19 +8091,19 @@
       <c r="A90" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="B90" s="57" t="s">
+      <c r="B90" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="C90" s="57">
+      <c r="C90" s="12">
         <v>1069</v>
       </c>
-      <c r="D90" s="57">
+      <c r="D90" s="12">
         <v>196</v>
       </c>
-      <c r="E90" s="57">
+      <c r="E90" s="12">
         <v>176</v>
       </c>
-      <c r="F90" s="57">
+      <c r="F90" s="12">
         <v>59</v>
       </c>
     </row>
@@ -8114,19 +8111,19 @@
       <c r="A91" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="B91" s="57" t="s">
+      <c r="B91" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C91" s="57">
+      <c r="C91" s="12">
         <v>1072</v>
       </c>
-      <c r="D91" s="57">
+      <c r="D91" s="12">
         <v>314</v>
       </c>
-      <c r="E91" s="57">
+      <c r="E91" s="12">
         <v>174</v>
       </c>
-      <c r="F91" s="57">
+      <c r="F91" s="12">
         <v>59</v>
       </c>
     </row>
@@ -8134,19 +8131,19 @@
       <c r="A92" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="B92" s="57" t="s">
-        <v>119</v>
-      </c>
-      <c r="C92" s="57">
+      <c r="B92" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C92" s="12">
         <v>1117</v>
       </c>
-      <c r="D92" s="57">
+      <c r="D92" s="12">
         <v>425</v>
       </c>
-      <c r="E92" s="57">
+      <c r="E92" s="12">
         <v>69</v>
       </c>
-      <c r="F92" s="57">
+      <c r="F92" s="12">
         <v>36</v>
       </c>
     </row>
@@ -8154,19 +8151,19 @@
       <c r="A93" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="B93" s="57" t="s">
-        <v>137</v>
-      </c>
-      <c r="C93" s="57">
+      <c r="B93" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="C93" s="12">
         <v>915</v>
       </c>
-      <c r="D93" s="57">
+      <c r="D93" s="12">
         <v>458</v>
       </c>
-      <c r="E93" s="57">
+      <c r="E93" s="12">
         <v>64</v>
       </c>
-      <c r="F93" s="57">
+      <c r="F93" s="12">
         <v>36</v>
       </c>
     </row>
@@ -8174,19 +8171,19 @@
       <c r="A94" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="B94" s="57" t="s">
+      <c r="B94" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="C94" s="57">
+      <c r="C94" s="12">
         <v>783</v>
       </c>
-      <c r="D94" s="57">
+      <c r="D94" s="12">
         <v>325</v>
       </c>
-      <c r="E94" s="57">
+      <c r="E94" s="12">
         <v>172</v>
       </c>
-      <c r="F94" s="57">
+      <c r="F94" s="12">
         <v>56</v>
       </c>
     </row>
@@ -8194,19 +8191,19 @@
       <c r="A95" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="B95" s="57" t="s">
+      <c r="B95" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="C95" s="57">
+      <c r="C95" s="12">
         <v>914</v>
       </c>
-      <c r="D95" s="57">
+      <c r="D95" s="12">
         <v>148</v>
       </c>
-      <c r="E95" s="57">
+      <c r="E95" s="12">
         <v>64</v>
       </c>
-      <c r="F95" s="57">
+      <c r="F95" s="12">
         <v>35</v>
       </c>
     </row>
@@ -8214,19 +8211,19 @@
       <c r="A96" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="B96" s="57" t="s">
-        <v>120</v>
-      </c>
-      <c r="C96" s="57">
+      <c r="B96" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C96" s="12">
         <v>817</v>
       </c>
-      <c r="D96" s="57">
+      <c r="D96" s="12">
         <v>458</v>
       </c>
-      <c r="E96" s="57">
+      <c r="E96" s="12">
         <v>73</v>
       </c>
-      <c r="F96" s="57">
+      <c r="F96" s="12">
         <v>38</v>
       </c>
     </row>
@@ -8234,19 +8231,19 @@
       <c r="A97" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="B97" s="57" t="s">
-        <v>110</v>
-      </c>
-      <c r="C97" s="57">
+      <c r="B97" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C97" s="12">
         <v>650</v>
       </c>
-      <c r="D97" s="57">
+      <c r="D97" s="12">
         <v>330</v>
       </c>
-      <c r="E97" s="57">
+      <c r="E97" s="12">
         <v>32</v>
       </c>
-      <c r="F97" s="57">
+      <c r="F97" s="12">
         <v>88</v>
       </c>
     </row>
@@ -8254,19 +8251,19 @@
       <c r="A98" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="B98" s="57" t="s">
+      <c r="B98" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="C98" s="57">
+      <c r="C98" s="12">
         <v>586</v>
       </c>
-      <c r="D98" s="57">
+      <c r="D98" s="12">
         <v>329</v>
       </c>
-      <c r="E98" s="57">
+      <c r="E98" s="12">
         <v>39</v>
       </c>
-      <c r="F98" s="57">
+      <c r="F98" s="12">
         <v>89</v>
       </c>
     </row>
@@ -8274,19 +8271,19 @@
       <c r="A99" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="B99" s="57" t="s">
+      <c r="B99" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="C99" s="57">
+      <c r="C99" s="12">
         <v>296</v>
       </c>
-      <c r="D99" s="57">
+      <c r="D99" s="12">
         <v>343</v>
       </c>
-      <c r="E99" s="57">
+      <c r="E99" s="12">
         <v>59</v>
       </c>
-      <c r="F99" s="57">
+      <c r="F99" s="12">
         <v>170</v>
       </c>
     </row>
@@ -8294,19 +8291,19 @@
       <c r="A100" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="B100" s="57" t="s">
+      <c r="B100" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="C100" s="57">
+      <c r="C100" s="12">
         <v>467</v>
       </c>
-      <c r="D100" s="57">
+      <c r="D100" s="12">
         <v>442</v>
       </c>
-      <c r="E100" s="57">
+      <c r="E100" s="12">
         <v>38</v>
       </c>
-      <c r="F100" s="57">
+      <c r="F100" s="12">
         <v>69</v>
       </c>
     </row>
@@ -8314,19 +8311,19 @@
       <c r="A101" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="B101" s="57" t="s">
+      <c r="B101" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="C101" s="57">
+      <c r="C101" s="12">
         <v>530</v>
       </c>
-      <c r="D101" s="57">
+      <c r="D101" s="12">
         <v>444</v>
       </c>
-      <c r="E101" s="57">
+      <c r="E101" s="12">
         <v>35</v>
       </c>
-      <c r="F101" s="57">
+      <c r="F101" s="12">
         <v>66</v>
       </c>
     </row>
@@ -8334,19 +8331,19 @@
       <c r="A102" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="B102" s="57" t="s">
+      <c r="B102" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="C102" s="57">
+      <c r="C102" s="12">
         <v>586</v>
       </c>
-      <c r="D102" s="57">
+      <c r="D102" s="12">
         <v>443</v>
       </c>
-      <c r="E102" s="57">
+      <c r="E102" s="12">
         <v>36</v>
       </c>
-      <c r="F102" s="57">
+      <c r="F102" s="12">
         <v>68</v>
       </c>
     </row>
@@ -8354,19 +8351,19 @@
       <c r="A103" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="B103" s="57" t="s">
+      <c r="B103" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="C103" s="57">
+      <c r="C103" s="12">
         <v>648</v>
       </c>
-      <c r="D103" s="57">
+      <c r="D103" s="12">
         <v>442</v>
       </c>
-      <c r="E103" s="57">
+      <c r="E103" s="12">
         <v>37</v>
       </c>
-      <c r="F103" s="57">
+      <c r="F103" s="12">
         <v>71</v>
       </c>
     </row>
@@ -8374,19 +8371,19 @@
       <c r="A104" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="B104" s="57" t="s">
+      <c r="B104" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="C104" s="57">
+      <c r="C104" s="12">
         <v>409</v>
       </c>
-      <c r="D104" s="57">
+      <c r="D104" s="12">
         <v>440</v>
       </c>
-      <c r="E104" s="57">
+      <c r="E104" s="12">
         <v>35</v>
       </c>
-      <c r="F104" s="57">
+      <c r="F104" s="12">
         <v>72</v>
       </c>
     </row>
@@ -8394,19 +8391,19 @@
       <c r="A105" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="B105" s="57" t="s">
+      <c r="B105" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="C105" s="57">
+      <c r="C105" s="12">
         <v>408</v>
       </c>
-      <c r="D105" s="57">
+      <c r="D105" s="12">
         <v>331</v>
       </c>
-      <c r="E105" s="57">
+      <c r="E105" s="12">
         <v>38</v>
       </c>
-      <c r="F105" s="57">
+      <c r="F105" s="12">
         <v>70</v>
       </c>
     </row>
@@ -8414,19 +8411,19 @@
       <c r="A106" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="B106" s="57" t="s">
+      <c r="B106" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="C106" s="57">
+      <c r="C106" s="12">
         <v>469</v>
       </c>
-      <c r="D106" s="57">
+      <c r="D106" s="12">
         <v>333</v>
       </c>
-      <c r="E106" s="57">
+      <c r="E106" s="12">
         <v>37</v>
       </c>
-      <c r="F106" s="57">
+      <c r="F106" s="12">
         <v>68</v>
       </c>
     </row>
@@ -8434,19 +8431,19 @@
       <c r="A107" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="B107" s="57" t="s">
+      <c r="B107" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="C107" s="57">
+      <c r="C107" s="12">
         <v>529</v>
       </c>
-      <c r="D107" s="57">
+      <c r="D107" s="12">
         <v>331</v>
       </c>
-      <c r="E107" s="57">
+      <c r="E107" s="12">
         <v>36</v>
       </c>
-      <c r="F107" s="57">
+      <c r="F107" s="12">
         <v>70</v>
       </c>
     </row>
@@ -8454,19 +8451,19 @@
       <c r="A108" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="B108" s="57" t="s">
-        <v>148</v>
-      </c>
-      <c r="C108" s="57">
+      <c r="B108" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C108" s="12">
         <v>210</v>
       </c>
-      <c r="D108" s="57">
+      <c r="D108" s="12">
         <v>467</v>
       </c>
-      <c r="E108" s="57">
+      <c r="E108" s="12">
         <v>67</v>
       </c>
-      <c r="F108" s="57">
+      <c r="F108" s="12">
         <v>37</v>
       </c>
     </row>
@@ -8498,3422 +8495,494 @@
       <c r="E112" s="33"/>
       <c r="F112" s="33"/>
     </row>
-    <row r="113" spans="2:6">
-      <c r="B113" s="33"/>
-      <c r="C113" s="33"/>
-      <c r="D113" s="33"/>
-      <c r="E113" s="33"/>
-      <c r="F113" s="33"/>
-    </row>
-    <row r="114" spans="2:6">
-      <c r="B114" s="33"/>
-      <c r="C114" s="33"/>
-      <c r="D114" s="33"/>
-      <c r="E114" s="33"/>
-      <c r="F114" s="33"/>
-    </row>
-    <row r="115" spans="2:6">
-      <c r="B115" s="33"/>
-      <c r="C115" s="33"/>
-      <c r="D115" s="33"/>
-      <c r="E115" s="33"/>
-      <c r="F115" s="33"/>
-    </row>
-    <row r="116" spans="2:6">
-      <c r="B116" s="33"/>
-      <c r="C116" s="33"/>
-      <c r="D116" s="33"/>
-      <c r="E116" s="33"/>
-      <c r="F116" s="33"/>
-    </row>
-    <row r="117" spans="2:6">
-      <c r="B117" s="33"/>
-      <c r="C117" s="33"/>
-      <c r="D117" s="33"/>
-      <c r="E117" s="33"/>
-      <c r="F117" s="33"/>
-    </row>
-    <row r="118" spans="2:6">
-      <c r="B118" s="33"/>
-      <c r="C118" s="33"/>
-      <c r="D118" s="33"/>
-      <c r="E118" s="33"/>
-      <c r="F118" s="33"/>
-    </row>
-    <row r="119" spans="2:6">
-      <c r="B119" s="33"/>
-      <c r="C119" s="33"/>
-      <c r="D119" s="33"/>
-      <c r="E119" s="33"/>
-      <c r="F119" s="33"/>
-    </row>
-    <row r="120" spans="2:6">
-      <c r="B120" s="33"/>
-      <c r="C120" s="33"/>
-      <c r="D120" s="33"/>
-      <c r="E120" s="33"/>
-      <c r="F120" s="33"/>
-    </row>
-    <row r="121" spans="2:6">
-      <c r="B121" s="33"/>
-      <c r="C121" s="33"/>
-      <c r="D121" s="33"/>
-      <c r="E121" s="33"/>
-      <c r="F121" s="33"/>
-    </row>
-    <row r="122" spans="2:6">
-      <c r="B122" s="33"/>
-      <c r="C122" s="33"/>
-      <c r="D122" s="33"/>
-      <c r="E122" s="33"/>
-      <c r="F122" s="33"/>
-    </row>
-    <row r="123" spans="2:6">
-      <c r="B123" s="33"/>
-      <c r="C123" s="33"/>
-      <c r="D123" s="33"/>
-      <c r="E123" s="33"/>
-      <c r="F123" s="33"/>
-    </row>
-    <row r="124" spans="2:6">
-      <c r="B124" s="33"/>
-      <c r="C124" s="33"/>
-      <c r="D124" s="33"/>
-      <c r="E124" s="33"/>
-      <c r="F124" s="33"/>
-    </row>
-    <row r="125" spans="2:6">
-      <c r="B125" s="33"/>
-      <c r="C125" s="33"/>
-      <c r="D125" s="33"/>
-      <c r="E125" s="33"/>
-      <c r="F125" s="33"/>
-    </row>
-    <row r="126" spans="2:6">
-      <c r="B126" s="33"/>
-      <c r="C126" s="33"/>
-      <c r="D126" s="33"/>
-      <c r="E126" s="33"/>
-      <c r="F126" s="33"/>
-    </row>
-    <row r="127" spans="2:6">
-      <c r="B127" s="33"/>
-      <c r="C127" s="33"/>
-      <c r="D127" s="33"/>
-      <c r="E127" s="33"/>
-      <c r="F127" s="33"/>
-    </row>
-    <row r="128" spans="2:6">
-      <c r="B128" s="33"/>
-      <c r="C128" s="33"/>
-      <c r="D128" s="33"/>
-      <c r="E128" s="33"/>
-      <c r="F128" s="33"/>
-    </row>
-    <row r="129" spans="2:6">
-      <c r="B129" s="33"/>
-      <c r="C129" s="33"/>
-      <c r="D129" s="33"/>
-      <c r="E129" s="33"/>
-      <c r="F129" s="33"/>
-    </row>
-    <row r="130" spans="2:6">
-      <c r="B130" s="33"/>
-      <c r="C130" s="33"/>
-      <c r="D130" s="33"/>
-      <c r="E130" s="33"/>
-      <c r="F130" s="33"/>
-    </row>
-    <row r="131" spans="2:6">
-      <c r="B131" s="33"/>
-      <c r="C131" s="33"/>
-      <c r="D131" s="33"/>
-      <c r="E131" s="33"/>
-      <c r="F131" s="33"/>
-    </row>
-    <row r="132" spans="2:6">
-      <c r="B132" s="33"/>
-      <c r="C132" s="33"/>
-      <c r="D132" s="33"/>
-      <c r="E132" s="33"/>
-      <c r="F132" s="33"/>
-    </row>
-    <row r="133" spans="2:6">
-      <c r="B133" s="33"/>
-      <c r="C133" s="33"/>
-      <c r="D133" s="33"/>
-      <c r="E133" s="33"/>
-      <c r="F133" s="33"/>
-    </row>
-    <row r="134" spans="2:6">
-      <c r="B134" s="33"/>
-      <c r="C134" s="33"/>
-      <c r="D134" s="33"/>
-      <c r="E134" s="33"/>
-      <c r="F134" s="33"/>
-    </row>
-    <row r="135" spans="2:6">
-      <c r="B135" s="33"/>
-      <c r="C135" s="33"/>
-      <c r="D135" s="33"/>
-      <c r="E135" s="33"/>
-      <c r="F135" s="33"/>
-    </row>
-    <row r="136" spans="2:6">
-      <c r="B136" s="33"/>
-      <c r="C136" s="33"/>
-      <c r="D136" s="33"/>
-      <c r="E136" s="33"/>
-      <c r="F136" s="33"/>
-    </row>
-    <row r="137" spans="2:6">
-      <c r="B137" s="33"/>
-      <c r="C137" s="33"/>
-      <c r="D137" s="33"/>
-      <c r="E137" s="33"/>
-      <c r="F137" s="33"/>
-    </row>
-    <row r="138" spans="2:6">
-      <c r="B138" s="33"/>
-      <c r="C138" s="33"/>
-      <c r="D138" s="33"/>
-      <c r="E138" s="33"/>
-      <c r="F138" s="33"/>
-    </row>
-    <row r="139" spans="2:6">
-      <c r="B139" s="33"/>
-      <c r="C139" s="33"/>
-      <c r="D139" s="33"/>
-      <c r="E139" s="33"/>
-      <c r="F139" s="33"/>
-    </row>
-    <row r="140" spans="2:6">
-      <c r="B140" s="33"/>
-      <c r="C140" s="33"/>
-      <c r="D140" s="33"/>
-      <c r="E140" s="33"/>
-      <c r="F140" s="33"/>
-    </row>
-    <row r="141" spans="2:6">
-      <c r="B141" s="33"/>
-      <c r="C141" s="33"/>
-      <c r="D141" s="33"/>
-      <c r="E141" s="33"/>
-      <c r="F141" s="33"/>
-    </row>
-    <row r="142" spans="2:6">
-      <c r="B142" s="33"/>
-      <c r="C142" s="33"/>
-      <c r="D142" s="33"/>
-      <c r="E142" s="33"/>
-      <c r="F142" s="33"/>
-    </row>
-    <row r="143" spans="2:6">
-      <c r="B143" s="33"/>
-      <c r="C143" s="33"/>
-      <c r="D143" s="33"/>
-      <c r="E143" s="33"/>
-      <c r="F143" s="33"/>
-    </row>
-    <row r="144" spans="2:6">
-      <c r="B144" s="33"/>
-      <c r="C144" s="33"/>
-      <c r="D144" s="33"/>
-      <c r="E144" s="33"/>
-      <c r="F144" s="33"/>
-    </row>
-    <row r="145" spans="2:6">
-      <c r="B145" s="33"/>
-      <c r="C145" s="33"/>
-      <c r="D145" s="33"/>
-      <c r="E145" s="33"/>
-      <c r="F145" s="33"/>
-    </row>
-    <row r="146" spans="2:6">
-      <c r="B146" s="33"/>
-      <c r="C146" s="33"/>
-      <c r="D146" s="33"/>
-      <c r="E146" s="33"/>
-      <c r="F146" s="33"/>
-    </row>
-    <row r="147" spans="2:6">
-      <c r="B147" s="33"/>
-      <c r="C147" s="33"/>
-      <c r="D147" s="33"/>
-      <c r="E147" s="33"/>
-      <c r="F147" s="33"/>
-    </row>
-    <row r="148" spans="2:6">
-      <c r="B148" s="33"/>
-      <c r="C148" s="33"/>
-      <c r="D148" s="33"/>
-      <c r="E148" s="33"/>
-      <c r="F148" s="33"/>
-    </row>
-    <row r="149" spans="2:6">
-      <c r="B149" s="33"/>
-      <c r="C149" s="33"/>
-      <c r="D149" s="33"/>
-      <c r="E149" s="33"/>
-      <c r="F149" s="33"/>
-    </row>
-    <row r="150" spans="2:6">
-      <c r="B150" s="33"/>
-      <c r="C150" s="33"/>
-      <c r="D150" s="33"/>
-      <c r="E150" s="33"/>
-      <c r="F150" s="33"/>
-    </row>
-    <row r="151" spans="2:6">
-      <c r="B151" s="33"/>
-      <c r="C151" s="33"/>
-      <c r="D151" s="33"/>
-      <c r="E151" s="33"/>
-      <c r="F151" s="33"/>
-    </row>
-    <row r="152" spans="2:6">
-      <c r="B152" s="33"/>
-      <c r="C152" s="33"/>
-      <c r="D152" s="33"/>
-      <c r="E152" s="33"/>
-      <c r="F152" s="33"/>
-    </row>
-    <row r="153" spans="2:6">
-      <c r="B153" s="33"/>
-      <c r="C153" s="33"/>
-      <c r="D153" s="33"/>
-      <c r="E153" s="33"/>
-      <c r="F153" s="33"/>
-    </row>
-    <row r="154" spans="2:6">
-      <c r="B154" s="33"/>
-      <c r="C154" s="33"/>
-      <c r="D154" s="33"/>
-      <c r="E154" s="33"/>
-      <c r="F154" s="33"/>
-    </row>
-    <row r="155" spans="2:6">
-      <c r="B155" s="33"/>
-      <c r="C155" s="33"/>
-      <c r="D155" s="33"/>
-      <c r="E155" s="33"/>
-      <c r="F155" s="33"/>
-    </row>
-    <row r="156" spans="2:6">
-      <c r="B156" s="33"/>
-      <c r="C156" s="33"/>
-      <c r="D156" s="33"/>
-      <c r="E156" s="33"/>
-      <c r="F156" s="33"/>
-    </row>
-    <row r="157" spans="2:6">
-      <c r="B157" s="33"/>
-      <c r="C157" s="33"/>
-      <c r="D157" s="33"/>
-      <c r="E157" s="33"/>
-      <c r="F157" s="33"/>
-    </row>
-    <row r="158" spans="2:6">
-      <c r="B158" s="33"/>
-      <c r="C158" s="33"/>
-      <c r="D158" s="33"/>
-      <c r="E158" s="33"/>
-      <c r="F158" s="33"/>
-    </row>
-    <row r="159" spans="2:6">
-      <c r="B159" s="33"/>
-      <c r="C159" s="33"/>
-      <c r="D159" s="33"/>
-      <c r="E159" s="33"/>
-      <c r="F159" s="33"/>
-    </row>
-    <row r="160" spans="2:6">
-      <c r="B160" s="33"/>
-      <c r="C160" s="33"/>
-      <c r="D160" s="33"/>
-      <c r="E160" s="33"/>
-      <c r="F160" s="33"/>
-    </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="33"/>
-      <c r="C161" s="33"/>
-      <c r="D161" s="33"/>
-      <c r="E161" s="33"/>
-      <c r="F161" s="33"/>
-    </row>
-    <row r="162" spans="2:6">
-      <c r="B162" s="33"/>
-      <c r="C162" s="33"/>
-      <c r="D162" s="33"/>
-      <c r="E162" s="33"/>
-      <c r="F162" s="33"/>
-    </row>
-    <row r="163" spans="2:6">
-      <c r="B163" s="33"/>
-      <c r="C163" s="33"/>
-      <c r="D163" s="33"/>
-      <c r="E163" s="33"/>
-      <c r="F163" s="33"/>
-    </row>
-    <row r="164" spans="2:6">
-      <c r="B164" s="33"/>
-      <c r="C164" s="33"/>
-      <c r="D164" s="33"/>
-      <c r="E164" s="33"/>
-      <c r="F164" s="33"/>
-    </row>
-    <row r="165" spans="2:6">
-      <c r="B165" s="33"/>
-      <c r="C165" s="33"/>
-      <c r="D165" s="33"/>
-      <c r="E165" s="33"/>
-      <c r="F165" s="33"/>
-    </row>
-    <row r="166" spans="2:6">
-      <c r="B166" s="33"/>
-      <c r="C166" s="33"/>
-      <c r="D166" s="33"/>
-      <c r="E166" s="33"/>
-      <c r="F166" s="33"/>
-    </row>
-    <row r="167" spans="2:6">
-      <c r="B167" s="33"/>
-      <c r="C167" s="33"/>
-      <c r="D167" s="33"/>
-      <c r="E167" s="33"/>
-      <c r="F167" s="33"/>
-    </row>
-    <row r="168" spans="2:6">
-      <c r="B168" s="33"/>
-      <c r="C168" s="33"/>
-      <c r="D168" s="33"/>
-      <c r="E168" s="33"/>
-      <c r="F168" s="33"/>
-    </row>
-    <row r="169" spans="2:6">
-      <c r="B169" s="33"/>
-      <c r="C169" s="33"/>
-      <c r="D169" s="33"/>
-      <c r="E169" s="33"/>
-      <c r="F169" s="33"/>
-    </row>
-    <row r="170" spans="2:6">
-      <c r="B170" s="33"/>
-      <c r="C170" s="33"/>
-      <c r="D170" s="33"/>
-      <c r="E170" s="33"/>
-      <c r="F170" s="33"/>
-    </row>
-    <row r="171" spans="2:6">
-      <c r="B171" s="33"/>
-      <c r="C171" s="33"/>
-      <c r="D171" s="33"/>
-      <c r="E171" s="33"/>
-      <c r="F171" s="33"/>
-    </row>
-    <row r="172" spans="2:6">
-      <c r="B172" s="33"/>
-      <c r="C172" s="33"/>
-      <c r="D172" s="33"/>
-      <c r="E172" s="33"/>
-      <c r="F172" s="33"/>
-    </row>
-    <row r="173" spans="2:6">
-      <c r="B173" s="33"/>
-      <c r="C173" s="33"/>
-      <c r="D173" s="33"/>
-      <c r="E173" s="33"/>
-      <c r="F173" s="33"/>
-    </row>
-    <row r="174" spans="2:6">
-      <c r="B174" s="33"/>
-      <c r="C174" s="33"/>
-      <c r="D174" s="33"/>
-      <c r="E174" s="33"/>
-      <c r="F174" s="33"/>
-    </row>
-    <row r="175" spans="2:6">
-      <c r="B175" s="33"/>
-      <c r="C175" s="33"/>
-      <c r="D175" s="33"/>
-      <c r="E175" s="33"/>
-      <c r="F175" s="33"/>
-    </row>
-    <row r="176" spans="2:6">
-      <c r="B176" s="33"/>
-      <c r="C176" s="33"/>
-      <c r="D176" s="33"/>
-      <c r="E176" s="33"/>
-      <c r="F176" s="33"/>
-    </row>
-    <row r="177" spans="2:6">
-      <c r="B177" s="33"/>
-      <c r="C177" s="33"/>
-      <c r="D177" s="33"/>
-      <c r="E177" s="33"/>
-      <c r="F177" s="33"/>
-    </row>
-    <row r="178" spans="2:6">
-      <c r="B178" s="33"/>
-      <c r="C178" s="33"/>
-      <c r="D178" s="33"/>
-      <c r="E178" s="33"/>
-      <c r="F178" s="33"/>
-    </row>
-    <row r="179" spans="2:6">
-      <c r="B179" s="33"/>
-      <c r="C179" s="33"/>
-      <c r="D179" s="33"/>
-      <c r="E179" s="33"/>
-      <c r="F179" s="33"/>
-    </row>
-    <row r="180" spans="2:6">
-      <c r="B180" s="33"/>
-      <c r="C180" s="33"/>
-      <c r="D180" s="33"/>
-      <c r="E180" s="33"/>
-      <c r="F180" s="33"/>
-    </row>
-    <row r="181" spans="2:6">
-      <c r="B181" s="33"/>
-      <c r="C181" s="33"/>
-      <c r="D181" s="33"/>
-      <c r="E181" s="33"/>
-      <c r="F181" s="33"/>
-    </row>
-    <row r="182" spans="2:6">
-      <c r="B182" s="33"/>
-      <c r="C182" s="33"/>
-      <c r="D182" s="33"/>
-      <c r="E182" s="33"/>
-      <c r="F182" s="33"/>
-    </row>
-    <row r="183" spans="2:6">
-      <c r="B183" s="33"/>
-      <c r="C183" s="33"/>
-      <c r="D183" s="33"/>
-      <c r="E183" s="33"/>
-      <c r="F183" s="33"/>
-    </row>
-    <row r="184" spans="2:6">
-      <c r="B184" s="33"/>
-      <c r="C184" s="33"/>
-      <c r="D184" s="33"/>
-      <c r="E184" s="33"/>
-      <c r="F184" s="33"/>
-    </row>
-    <row r="185" spans="2:6">
-      <c r="B185" s="33"/>
-      <c r="C185" s="33"/>
-      <c r="D185" s="33"/>
-      <c r="E185" s="33"/>
-      <c r="F185" s="33"/>
-    </row>
-    <row r="186" spans="2:6">
-      <c r="B186" s="33"/>
-      <c r="C186" s="33"/>
-      <c r="D186" s="33"/>
-      <c r="E186" s="33"/>
-      <c r="F186" s="33"/>
-    </row>
-    <row r="187" spans="2:6">
-      <c r="B187" s="33"/>
-      <c r="C187" s="33"/>
-      <c r="D187" s="33"/>
-      <c r="E187" s="33"/>
-      <c r="F187" s="33"/>
-    </row>
-    <row r="188" spans="2:6">
-      <c r="B188" s="33"/>
-      <c r="C188" s="33"/>
-      <c r="D188" s="33"/>
-      <c r="E188" s="33"/>
-      <c r="F188" s="33"/>
-    </row>
-    <row r="189" spans="2:6">
-      <c r="B189" s="33"/>
-      <c r="C189" s="33"/>
-      <c r="D189" s="33"/>
-      <c r="E189" s="33"/>
-      <c r="F189" s="33"/>
-    </row>
-    <row r="190" spans="2:6">
-      <c r="B190" s="33"/>
-      <c r="C190" s="33"/>
-      <c r="D190" s="33"/>
-      <c r="E190" s="33"/>
-      <c r="F190" s="33"/>
-    </row>
-    <row r="191" spans="2:6">
-      <c r="B191" s="33"/>
-      <c r="C191" s="33"/>
-      <c r="D191" s="33"/>
-      <c r="E191" s="33"/>
-      <c r="F191" s="33"/>
-    </row>
-    <row r="192" spans="2:6">
-      <c r="B192" s="33"/>
-      <c r="C192" s="33"/>
-      <c r="D192" s="33"/>
-      <c r="E192" s="33"/>
-      <c r="F192" s="33"/>
-    </row>
-    <row r="193" spans="2:6">
-      <c r="B193" s="33"/>
-      <c r="C193" s="33"/>
-      <c r="D193" s="33"/>
-      <c r="E193" s="33"/>
-      <c r="F193" s="33"/>
-    </row>
-    <row r="194" spans="2:6">
-      <c r="B194" s="33"/>
-      <c r="C194" s="33"/>
-      <c r="D194" s="33"/>
-      <c r="E194" s="33"/>
-      <c r="F194" s="33"/>
-    </row>
-    <row r="195" spans="2:6">
-      <c r="B195" s="33"/>
-      <c r="C195" s="33"/>
-      <c r="D195" s="33"/>
-      <c r="E195" s="33"/>
-      <c r="F195" s="33"/>
-    </row>
-    <row r="196" spans="2:6">
-      <c r="B196" s="33"/>
-      <c r="C196" s="33"/>
-      <c r="D196" s="33"/>
-      <c r="E196" s="33"/>
-      <c r="F196" s="33"/>
-    </row>
-    <row r="197" spans="2:6">
-      <c r="B197" s="33"/>
-      <c r="C197" s="33"/>
-      <c r="D197" s="33"/>
-      <c r="E197" s="33"/>
-      <c r="F197" s="33"/>
-    </row>
-    <row r="198" spans="2:6">
-      <c r="B198" s="33"/>
-      <c r="C198" s="33"/>
-      <c r="D198" s="33"/>
-      <c r="E198" s="33"/>
-      <c r="F198" s="33"/>
-    </row>
-    <row r="199" spans="2:6">
-      <c r="B199" s="33"/>
-      <c r="C199" s="33"/>
-      <c r="D199" s="33"/>
-      <c r="E199" s="33"/>
-      <c r="F199" s="33"/>
-    </row>
-    <row r="200" spans="2:6">
-      <c r="B200" s="33"/>
-      <c r="C200" s="33"/>
-      <c r="D200" s="33"/>
-      <c r="E200" s="33"/>
-      <c r="F200" s="33"/>
-    </row>
-    <row r="201" spans="2:6">
-      <c r="B201" s="33"/>
-      <c r="C201" s="33"/>
-      <c r="D201" s="33"/>
-      <c r="E201" s="33"/>
-      <c r="F201" s="33"/>
-    </row>
-    <row r="202" spans="2:6">
-      <c r="B202" s="33"/>
-      <c r="C202" s="33"/>
-      <c r="D202" s="33"/>
-      <c r="E202" s="33"/>
-      <c r="F202" s="33"/>
-    </row>
-    <row r="203" spans="2:6">
-      <c r="B203" s="33"/>
-      <c r="C203" s="33"/>
-      <c r="D203" s="33"/>
-      <c r="E203" s="33"/>
-      <c r="F203" s="33"/>
-    </row>
-    <row r="204" spans="2:6">
-      <c r="B204" s="33"/>
-      <c r="C204" s="33"/>
-      <c r="D204" s="33"/>
-      <c r="E204" s="33"/>
-      <c r="F204" s="33"/>
-    </row>
-    <row r="205" spans="2:6">
-      <c r="B205" s="33"/>
-      <c r="C205" s="33"/>
-      <c r="D205" s="33"/>
-      <c r="E205" s="33"/>
-      <c r="F205" s="33"/>
-    </row>
-    <row r="206" spans="2:6">
-      <c r="B206" s="33"/>
-      <c r="C206" s="33"/>
-      <c r="D206" s="33"/>
-      <c r="E206" s="33"/>
-      <c r="F206" s="33"/>
-    </row>
-    <row r="207" spans="2:6">
-      <c r="B207" s="33"/>
-      <c r="C207" s="33"/>
-      <c r="D207" s="33"/>
-      <c r="E207" s="33"/>
-      <c r="F207" s="33"/>
-    </row>
-    <row r="208" spans="2:6">
-      <c r="B208" s="33"/>
-      <c r="C208" s="33"/>
-      <c r="D208" s="33"/>
-      <c r="E208" s="33"/>
-      <c r="F208" s="33"/>
-    </row>
-    <row r="209" spans="2:6">
-      <c r="B209" s="33"/>
-      <c r="C209" s="33"/>
-      <c r="D209" s="33"/>
-      <c r="E209" s="33"/>
-      <c r="F209" s="33"/>
-    </row>
-    <row r="210" spans="2:6">
-      <c r="B210" s="33"/>
-      <c r="C210" s="33"/>
-      <c r="D210" s="33"/>
-      <c r="E210" s="33"/>
-      <c r="F210" s="33"/>
-    </row>
-    <row r="211" spans="2:6">
-      <c r="B211" s="33"/>
-      <c r="C211" s="33"/>
-      <c r="D211" s="33"/>
-      <c r="E211" s="33"/>
-      <c r="F211" s="33"/>
-    </row>
-    <row r="212" spans="2:6">
-      <c r="B212" s="33"/>
-      <c r="C212" s="33"/>
-      <c r="D212" s="33"/>
-      <c r="E212" s="33"/>
-      <c r="F212" s="33"/>
-    </row>
-    <row r="213" spans="2:6">
-      <c r="B213" s="33"/>
-      <c r="C213" s="33"/>
-      <c r="D213" s="33"/>
-      <c r="E213" s="33"/>
-      <c r="F213" s="33"/>
-    </row>
-    <row r="214" spans="2:6">
-      <c r="B214" s="33"/>
-      <c r="C214" s="33"/>
-      <c r="D214" s="33"/>
-      <c r="E214" s="33"/>
-      <c r="F214" s="33"/>
-    </row>
-    <row r="215" spans="2:6">
-      <c r="B215" s="33"/>
-      <c r="C215" s="33"/>
-      <c r="D215" s="33"/>
-      <c r="E215" s="33"/>
-      <c r="F215" s="33"/>
-    </row>
-    <row r="216" spans="2:6">
-      <c r="B216" s="33"/>
-      <c r="C216" s="33"/>
-      <c r="D216" s="33"/>
-      <c r="E216" s="33"/>
-      <c r="F216" s="33"/>
-    </row>
-    <row r="217" spans="2:6">
-      <c r="B217" s="33"/>
-      <c r="C217" s="33"/>
-      <c r="D217" s="33"/>
-      <c r="E217" s="33"/>
-      <c r="F217" s="33"/>
-    </row>
-    <row r="218" spans="2:6">
-      <c r="B218" s="33"/>
-      <c r="C218" s="33"/>
-      <c r="D218" s="33"/>
-      <c r="E218" s="33"/>
-      <c r="F218" s="33"/>
-    </row>
-    <row r="219" spans="2:6">
-      <c r="B219" s="33"/>
-      <c r="C219" s="33"/>
-      <c r="D219" s="33"/>
-      <c r="E219" s="33"/>
-      <c r="F219" s="33"/>
-    </row>
-    <row r="220" spans="2:6">
-      <c r="B220" s="33"/>
-      <c r="C220" s="33"/>
-      <c r="D220" s="33"/>
-      <c r="E220" s="33"/>
-      <c r="F220" s="33"/>
-    </row>
-    <row r="221" spans="2:6">
-      <c r="B221" s="33"/>
-      <c r="C221" s="33"/>
-      <c r="D221" s="33"/>
-      <c r="E221" s="33"/>
-      <c r="F221" s="33"/>
-    </row>
-    <row r="222" spans="2:6">
-      <c r="B222" s="33"/>
-      <c r="C222" s="33"/>
-      <c r="D222" s="33"/>
-      <c r="E222" s="33"/>
-      <c r="F222" s="33"/>
-    </row>
-    <row r="223" spans="2:6">
-      <c r="B223" s="33"/>
-      <c r="C223" s="33"/>
-      <c r="D223" s="33"/>
-      <c r="E223" s="33"/>
-      <c r="F223" s="33"/>
-    </row>
-    <row r="224" spans="2:6">
-      <c r="B224" s="33"/>
-      <c r="C224" s="33"/>
-      <c r="D224" s="33"/>
-      <c r="E224" s="33"/>
-      <c r="F224" s="33"/>
-    </row>
-    <row r="225" spans="2:6">
-      <c r="B225" s="33"/>
-      <c r="C225" s="33"/>
-      <c r="D225" s="33"/>
-      <c r="E225" s="33"/>
-      <c r="F225" s="33"/>
-    </row>
-    <row r="226" spans="2:6">
-      <c r="B226" s="33"/>
-      <c r="C226" s="33"/>
-      <c r="D226" s="33"/>
-      <c r="E226" s="33"/>
-      <c r="F226" s="33"/>
-    </row>
-    <row r="227" spans="2:6">
-      <c r="B227" s="33"/>
-      <c r="C227" s="33"/>
-      <c r="D227" s="33"/>
-      <c r="E227" s="33"/>
-      <c r="F227" s="33"/>
-    </row>
-    <row r="228" spans="2:6">
-      <c r="B228" s="33"/>
-      <c r="C228" s="33"/>
-      <c r="D228" s="33"/>
-      <c r="E228" s="33"/>
-      <c r="F228" s="33"/>
-    </row>
-    <row r="229" spans="2:6">
-      <c r="B229" s="33"/>
-      <c r="C229" s="33"/>
-      <c r="D229" s="33"/>
-      <c r="E229" s="33"/>
-      <c r="F229" s="33"/>
-    </row>
-    <row r="230" spans="2:6">
-      <c r="B230" s="33"/>
-      <c r="C230" s="33"/>
-      <c r="D230" s="33"/>
-      <c r="E230" s="33"/>
-      <c r="F230" s="33"/>
-    </row>
-    <row r="231" spans="2:6">
-      <c r="B231" s="33"/>
-      <c r="C231" s="33"/>
-      <c r="D231" s="33"/>
-      <c r="E231" s="33"/>
-      <c r="F231" s="33"/>
-    </row>
-    <row r="232" spans="2:6">
-      <c r="B232" s="33"/>
-      <c r="C232" s="33"/>
-      <c r="D232" s="33"/>
-      <c r="E232" s="33"/>
-      <c r="F232" s="33"/>
-    </row>
-    <row r="233" spans="2:6">
-      <c r="B233" s="33"/>
-      <c r="C233" s="33"/>
-      <c r="D233" s="33"/>
-      <c r="E233" s="33"/>
-      <c r="F233" s="33"/>
-    </row>
-    <row r="234" spans="2:6">
-      <c r="B234" s="33"/>
-      <c r="C234" s="33"/>
-      <c r="D234" s="33"/>
-      <c r="E234" s="33"/>
-      <c r="F234" s="33"/>
-    </row>
-    <row r="235" spans="2:6">
-      <c r="B235" s="33"/>
-      <c r="C235" s="33"/>
-      <c r="D235" s="33"/>
-      <c r="E235" s="33"/>
-      <c r="F235" s="33"/>
-    </row>
-    <row r="236" spans="2:6">
-      <c r="B236" s="33"/>
-      <c r="C236" s="33"/>
-      <c r="D236" s="33"/>
-      <c r="E236" s="33"/>
-      <c r="F236" s="33"/>
-    </row>
-    <row r="237" spans="2:6">
-      <c r="B237" s="33"/>
-      <c r="C237" s="33"/>
-      <c r="D237" s="33"/>
-      <c r="E237" s="33"/>
-      <c r="F237" s="33"/>
-    </row>
-    <row r="238" spans="2:6">
-      <c r="B238" s="33"/>
-      <c r="C238" s="33"/>
-      <c r="D238" s="33"/>
-      <c r="E238" s="33"/>
-      <c r="F238" s="33"/>
-    </row>
-    <row r="239" spans="2:6">
-      <c r="B239" s="33"/>
-      <c r="C239" s="33"/>
-      <c r="D239" s="33"/>
-      <c r="E239" s="33"/>
-      <c r="F239" s="33"/>
-    </row>
-    <row r="240" spans="2:6">
-      <c r="B240" s="33"/>
-      <c r="C240" s="33"/>
-      <c r="D240" s="33"/>
-      <c r="E240" s="33"/>
-      <c r="F240" s="33"/>
-    </row>
-    <row r="241" spans="2:6">
-      <c r="B241" s="33"/>
-      <c r="C241" s="33"/>
-      <c r="D241" s="33"/>
-      <c r="E241" s="33"/>
-      <c r="F241" s="33"/>
-    </row>
-    <row r="242" spans="2:6">
-      <c r="B242" s="33"/>
-      <c r="C242" s="33"/>
-      <c r="D242" s="33"/>
-      <c r="E242" s="33"/>
-      <c r="F242" s="33"/>
-    </row>
-    <row r="243" spans="2:6">
-      <c r="B243" s="33"/>
-      <c r="C243" s="33"/>
-      <c r="D243" s="33"/>
-      <c r="E243" s="33"/>
-      <c r="F243" s="33"/>
-    </row>
-    <row r="244" spans="2:6">
-      <c r="B244" s="33"/>
-      <c r="C244" s="33"/>
-      <c r="D244" s="33"/>
-      <c r="E244" s="33"/>
-      <c r="F244" s="33"/>
-    </row>
-    <row r="245" spans="2:6">
-      <c r="B245" s="33"/>
-      <c r="C245" s="33"/>
-      <c r="D245" s="33"/>
-      <c r="E245" s="33"/>
-      <c r="F245" s="33"/>
-    </row>
-    <row r="246" spans="2:6">
-      <c r="B246" s="33"/>
-      <c r="C246" s="33"/>
-      <c r="D246" s="33"/>
-      <c r="E246" s="33"/>
-      <c r="F246" s="33"/>
-    </row>
-    <row r="247" spans="2:6">
-      <c r="B247" s="33"/>
-      <c r="C247" s="33"/>
-      <c r="D247" s="33"/>
-      <c r="E247" s="33"/>
-      <c r="F247" s="33"/>
-    </row>
-    <row r="248" spans="2:6">
-      <c r="B248" s="33"/>
-      <c r="C248" s="33"/>
-      <c r="D248" s="33"/>
-      <c r="E248" s="33"/>
-      <c r="F248" s="33"/>
-    </row>
-    <row r="249" spans="2:6">
-      <c r="B249" s="33"/>
-      <c r="C249" s="33"/>
-      <c r="D249" s="33"/>
-      <c r="E249" s="33"/>
-      <c r="F249" s="33"/>
-    </row>
-    <row r="250" spans="2:6">
-      <c r="B250" s="33"/>
-      <c r="C250" s="33"/>
-      <c r="D250" s="33"/>
-      <c r="E250" s="33"/>
-      <c r="F250" s="33"/>
-    </row>
-    <row r="251" spans="2:6">
-      <c r="B251" s="33"/>
-      <c r="C251" s="33"/>
-      <c r="D251" s="33"/>
-      <c r="E251" s="33"/>
-      <c r="F251" s="33"/>
-    </row>
-    <row r="252" spans="2:6">
-      <c r="B252" s="33"/>
-      <c r="C252" s="33"/>
-      <c r="D252" s="33"/>
-      <c r="E252" s="33"/>
-      <c r="F252" s="33"/>
-    </row>
-    <row r="253" spans="2:6">
-      <c r="B253" s="33"/>
-      <c r="C253" s="33"/>
-      <c r="D253" s="33"/>
-      <c r="E253" s="33"/>
-      <c r="F253" s="33"/>
-    </row>
-    <row r="254" spans="2:6">
-      <c r="B254" s="33"/>
-      <c r="C254" s="33"/>
-      <c r="D254" s="33"/>
-      <c r="E254" s="33"/>
-      <c r="F254" s="33"/>
-    </row>
-    <row r="255" spans="2:6">
-      <c r="B255" s="33"/>
-      <c r="C255" s="33"/>
-      <c r="D255" s="33"/>
-      <c r="E255" s="33"/>
-      <c r="F255" s="33"/>
-    </row>
-    <row r="256" spans="2:6">
-      <c r="B256" s="33"/>
-      <c r="C256" s="33"/>
-      <c r="D256" s="33"/>
-      <c r="E256" s="33"/>
-      <c r="F256" s="33"/>
-    </row>
-    <row r="257" spans="2:6">
-      <c r="B257" s="33"/>
-      <c r="C257" s="33"/>
-      <c r="D257" s="33"/>
-      <c r="E257" s="33"/>
-      <c r="F257" s="33"/>
-    </row>
-    <row r="258" spans="2:6">
-      <c r="B258" s="33"/>
-      <c r="C258" s="33"/>
-      <c r="D258" s="33"/>
-      <c r="E258" s="33"/>
-      <c r="F258" s="33"/>
-    </row>
-    <row r="259" spans="2:6">
-      <c r="B259" s="33"/>
-      <c r="C259" s="33"/>
-      <c r="D259" s="33"/>
-      <c r="E259" s="33"/>
-      <c r="F259" s="33"/>
-    </row>
-    <row r="260" spans="2:6">
-      <c r="B260" s="33"/>
-      <c r="C260" s="33"/>
-      <c r="D260" s="33"/>
-      <c r="E260" s="33"/>
-      <c r="F260" s="33"/>
-    </row>
-    <row r="261" spans="2:6">
-      <c r="B261" s="33"/>
-      <c r="C261" s="33"/>
-      <c r="D261" s="33"/>
-      <c r="E261" s="33"/>
-      <c r="F261" s="33"/>
-    </row>
-    <row r="262" spans="2:6">
-      <c r="B262" s="33"/>
-      <c r="C262" s="33"/>
-      <c r="D262" s="33"/>
-      <c r="E262" s="33"/>
-      <c r="F262" s="33"/>
-    </row>
-    <row r="263" spans="2:6">
-      <c r="B263" s="33"/>
-      <c r="C263" s="33"/>
-      <c r="D263" s="33"/>
-      <c r="E263" s="33"/>
-      <c r="F263" s="33"/>
-    </row>
-    <row r="264" spans="2:6">
-      <c r="B264" s="33"/>
-      <c r="C264" s="33"/>
-      <c r="D264" s="33"/>
-      <c r="E264" s="33"/>
-      <c r="F264" s="33"/>
-    </row>
-    <row r="265" spans="2:6">
-      <c r="B265" s="33"/>
-      <c r="C265" s="33"/>
-      <c r="D265" s="33"/>
-      <c r="E265" s="33"/>
-      <c r="F265" s="33"/>
-    </row>
-    <row r="266" spans="2:6">
-      <c r="B266" s="33"/>
-      <c r="C266" s="33"/>
-      <c r="D266" s="33"/>
-      <c r="E266" s="33"/>
-      <c r="F266" s="33"/>
-    </row>
-    <row r="267" spans="2:6">
-      <c r="B267" s="33"/>
-      <c r="C267" s="33"/>
-      <c r="D267" s="33"/>
-      <c r="E267" s="33"/>
-      <c r="F267" s="33"/>
-    </row>
-    <row r="268" spans="2:6">
-      <c r="B268" s="33"/>
-      <c r="C268" s="33"/>
-      <c r="D268" s="33"/>
-      <c r="E268" s="33"/>
-      <c r="F268" s="33"/>
-    </row>
-    <row r="269" spans="2:6">
-      <c r="B269" s="33"/>
-      <c r="C269" s="33"/>
-      <c r="D269" s="33"/>
-      <c r="E269" s="33"/>
-      <c r="F269" s="33"/>
-    </row>
-    <row r="270" spans="2:6">
-      <c r="B270" s="33"/>
-      <c r="C270" s="33"/>
-      <c r="D270" s="33"/>
-      <c r="E270" s="33"/>
-      <c r="F270" s="33"/>
-    </row>
-    <row r="271" spans="2:6">
-      <c r="B271" s="33"/>
-      <c r="C271" s="33"/>
-      <c r="D271" s="33"/>
-      <c r="E271" s="33"/>
-      <c r="F271" s="33"/>
-    </row>
-    <row r="272" spans="2:6">
-      <c r="B272" s="33"/>
-      <c r="C272" s="33"/>
-      <c r="D272" s="33"/>
-      <c r="E272" s="33"/>
-      <c r="F272" s="33"/>
-    </row>
-    <row r="273" spans="2:6">
-      <c r="B273" s="33"/>
-      <c r="C273" s="33"/>
-      <c r="D273" s="33"/>
-      <c r="E273" s="33"/>
-      <c r="F273" s="33"/>
-    </row>
-    <row r="274" spans="2:6">
-      <c r="B274" s="33"/>
-      <c r="C274" s="33"/>
-      <c r="D274" s="33"/>
-      <c r="E274" s="33"/>
-      <c r="F274" s="33"/>
-    </row>
-    <row r="275" spans="2:6">
-      <c r="B275" s="33"/>
-      <c r="C275" s="33"/>
-      <c r="D275" s="33"/>
-      <c r="E275" s="33"/>
-      <c r="F275" s="33"/>
-    </row>
-    <row r="276" spans="2:6">
-      <c r="B276" s="33"/>
-      <c r="C276" s="33"/>
-      <c r="D276" s="33"/>
-      <c r="E276" s="33"/>
-      <c r="F276" s="33"/>
-    </row>
-    <row r="277" spans="2:6">
-      <c r="B277" s="33"/>
-      <c r="C277" s="33"/>
-      <c r="D277" s="33"/>
-      <c r="E277" s="33"/>
-      <c r="F277" s="33"/>
-    </row>
-    <row r="278" spans="2:6">
-      <c r="B278" s="33"/>
-      <c r="C278" s="33"/>
-      <c r="D278" s="33"/>
-      <c r="E278" s="33"/>
-      <c r="F278" s="33"/>
-    </row>
-    <row r="279" spans="2:6">
-      <c r="B279" s="33"/>
-      <c r="C279" s="33"/>
-      <c r="D279" s="33"/>
-      <c r="E279" s="33"/>
-      <c r="F279" s="33"/>
-    </row>
-    <row r="280" spans="2:6">
-      <c r="B280" s="33"/>
-      <c r="C280" s="33"/>
-      <c r="D280" s="33"/>
-      <c r="E280" s="33"/>
-      <c r="F280" s="33"/>
-    </row>
-    <row r="281" spans="2:6">
-      <c r="B281" s="33"/>
-      <c r="C281" s="33"/>
-      <c r="D281" s="33"/>
-      <c r="E281" s="33"/>
-      <c r="F281" s="33"/>
-    </row>
-    <row r="282" spans="2:6">
-      <c r="B282" s="33"/>
-      <c r="C282" s="33"/>
-      <c r="D282" s="33"/>
-      <c r="E282" s="33"/>
-      <c r="F282" s="33"/>
-    </row>
-    <row r="283" spans="2:6">
-      <c r="B283" s="33"/>
-      <c r="C283" s="33"/>
-      <c r="D283" s="33"/>
-      <c r="E283" s="33"/>
-      <c r="F283" s="33"/>
-    </row>
-    <row r="284" spans="2:6">
-      <c r="B284" s="33"/>
-      <c r="C284" s="33"/>
-      <c r="D284" s="33"/>
-      <c r="E284" s="33"/>
-      <c r="F284" s="33"/>
-    </row>
-    <row r="285" spans="2:6">
-      <c r="B285" s="33"/>
-      <c r="C285" s="33"/>
-      <c r="D285" s="33"/>
-      <c r="E285" s="33"/>
-      <c r="F285" s="33"/>
-    </row>
-    <row r="286" spans="2:6">
-      <c r="B286" s="33"/>
-      <c r="C286" s="33"/>
-      <c r="D286" s="33"/>
-      <c r="E286" s="33"/>
-      <c r="F286" s="33"/>
-    </row>
-    <row r="287" spans="2:6">
-      <c r="B287" s="33"/>
-      <c r="C287" s="33"/>
-      <c r="D287" s="33"/>
-      <c r="E287" s="33"/>
-      <c r="F287" s="33"/>
-    </row>
-    <row r="288" spans="2:6">
-      <c r="B288" s="33"/>
-      <c r="C288" s="33"/>
-      <c r="D288" s="33"/>
-      <c r="E288" s="33"/>
-      <c r="F288" s="33"/>
-    </row>
-    <row r="289" spans="2:6">
-      <c r="B289" s="33"/>
-      <c r="C289" s="33"/>
-      <c r="D289" s="33"/>
-      <c r="E289" s="33"/>
-      <c r="F289" s="33"/>
-    </row>
-    <row r="290" spans="2:6">
-      <c r="B290" s="33"/>
-      <c r="C290" s="33"/>
-      <c r="D290" s="33"/>
-      <c r="E290" s="33"/>
-      <c r="F290" s="33"/>
-    </row>
-    <row r="291" spans="2:6">
-      <c r="B291" s="33"/>
-      <c r="C291" s="33"/>
-      <c r="D291" s="33"/>
-      <c r="E291" s="33"/>
-      <c r="F291" s="33"/>
-    </row>
-    <row r="292" spans="2:6">
-      <c r="B292" s="33"/>
-      <c r="C292" s="33"/>
-      <c r="D292" s="33"/>
-      <c r="E292" s="33"/>
-      <c r="F292" s="33"/>
-    </row>
-    <row r="293" spans="2:6">
-      <c r="B293" s="33"/>
-      <c r="C293" s="33"/>
-      <c r="D293" s="33"/>
-      <c r="E293" s="33"/>
-      <c r="F293" s="33"/>
-    </row>
-    <row r="294" spans="2:6">
-      <c r="B294" s="33"/>
-      <c r="C294" s="33"/>
-      <c r="D294" s="33"/>
-      <c r="E294" s="33"/>
-      <c r="F294" s="33"/>
-    </row>
-    <row r="295" spans="2:6">
-      <c r="B295" s="33"/>
-      <c r="C295" s="33"/>
-      <c r="D295" s="33"/>
-      <c r="E295" s="33"/>
-      <c r="F295" s="33"/>
-    </row>
-    <row r="296" spans="2:6">
-      <c r="B296" s="33"/>
-      <c r="C296" s="33"/>
-      <c r="D296" s="33"/>
-      <c r="E296" s="33"/>
-      <c r="F296" s="33"/>
-    </row>
-    <row r="297" spans="2:6">
-      <c r="B297" s="33"/>
-      <c r="C297" s="33"/>
-      <c r="D297" s="33"/>
-      <c r="E297" s="33"/>
-      <c r="F297" s="33"/>
-    </row>
-    <row r="298" spans="2:6">
-      <c r="B298" s="33"/>
-      <c r="C298" s="33"/>
-      <c r="D298" s="33"/>
-      <c r="E298" s="33"/>
-      <c r="F298" s="33"/>
-    </row>
-    <row r="299" spans="2:6">
-      <c r="B299" s="33"/>
-      <c r="C299" s="33"/>
-      <c r="D299" s="33"/>
-      <c r="E299" s="33"/>
-      <c r="F299" s="33"/>
-    </row>
-    <row r="300" spans="2:6">
-      <c r="B300" s="33"/>
-      <c r="C300" s="33"/>
-      <c r="D300" s="33"/>
-      <c r="E300" s="33"/>
-      <c r="F300" s="33"/>
-    </row>
-    <row r="301" spans="2:6">
-      <c r="B301" s="33"/>
-      <c r="C301" s="33"/>
-      <c r="D301" s="33"/>
-      <c r="E301" s="33"/>
-      <c r="F301" s="33"/>
-    </row>
-    <row r="302" spans="2:6">
-      <c r="B302" s="33"/>
-      <c r="C302" s="33"/>
-      <c r="D302" s="33"/>
-      <c r="E302" s="33"/>
-      <c r="F302" s="33"/>
-    </row>
-    <row r="303" spans="2:6">
-      <c r="B303" s="33"/>
-      <c r="C303" s="33"/>
-      <c r="D303" s="33"/>
-      <c r="E303" s="33"/>
-      <c r="F303" s="33"/>
-    </row>
-    <row r="304" spans="2:6">
-      <c r="B304" s="33"/>
-      <c r="C304" s="33"/>
-      <c r="D304" s="33"/>
-      <c r="E304" s="33"/>
-      <c r="F304" s="33"/>
-    </row>
-    <row r="305" spans="2:6">
-      <c r="B305" s="33"/>
-      <c r="C305" s="33"/>
-      <c r="D305" s="33"/>
-      <c r="E305" s="33"/>
-      <c r="F305" s="33"/>
-    </row>
-    <row r="306" spans="2:6">
-      <c r="B306" s="33"/>
-      <c r="C306" s="33"/>
-      <c r="D306" s="33"/>
-      <c r="E306" s="33"/>
-      <c r="F306" s="33"/>
-    </row>
-    <row r="307" spans="2:6">
-      <c r="B307" s="33"/>
-      <c r="C307" s="33"/>
-      <c r="D307" s="33"/>
-      <c r="E307" s="33"/>
-      <c r="F307" s="33"/>
-    </row>
-    <row r="308" spans="2:6">
-      <c r="B308" s="33"/>
-      <c r="C308" s="33"/>
-      <c r="D308" s="33"/>
-      <c r="E308" s="33"/>
-      <c r="F308" s="33"/>
-    </row>
-    <row r="309" spans="2:6">
-      <c r="B309" s="33"/>
-      <c r="C309" s="33"/>
-      <c r="D309" s="33"/>
-      <c r="E309" s="33"/>
-      <c r="F309" s="33"/>
-    </row>
-    <row r="310" spans="2:6">
-      <c r="B310" s="33"/>
-      <c r="C310" s="33"/>
-      <c r="D310" s="33"/>
-      <c r="E310" s="33"/>
-      <c r="F310" s="33"/>
-    </row>
-    <row r="311" spans="2:6">
-      <c r="B311" s="33"/>
-      <c r="C311" s="33"/>
-      <c r="D311" s="33"/>
-      <c r="E311" s="33"/>
-      <c r="F311" s="33"/>
-    </row>
-    <row r="312" spans="2:6">
-      <c r="B312" s="33"/>
-      <c r="C312" s="33"/>
-      <c r="D312" s="33"/>
-      <c r="E312" s="33"/>
-      <c r="F312" s="33"/>
-    </row>
-    <row r="313" spans="2:6">
-      <c r="B313" s="33"/>
-      <c r="C313" s="33"/>
-      <c r="D313" s="33"/>
-      <c r="E313" s="33"/>
-      <c r="F313" s="33"/>
-    </row>
-    <row r="314" spans="2:6">
-      <c r="B314" s="33"/>
-      <c r="C314" s="33"/>
-      <c r="D314" s="33"/>
-      <c r="E314" s="33"/>
-      <c r="F314" s="33"/>
-    </row>
-    <row r="315" spans="2:6">
-      <c r="B315" s="33"/>
-      <c r="C315" s="33"/>
-      <c r="D315" s="33"/>
-      <c r="E315" s="33"/>
-      <c r="F315" s="33"/>
-    </row>
-    <row r="316" spans="2:6">
-      <c r="B316" s="33"/>
-      <c r="C316" s="33"/>
-      <c r="D316" s="33"/>
-      <c r="E316" s="33"/>
-      <c r="F316" s="33"/>
-    </row>
-    <row r="317" spans="2:6">
-      <c r="B317" s="33"/>
-      <c r="C317" s="33"/>
-      <c r="D317" s="33"/>
-      <c r="E317" s="33"/>
-      <c r="F317" s="33"/>
-    </row>
-    <row r="318" spans="2:6">
-      <c r="B318" s="33"/>
-      <c r="C318" s="33"/>
-      <c r="D318" s="33"/>
-      <c r="E318" s="33"/>
-      <c r="F318" s="33"/>
-    </row>
-    <row r="319" spans="2:6">
-      <c r="B319" s="33"/>
-      <c r="C319" s="33"/>
-      <c r="D319" s="33"/>
-      <c r="E319" s="33"/>
-      <c r="F319" s="33"/>
-    </row>
-    <row r="320" spans="2:6">
-      <c r="B320" s="33"/>
-      <c r="C320" s="33"/>
-      <c r="D320" s="33"/>
-      <c r="E320" s="33"/>
-      <c r="F320" s="33"/>
-    </row>
-    <row r="321" spans="2:6">
-      <c r="B321" s="33"/>
-      <c r="C321" s="33"/>
-      <c r="D321" s="33"/>
-      <c r="E321" s="33"/>
-      <c r="F321" s="33"/>
-    </row>
-    <row r="322" spans="2:6">
-      <c r="B322" s="33"/>
-      <c r="C322" s="33"/>
-      <c r="D322" s="33"/>
-      <c r="E322" s="33"/>
-      <c r="F322" s="33"/>
-    </row>
-    <row r="323" spans="2:6">
-      <c r="B323" s="33"/>
-      <c r="C323" s="33"/>
-      <c r="D323" s="33"/>
-      <c r="E323" s="33"/>
-      <c r="F323" s="33"/>
-    </row>
-    <row r="324" spans="2:6">
-      <c r="B324" s="33"/>
-      <c r="C324" s="33"/>
-      <c r="D324" s="33"/>
-      <c r="E324" s="33"/>
-      <c r="F324" s="33"/>
-    </row>
-    <row r="325" spans="2:6">
-      <c r="B325" s="33"/>
-      <c r="C325" s="33"/>
-      <c r="D325" s="33"/>
-      <c r="E325" s="33"/>
-      <c r="F325" s="33"/>
-    </row>
-    <row r="326" spans="2:6">
-      <c r="B326" s="33"/>
-      <c r="C326" s="33"/>
-      <c r="D326" s="33"/>
-      <c r="E326" s="33"/>
-      <c r="F326" s="33"/>
-    </row>
-    <row r="327" spans="2:6">
-      <c r="B327" s="33"/>
-      <c r="C327" s="33"/>
-      <c r="D327" s="33"/>
-      <c r="E327" s="33"/>
-      <c r="F327" s="33"/>
-    </row>
-    <row r="328" spans="2:6">
-      <c r="B328" s="33"/>
-      <c r="C328" s="33"/>
-      <c r="D328" s="33"/>
-      <c r="E328" s="33"/>
-      <c r="F328" s="33"/>
-    </row>
-    <row r="329" spans="2:6">
-      <c r="B329" s="33"/>
-      <c r="C329" s="33"/>
-      <c r="D329" s="33"/>
-      <c r="E329" s="33"/>
-      <c r="F329" s="33"/>
-    </row>
-    <row r="330" spans="2:6">
-      <c r="B330" s="33"/>
-      <c r="C330" s="33"/>
-      <c r="D330" s="33"/>
-      <c r="E330" s="33"/>
-      <c r="F330" s="33"/>
-    </row>
-    <row r="331" spans="2:6">
-      <c r="B331" s="33"/>
-      <c r="C331" s="33"/>
-      <c r="D331" s="33"/>
-      <c r="E331" s="33"/>
-      <c r="F331" s="33"/>
-    </row>
-    <row r="332" spans="2:6">
-      <c r="B332" s="33"/>
-      <c r="C332" s="33"/>
-      <c r="D332" s="33"/>
-      <c r="E332" s="33"/>
-      <c r="F332" s="33"/>
-    </row>
-    <row r="333" spans="2:6">
-      <c r="B333" s="33"/>
-      <c r="C333" s="33"/>
-      <c r="D333" s="33"/>
-      <c r="E333" s="33"/>
-      <c r="F333" s="33"/>
-    </row>
-    <row r="334" spans="2:6">
-      <c r="B334" s="33"/>
-      <c r="C334" s="33"/>
-      <c r="D334" s="33"/>
-      <c r="E334" s="33"/>
-      <c r="F334" s="33"/>
-    </row>
-    <row r="335" spans="2:6">
-      <c r="B335" s="33"/>
-      <c r="C335" s="33"/>
-      <c r="D335" s="33"/>
-      <c r="E335" s="33"/>
-      <c r="F335" s="33"/>
-    </row>
-    <row r="336" spans="2:6">
-      <c r="B336" s="33"/>
-      <c r="C336" s="33"/>
-      <c r="D336" s="33"/>
-      <c r="E336" s="33"/>
-      <c r="F336" s="33"/>
-    </row>
-    <row r="337" spans="2:6">
-      <c r="B337" s="33"/>
-      <c r="C337" s="33"/>
-      <c r="D337" s="33"/>
-      <c r="E337" s="33"/>
-      <c r="F337" s="33"/>
-    </row>
-    <row r="338" spans="2:6">
-      <c r="B338" s="33"/>
-      <c r="C338" s="33"/>
-      <c r="D338" s="33"/>
-      <c r="E338" s="33"/>
-      <c r="F338" s="33"/>
-    </row>
-    <row r="339" spans="2:6">
-      <c r="B339" s="33"/>
-      <c r="C339" s="33"/>
-      <c r="D339" s="33"/>
-      <c r="E339" s="33"/>
-      <c r="F339" s="33"/>
-    </row>
-    <row r="340" spans="2:6">
-      <c r="B340" s="33"/>
-      <c r="C340" s="33"/>
-      <c r="D340" s="33"/>
-      <c r="E340" s="33"/>
-      <c r="F340" s="33"/>
-    </row>
-    <row r="341" spans="2:6">
-      <c r="B341" s="33"/>
-      <c r="C341" s="33"/>
-      <c r="D341" s="33"/>
-      <c r="E341" s="33"/>
-      <c r="F341" s="33"/>
-    </row>
-    <row r="342" spans="2:6">
-      <c r="B342" s="33"/>
-      <c r="C342" s="33"/>
-      <c r="D342" s="33"/>
-      <c r="E342" s="33"/>
-      <c r="F342" s="33"/>
-    </row>
-    <row r="343" spans="2:6">
-      <c r="B343" s="33"/>
-      <c r="C343" s="33"/>
-      <c r="D343" s="33"/>
-      <c r="E343" s="33"/>
-      <c r="F343" s="33"/>
-    </row>
-    <row r="344" spans="2:6">
-      <c r="B344" s="33"/>
-      <c r="C344" s="33"/>
-      <c r="D344" s="33"/>
-      <c r="E344" s="33"/>
-      <c r="F344" s="33"/>
-    </row>
-    <row r="345" spans="2:6">
-      <c r="B345" s="33"/>
-      <c r="C345" s="33"/>
-      <c r="D345" s="33"/>
-      <c r="E345" s="33"/>
-      <c r="F345" s="33"/>
-    </row>
-    <row r="346" spans="2:6">
-      <c r="B346" s="33"/>
-      <c r="C346" s="33"/>
-      <c r="D346" s="33"/>
-      <c r="E346" s="33"/>
-      <c r="F346" s="33"/>
-    </row>
-    <row r="347" spans="2:6">
-      <c r="B347" s="33"/>
-      <c r="C347" s="33"/>
-      <c r="D347" s="33"/>
-      <c r="E347" s="33"/>
-      <c r="F347" s="33"/>
-    </row>
-    <row r="348" spans="2:6">
-      <c r="B348" s="33"/>
-      <c r="C348" s="33"/>
-      <c r="D348" s="33"/>
-      <c r="E348" s="33"/>
-      <c r="F348" s="33"/>
-    </row>
-    <row r="349" spans="2:6">
-      <c r="B349" s="33"/>
-      <c r="C349" s="33"/>
-      <c r="D349" s="33"/>
-      <c r="E349" s="33"/>
-      <c r="F349" s="33"/>
-    </row>
-    <row r="350" spans="2:6">
-      <c r="B350" s="33"/>
-      <c r="C350" s="33"/>
-      <c r="D350" s="33"/>
-      <c r="E350" s="33"/>
-      <c r="F350" s="33"/>
-    </row>
-    <row r="351" spans="2:6">
-      <c r="B351" s="33"/>
-      <c r="C351" s="33"/>
-      <c r="D351" s="33"/>
-      <c r="E351" s="33"/>
-      <c r="F351" s="33"/>
-    </row>
-    <row r="352" spans="2:6">
-      <c r="B352" s="33"/>
-      <c r="C352" s="33"/>
-      <c r="D352" s="33"/>
-      <c r="E352" s="33"/>
-      <c r="F352" s="33"/>
-    </row>
-    <row r="353" spans="2:6">
-      <c r="B353" s="33"/>
-      <c r="C353" s="33"/>
-      <c r="D353" s="33"/>
-      <c r="E353" s="33"/>
-      <c r="F353" s="33"/>
-    </row>
-    <row r="354" spans="2:6">
-      <c r="B354" s="33"/>
-      <c r="C354" s="33"/>
-      <c r="D354" s="33"/>
-      <c r="E354" s="33"/>
-      <c r="F354" s="33"/>
-    </row>
-    <row r="355" spans="2:6">
-      <c r="B355" s="33"/>
-      <c r="C355" s="33"/>
-      <c r="D355" s="33"/>
-      <c r="E355" s="33"/>
-      <c r="F355" s="33"/>
-    </row>
-    <row r="356" spans="2:6">
-      <c r="B356" s="33"/>
-      <c r="C356" s="33"/>
-      <c r="D356" s="33"/>
-      <c r="E356" s="33"/>
-      <c r="F356" s="33"/>
-    </row>
-    <row r="357" spans="2:6">
-      <c r="B357" s="33"/>
-      <c r="C357" s="33"/>
-      <c r="D357" s="33"/>
-      <c r="E357" s="33"/>
-      <c r="F357" s="33"/>
-    </row>
-    <row r="358" spans="2:6">
-      <c r="B358" s="33"/>
-      <c r="C358" s="33"/>
-      <c r="D358" s="33"/>
-      <c r="E358" s="33"/>
-      <c r="F358" s="33"/>
-    </row>
-    <row r="359" spans="2:6">
-      <c r="B359" s="33"/>
-      <c r="C359" s="33"/>
-      <c r="D359" s="33"/>
-      <c r="E359" s="33"/>
-      <c r="F359" s="33"/>
-    </row>
-    <row r="360" spans="2:6">
-      <c r="B360" s="33"/>
-      <c r="C360" s="33"/>
-      <c r="D360" s="33"/>
-      <c r="E360" s="33"/>
-      <c r="F360" s="33"/>
-    </row>
-    <row r="361" spans="2:6">
-      <c r="B361" s="33"/>
-      <c r="C361" s="33"/>
-      <c r="D361" s="33"/>
-      <c r="E361" s="33"/>
-      <c r="F361" s="33"/>
-    </row>
-    <row r="362" spans="2:6">
-      <c r="B362" s="33"/>
-      <c r="C362" s="33"/>
-      <c r="D362" s="33"/>
-      <c r="E362" s="33"/>
-      <c r="F362" s="33"/>
-    </row>
-    <row r="363" spans="2:6">
-      <c r="B363" s="33"/>
-      <c r="C363" s="33"/>
-      <c r="D363" s="33"/>
-      <c r="E363" s="33"/>
-      <c r="F363" s="33"/>
-    </row>
-    <row r="364" spans="2:6">
-      <c r="B364" s="33"/>
-      <c r="C364" s="33"/>
-      <c r="D364" s="33"/>
-      <c r="E364" s="33"/>
-      <c r="F364" s="33"/>
-    </row>
-    <row r="365" spans="2:6">
-      <c r="B365" s="33"/>
-      <c r="C365" s="33"/>
-      <c r="D365" s="33"/>
-      <c r="E365" s="33"/>
-      <c r="F365" s="33"/>
-    </row>
-    <row r="366" spans="2:6">
-      <c r="B366" s="33"/>
-      <c r="C366" s="33"/>
-      <c r="D366" s="33"/>
-      <c r="E366" s="33"/>
-      <c r="F366" s="33"/>
-    </row>
-    <row r="367" spans="2:6">
-      <c r="B367" s="33"/>
-      <c r="C367" s="33"/>
-      <c r="D367" s="33"/>
-      <c r="E367" s="33"/>
-      <c r="F367" s="33"/>
-    </row>
-    <row r="368" spans="2:6">
-      <c r="B368" s="33"/>
-      <c r="C368" s="33"/>
-      <c r="D368" s="33"/>
-      <c r="E368" s="33"/>
-      <c r="F368" s="33"/>
-    </row>
-    <row r="369" spans="2:6">
-      <c r="B369" s="33"/>
-      <c r="C369" s="33"/>
-      <c r="D369" s="33"/>
-      <c r="E369" s="33"/>
-      <c r="F369" s="33"/>
-    </row>
-    <row r="370" spans="2:6">
-      <c r="B370" s="33"/>
-      <c r="C370" s="33"/>
-      <c r="D370" s="33"/>
-      <c r="E370" s="33"/>
-      <c r="F370" s="33"/>
-    </row>
-    <row r="371" spans="2:6">
-      <c r="B371" s="33"/>
-      <c r="C371" s="33"/>
-      <c r="D371" s="33"/>
-      <c r="E371" s="33"/>
-      <c r="F371" s="33"/>
-    </row>
-    <row r="372" spans="2:6">
-      <c r="B372" s="33"/>
-      <c r="C372" s="33"/>
-      <c r="D372" s="33"/>
-      <c r="E372" s="33"/>
-      <c r="F372" s="33"/>
-    </row>
-    <row r="373" spans="2:6">
-      <c r="B373" s="33"/>
-      <c r="C373" s="33"/>
-      <c r="D373" s="33"/>
-      <c r="E373" s="33"/>
-      <c r="F373" s="33"/>
-    </row>
-    <row r="374" spans="2:6">
-      <c r="B374" s="33"/>
-      <c r="C374" s="33"/>
-      <c r="D374" s="33"/>
-      <c r="E374" s="33"/>
-      <c r="F374" s="33"/>
-    </row>
-    <row r="375" spans="2:6">
-      <c r="B375" s="33"/>
-      <c r="C375" s="33"/>
-      <c r="D375" s="33"/>
-      <c r="E375" s="33"/>
-      <c r="F375" s="33"/>
-    </row>
-    <row r="376" spans="2:6">
-      <c r="B376" s="33"/>
-      <c r="C376" s="33"/>
-      <c r="D376" s="33"/>
-      <c r="E376" s="33"/>
-      <c r="F376" s="33"/>
-    </row>
-    <row r="377" spans="2:6">
-      <c r="B377" s="33"/>
-      <c r="C377" s="33"/>
-      <c r="D377" s="33"/>
-      <c r="E377" s="33"/>
-      <c r="F377" s="33"/>
-    </row>
-    <row r="378" spans="2:6">
-      <c r="B378" s="33"/>
-      <c r="C378" s="33"/>
-      <c r="D378" s="33"/>
-      <c r="E378" s="33"/>
-      <c r="F378" s="33"/>
-    </row>
-    <row r="379" spans="2:6">
-      <c r="B379" s="33"/>
-      <c r="C379" s="33"/>
-      <c r="D379" s="33"/>
-      <c r="E379" s="33"/>
-      <c r="F379" s="33"/>
-    </row>
-    <row r="380" spans="2:6">
-      <c r="B380" s="33"/>
-      <c r="C380" s="33"/>
-      <c r="D380" s="33"/>
-      <c r="E380" s="33"/>
-      <c r="F380" s="33"/>
-    </row>
-    <row r="381" spans="2:6">
-      <c r="B381" s="33"/>
-      <c r="C381" s="33"/>
-      <c r="D381" s="33"/>
-      <c r="E381" s="33"/>
-      <c r="F381" s="33"/>
-    </row>
-    <row r="382" spans="2:6">
-      <c r="B382" s="33"/>
-      <c r="C382" s="33"/>
-      <c r="D382" s="33"/>
-      <c r="E382" s="33"/>
-      <c r="F382" s="33"/>
-    </row>
-    <row r="383" spans="2:6">
-      <c r="B383" s="33"/>
-      <c r="C383" s="33"/>
-      <c r="D383" s="33"/>
-      <c r="E383" s="33"/>
-      <c r="F383" s="33"/>
-    </row>
-    <row r="384" spans="2:6">
-      <c r="B384" s="33"/>
-      <c r="C384" s="33"/>
-      <c r="D384" s="33"/>
-      <c r="E384" s="33"/>
-      <c r="F384" s="33"/>
-    </row>
-    <row r="385" spans="2:6">
-      <c r="B385" s="33"/>
-      <c r="C385" s="33"/>
-      <c r="D385" s="33"/>
-      <c r="E385" s="33"/>
-      <c r="F385" s="33"/>
-    </row>
-    <row r="386" spans="2:6">
-      <c r="B386" s="33"/>
-      <c r="C386" s="33"/>
-      <c r="D386" s="33"/>
-      <c r="E386" s="33"/>
-      <c r="F386" s="33"/>
-    </row>
-    <row r="387" spans="2:6">
-      <c r="B387" s="33"/>
-      <c r="C387" s="33"/>
-      <c r="D387" s="33"/>
-      <c r="E387" s="33"/>
-      <c r="F387" s="33"/>
-    </row>
-    <row r="388" spans="2:6">
-      <c r="B388" s="33"/>
-      <c r="C388" s="33"/>
-      <c r="D388" s="33"/>
-      <c r="E388" s="33"/>
-      <c r="F388" s="33"/>
-    </row>
-    <row r="389" spans="2:6">
-      <c r="B389" s="33"/>
-      <c r="C389" s="33"/>
-      <c r="D389" s="33"/>
-      <c r="E389" s="33"/>
-      <c r="F389" s="33"/>
-    </row>
-    <row r="390" spans="2:6">
-      <c r="B390" s="33"/>
-      <c r="C390" s="33"/>
-      <c r="D390" s="33"/>
-      <c r="E390" s="33"/>
-      <c r="F390" s="33"/>
-    </row>
-    <row r="391" spans="2:6">
-      <c r="B391" s="33"/>
-      <c r="C391" s="33"/>
-      <c r="D391" s="33"/>
-      <c r="E391" s="33"/>
-      <c r="F391" s="33"/>
-    </row>
-    <row r="392" spans="2:6">
-      <c r="B392" s="33"/>
-      <c r="C392" s="33"/>
-      <c r="D392" s="33"/>
-      <c r="E392" s="33"/>
-      <c r="F392" s="33"/>
-    </row>
-    <row r="393" spans="2:6">
-      <c r="B393" s="33"/>
-      <c r="C393" s="33"/>
-      <c r="D393" s="33"/>
-      <c r="E393" s="33"/>
-      <c r="F393" s="33"/>
-    </row>
-    <row r="394" spans="2:6">
-      <c r="B394" s="33"/>
-      <c r="C394" s="33"/>
-      <c r="D394" s="33"/>
-      <c r="E394" s="33"/>
-      <c r="F394" s="33"/>
-    </row>
-    <row r="395" spans="2:6">
-      <c r="B395" s="33"/>
-      <c r="C395" s="33"/>
-      <c r="D395" s="33"/>
-      <c r="E395" s="33"/>
-      <c r="F395" s="33"/>
-    </row>
-    <row r="396" spans="2:6">
-      <c r="B396" s="33"/>
-      <c r="C396" s="33"/>
-      <c r="D396" s="33"/>
-      <c r="E396" s="33"/>
-      <c r="F396" s="33"/>
-    </row>
-    <row r="397" spans="2:6">
-      <c r="B397" s="33"/>
-      <c r="C397" s="33"/>
-      <c r="D397" s="33"/>
-      <c r="E397" s="33"/>
-      <c r="F397" s="33"/>
-    </row>
-    <row r="398" spans="2:6">
-      <c r="B398" s="33"/>
-      <c r="C398" s="33"/>
-      <c r="D398" s="33"/>
-      <c r="E398" s="33"/>
-      <c r="F398" s="33"/>
-    </row>
-    <row r="399" spans="2:6">
-      <c r="B399" s="33"/>
-      <c r="C399" s="33"/>
-      <c r="D399" s="33"/>
-      <c r="E399" s="33"/>
-      <c r="F399" s="33"/>
-    </row>
-    <row r="400" spans="2:6">
-      <c r="B400" s="33"/>
-      <c r="C400" s="33"/>
-      <c r="D400" s="33"/>
-      <c r="E400" s="33"/>
-      <c r="F400" s="33"/>
-    </row>
-    <row r="401" spans="2:6">
-      <c r="B401" s="33"/>
-      <c r="C401" s="33"/>
-      <c r="D401" s="33"/>
-      <c r="E401" s="33"/>
-      <c r="F401" s="33"/>
-    </row>
-    <row r="402" spans="2:6">
-      <c r="B402" s="33"/>
-      <c r="C402" s="33"/>
-      <c r="D402" s="33"/>
-      <c r="E402" s="33"/>
-      <c r="F402" s="33"/>
-    </row>
-    <row r="403" spans="2:6">
-      <c r="B403" s="33"/>
-      <c r="C403" s="33"/>
-      <c r="D403" s="33"/>
-      <c r="E403" s="33"/>
-      <c r="F403" s="33"/>
-    </row>
-    <row r="404" spans="2:6">
-      <c r="B404" s="33"/>
-      <c r="C404" s="33"/>
-      <c r="D404" s="33"/>
-      <c r="E404" s="33"/>
-      <c r="F404" s="33"/>
-    </row>
-    <row r="405" spans="2:6">
-      <c r="B405" s="33"/>
-      <c r="C405" s="33"/>
-      <c r="D405" s="33"/>
-      <c r="E405" s="33"/>
-      <c r="F405" s="33"/>
-    </row>
-    <row r="406" spans="2:6">
-      <c r="B406" s="33"/>
-      <c r="C406" s="33"/>
-      <c r="D406" s="33"/>
-      <c r="E406" s="33"/>
-      <c r="F406" s="33"/>
-    </row>
-    <row r="407" spans="2:6">
-      <c r="B407" s="33"/>
-      <c r="C407" s="33"/>
-      <c r="D407" s="33"/>
-      <c r="E407" s="33"/>
-      <c r="F407" s="33"/>
-    </row>
-    <row r="408" spans="2:6">
-      <c r="B408" s="33"/>
-      <c r="C408" s="33"/>
-      <c r="D408" s="33"/>
-      <c r="E408" s="33"/>
-      <c r="F408" s="33"/>
-    </row>
-    <row r="409" spans="2:6">
-      <c r="B409" s="33"/>
-      <c r="C409" s="33"/>
-      <c r="D409" s="33"/>
-      <c r="E409" s="33"/>
-      <c r="F409" s="33"/>
-    </row>
-    <row r="410" spans="2:6">
-      <c r="B410" s="33"/>
-      <c r="C410" s="33"/>
-      <c r="D410" s="33"/>
-      <c r="E410" s="33"/>
-      <c r="F410" s="33"/>
-    </row>
-    <row r="411" spans="2:6">
-      <c r="B411" s="33"/>
-      <c r="C411" s="33"/>
-      <c r="D411" s="33"/>
-      <c r="E411" s="33"/>
-      <c r="F411" s="33"/>
-    </row>
-    <row r="412" spans="2:6">
-      <c r="B412" s="33"/>
-      <c r="C412" s="33"/>
-      <c r="D412" s="33"/>
-      <c r="E412" s="33"/>
-      <c r="F412" s="33"/>
-    </row>
-    <row r="413" spans="2:6">
-      <c r="B413" s="33"/>
-      <c r="C413" s="33"/>
-      <c r="D413" s="33"/>
-      <c r="E413" s="33"/>
-      <c r="F413" s="33"/>
-    </row>
-    <row r="414" spans="2:6">
-      <c r="B414" s="33"/>
-      <c r="C414" s="33"/>
-      <c r="D414" s="33"/>
-      <c r="E414" s="33"/>
-      <c r="F414" s="33"/>
-    </row>
-    <row r="415" spans="2:6">
-      <c r="B415" s="33"/>
-      <c r="C415" s="33"/>
-      <c r="D415" s="33"/>
-      <c r="E415" s="33"/>
-      <c r="F415" s="33"/>
-    </row>
-    <row r="416" spans="2:6">
-      <c r="B416" s="33"/>
-      <c r="C416" s="33"/>
-      <c r="D416" s="33"/>
-      <c r="E416" s="33"/>
-      <c r="F416" s="33"/>
-    </row>
-    <row r="417" spans="2:6">
-      <c r="B417" s="33"/>
-      <c r="C417" s="33"/>
-      <c r="D417" s="33"/>
-      <c r="E417" s="33"/>
-      <c r="F417" s="33"/>
-    </row>
-    <row r="418" spans="2:6">
-      <c r="B418" s="33"/>
-      <c r="C418" s="33"/>
-      <c r="D418" s="33"/>
-      <c r="E418" s="33"/>
-      <c r="F418" s="33"/>
-    </row>
-    <row r="419" spans="2:6">
-      <c r="B419" s="33"/>
-      <c r="C419" s="33"/>
-      <c r="D419" s="33"/>
-      <c r="E419" s="33"/>
-      <c r="F419" s="33"/>
-    </row>
-    <row r="420" spans="2:6">
-      <c r="B420" s="33"/>
-      <c r="C420" s="33"/>
-      <c r="D420" s="33"/>
-      <c r="E420" s="33"/>
-      <c r="F420" s="33"/>
-    </row>
-    <row r="421" spans="2:6">
-      <c r="B421" s="33"/>
-      <c r="C421" s="33"/>
-      <c r="D421" s="33"/>
-      <c r="E421" s="33"/>
-      <c r="F421" s="33"/>
-    </row>
-    <row r="422" spans="2:6">
-      <c r="B422" s="33"/>
-      <c r="C422" s="33"/>
-      <c r="D422" s="33"/>
-      <c r="E422" s="33"/>
-      <c r="F422" s="33"/>
-    </row>
-    <row r="423" spans="2:6">
-      <c r="B423" s="33"/>
-      <c r="C423" s="33"/>
-      <c r="D423" s="33"/>
-      <c r="E423" s="33"/>
-      <c r="F423" s="33"/>
-    </row>
-    <row r="424" spans="2:6">
-      <c r="B424" s="33"/>
-      <c r="C424" s="33"/>
-      <c r="D424" s="33"/>
-      <c r="E424" s="33"/>
-      <c r="F424" s="33"/>
-    </row>
-    <row r="425" spans="2:6">
-      <c r="B425" s="33"/>
-      <c r="C425" s="33"/>
-      <c r="D425" s="33"/>
-      <c r="E425" s="33"/>
-      <c r="F425" s="33"/>
-    </row>
-    <row r="426" spans="2:6">
-      <c r="B426" s="33"/>
-      <c r="C426" s="33"/>
-      <c r="D426" s="33"/>
-      <c r="E426" s="33"/>
-      <c r="F426" s="33"/>
-    </row>
-    <row r="427" spans="2:6">
-      <c r="B427" s="33"/>
-      <c r="C427" s="33"/>
-      <c r="D427" s="33"/>
-      <c r="E427" s="33"/>
-      <c r="F427" s="33"/>
-    </row>
-    <row r="428" spans="2:6">
-      <c r="B428" s="33"/>
-      <c r="C428" s="33"/>
-      <c r="D428" s="33"/>
-      <c r="E428" s="33"/>
-      <c r="F428" s="33"/>
-    </row>
-    <row r="429" spans="2:6">
-      <c r="B429" s="33"/>
-      <c r="C429" s="33"/>
-      <c r="D429" s="33"/>
-      <c r="E429" s="33"/>
-      <c r="F429" s="33"/>
-    </row>
-    <row r="430" spans="2:6">
-      <c r="B430" s="33"/>
-      <c r="C430" s="33"/>
-      <c r="D430" s="33"/>
-      <c r="E430" s="33"/>
-      <c r="F430" s="33"/>
-    </row>
-    <row r="431" spans="2:6">
-      <c r="B431" s="33"/>
-      <c r="C431" s="33"/>
-      <c r="D431" s="33"/>
-      <c r="E431" s="33"/>
-      <c r="F431" s="33"/>
-    </row>
-    <row r="432" spans="2:6">
-      <c r="B432" s="33"/>
-      <c r="C432" s="33"/>
-      <c r="D432" s="33"/>
-      <c r="E432" s="33"/>
-      <c r="F432" s="33"/>
-    </row>
-    <row r="433" spans="2:6">
-      <c r="B433" s="33"/>
-      <c r="C433" s="33"/>
-      <c r="D433" s="33"/>
-      <c r="E433" s="33"/>
-      <c r="F433" s="33"/>
-    </row>
-    <row r="434" spans="2:6">
-      <c r="B434" s="33"/>
-      <c r="C434" s="33"/>
-      <c r="D434" s="33"/>
-      <c r="E434" s="33"/>
-      <c r="F434" s="33"/>
-    </row>
-    <row r="435" spans="2:6">
-      <c r="B435" s="33"/>
-      <c r="C435" s="33"/>
-      <c r="D435" s="33"/>
-      <c r="E435" s="33"/>
-      <c r="F435" s="33"/>
-    </row>
-    <row r="436" spans="2:6">
-      <c r="B436" s="33"/>
-      <c r="C436" s="33"/>
-      <c r="D436" s="33"/>
-      <c r="E436" s="33"/>
-      <c r="F436" s="33"/>
-    </row>
-    <row r="437" spans="2:6">
-      <c r="B437" s="33"/>
-      <c r="C437" s="33"/>
-      <c r="D437" s="33"/>
-      <c r="E437" s="33"/>
-      <c r="F437" s="33"/>
-    </row>
-    <row r="438" spans="2:6">
-      <c r="B438" s="33"/>
-      <c r="C438" s="33"/>
-      <c r="D438" s="33"/>
-      <c r="E438" s="33"/>
-      <c r="F438" s="33"/>
-    </row>
-    <row r="439" spans="2:6">
-      <c r="B439" s="33"/>
-      <c r="C439" s="33"/>
-      <c r="D439" s="33"/>
-      <c r="E439" s="33"/>
-      <c r="F439" s="33"/>
-    </row>
-    <row r="440" spans="2:6">
-      <c r="B440" s="33"/>
-      <c r="C440" s="33"/>
-      <c r="D440" s="33"/>
-      <c r="E440" s="33"/>
-      <c r="F440" s="33"/>
-    </row>
-    <row r="441" spans="2:6">
-      <c r="B441" s="33"/>
-      <c r="C441" s="33"/>
-      <c r="D441" s="33"/>
-      <c r="E441" s="33"/>
-      <c r="F441" s="33"/>
-    </row>
-    <row r="442" spans="2:6">
-      <c r="B442" s="33"/>
-      <c r="C442" s="33"/>
-      <c r="D442" s="33"/>
-      <c r="E442" s="33"/>
-      <c r="F442" s="33"/>
-    </row>
-    <row r="443" spans="2:6">
-      <c r="B443" s="33"/>
-      <c r="C443" s="33"/>
-      <c r="D443" s="33"/>
-      <c r="E443" s="33"/>
-      <c r="F443" s="33"/>
-    </row>
-    <row r="444" spans="2:6">
-      <c r="B444" s="33"/>
-      <c r="C444" s="33"/>
-      <c r="D444" s="33"/>
-      <c r="E444" s="33"/>
-      <c r="F444" s="33"/>
-    </row>
-    <row r="445" spans="2:6">
-      <c r="B445" s="33"/>
-      <c r="C445" s="33"/>
-      <c r="D445" s="33"/>
-      <c r="E445" s="33"/>
-      <c r="F445" s="33"/>
-    </row>
-    <row r="446" spans="2:6">
-      <c r="B446" s="33"/>
-      <c r="C446" s="33"/>
-      <c r="D446" s="33"/>
-      <c r="E446" s="33"/>
-      <c r="F446" s="33"/>
-    </row>
-    <row r="447" spans="2:6">
-      <c r="B447" s="33"/>
-      <c r="C447" s="33"/>
-      <c r="D447" s="33"/>
-      <c r="E447" s="33"/>
-      <c r="F447" s="33"/>
-    </row>
-    <row r="448" spans="2:6">
-      <c r="B448" s="33"/>
-      <c r="C448" s="33"/>
-      <c r="D448" s="33"/>
-      <c r="E448" s="33"/>
-      <c r="F448" s="33"/>
-    </row>
-    <row r="449" spans="2:6">
-      <c r="B449" s="33"/>
-      <c r="C449" s="33"/>
-      <c r="D449" s="33"/>
-      <c r="E449" s="33"/>
-      <c r="F449" s="33"/>
-    </row>
-    <row r="450" spans="2:6">
-      <c r="B450" s="33"/>
-      <c r="C450" s="33"/>
-      <c r="D450" s="33"/>
-      <c r="E450" s="33"/>
-      <c r="F450" s="33"/>
-    </row>
-    <row r="451" spans="2:6">
-      <c r="B451" s="33"/>
-      <c r="C451" s="33"/>
-      <c r="D451" s="33"/>
-      <c r="E451" s="33"/>
-      <c r="F451" s="33"/>
-    </row>
-    <row r="452" spans="2:6">
-      <c r="B452" s="33"/>
-      <c r="C452" s="33"/>
-      <c r="D452" s="33"/>
-      <c r="E452" s="33"/>
-      <c r="F452" s="33"/>
-    </row>
-    <row r="453" spans="2:6">
-      <c r="B453" s="33"/>
-      <c r="C453" s="33"/>
-      <c r="D453" s="33"/>
-      <c r="E453" s="33"/>
-      <c r="F453" s="33"/>
-    </row>
-    <row r="454" spans="2:6">
-      <c r="B454" s="33"/>
-      <c r="C454" s="33"/>
-      <c r="D454" s="33"/>
-      <c r="E454" s="33"/>
-      <c r="F454" s="33"/>
-    </row>
-    <row r="455" spans="2:6">
-      <c r="B455" s="33"/>
-      <c r="C455" s="33"/>
-      <c r="D455" s="33"/>
-      <c r="E455" s="33"/>
-      <c r="F455" s="33"/>
-    </row>
-    <row r="456" spans="2:6">
-      <c r="B456" s="33"/>
-      <c r="C456" s="33"/>
-      <c r="D456" s="33"/>
-      <c r="E456" s="33"/>
-      <c r="F456" s="33"/>
-    </row>
-    <row r="457" spans="2:6">
-      <c r="B457" s="33"/>
-      <c r="C457" s="33"/>
-      <c r="D457" s="33"/>
-      <c r="E457" s="33"/>
-      <c r="F457" s="33"/>
-    </row>
-    <row r="458" spans="2:6">
-      <c r="B458" s="33"/>
-      <c r="C458" s="33"/>
-      <c r="D458" s="33"/>
-      <c r="E458" s="33"/>
-      <c r="F458" s="33"/>
-    </row>
-    <row r="459" spans="2:6">
-      <c r="B459" s="33"/>
-      <c r="C459" s="33"/>
-      <c r="D459" s="33"/>
-      <c r="E459" s="33"/>
-      <c r="F459" s="33"/>
-    </row>
-    <row r="460" spans="2:6">
-      <c r="B460" s="33"/>
-      <c r="C460" s="33"/>
-      <c r="D460" s="33"/>
-      <c r="E460" s="33"/>
-      <c r="F460" s="33"/>
-    </row>
-    <row r="461" spans="2:6">
-      <c r="B461" s="33"/>
-      <c r="C461" s="33"/>
-      <c r="D461" s="33"/>
-      <c r="E461" s="33"/>
-      <c r="F461" s="33"/>
-    </row>
-    <row r="462" spans="2:6">
-      <c r="B462" s="33"/>
-      <c r="C462" s="33"/>
-      <c r="D462" s="33"/>
-      <c r="E462" s="33"/>
-      <c r="F462" s="33"/>
-    </row>
-    <row r="463" spans="2:6">
-      <c r="B463" s="33"/>
-      <c r="C463" s="33"/>
-      <c r="D463" s="33"/>
-      <c r="E463" s="33"/>
-      <c r="F463" s="33"/>
-    </row>
-    <row r="464" spans="2:6">
-      <c r="B464" s="33"/>
-      <c r="C464" s="33"/>
-      <c r="D464" s="33"/>
-      <c r="E464" s="33"/>
-      <c r="F464" s="33"/>
-    </row>
-    <row r="465" spans="2:6">
-      <c r="B465" s="33"/>
-      <c r="C465" s="33"/>
-      <c r="D465" s="33"/>
-      <c r="E465" s="33"/>
-      <c r="F465" s="33"/>
-    </row>
-    <row r="466" spans="2:6">
-      <c r="B466" s="33"/>
-      <c r="C466" s="33"/>
-      <c r="D466" s="33"/>
-      <c r="E466" s="33"/>
-      <c r="F466" s="33"/>
-    </row>
-    <row r="467" spans="2:6">
-      <c r="B467" s="33"/>
-      <c r="C467" s="33"/>
-      <c r="D467" s="33"/>
-      <c r="E467" s="33"/>
-      <c r="F467" s="33"/>
-    </row>
-    <row r="468" spans="2:6">
-      <c r="B468" s="33"/>
-      <c r="C468" s="33"/>
-      <c r="D468" s="33"/>
-      <c r="E468" s="33"/>
-      <c r="F468" s="33"/>
-    </row>
-    <row r="469" spans="2:6">
-      <c r="B469" s="33"/>
-      <c r="C469" s="33"/>
-      <c r="D469" s="33"/>
-      <c r="E469" s="33"/>
-      <c r="F469" s="33"/>
-    </row>
-    <row r="470" spans="2:6">
-      <c r="B470" s="33"/>
-      <c r="C470" s="33"/>
-      <c r="D470" s="33"/>
-      <c r="E470" s="33"/>
-      <c r="F470" s="33"/>
-    </row>
-    <row r="471" spans="2:6">
-      <c r="B471" s="33"/>
-      <c r="C471" s="33"/>
-      <c r="D471" s="33"/>
-      <c r="E471" s="33"/>
-      <c r="F471" s="33"/>
-    </row>
-    <row r="472" spans="2:6">
-      <c r="B472" s="33"/>
-      <c r="C472" s="33"/>
-      <c r="D472" s="33"/>
-      <c r="E472" s="33"/>
-      <c r="F472" s="33"/>
-    </row>
-    <row r="473" spans="2:6">
-      <c r="B473" s="33"/>
-      <c r="C473" s="33"/>
-      <c r="D473" s="33"/>
-      <c r="E473" s="33"/>
-      <c r="F473" s="33"/>
-    </row>
-    <row r="474" spans="2:6">
-      <c r="B474" s="33"/>
-      <c r="C474" s="33"/>
-      <c r="D474" s="33"/>
-      <c r="E474" s="33"/>
-      <c r="F474" s="33"/>
-    </row>
-    <row r="475" spans="2:6">
-      <c r="B475" s="33"/>
-      <c r="C475" s="33"/>
-      <c r="D475" s="33"/>
-      <c r="E475" s="33"/>
-      <c r="F475" s="33"/>
-    </row>
-    <row r="476" spans="2:6">
-      <c r="B476" s="33"/>
-      <c r="C476" s="33"/>
-      <c r="D476" s="33"/>
-      <c r="E476" s="33"/>
-      <c r="F476" s="33"/>
-    </row>
-    <row r="477" spans="2:6">
-      <c r="B477" s="33"/>
-      <c r="C477" s="33"/>
-      <c r="D477" s="33"/>
-      <c r="E477" s="33"/>
-      <c r="F477" s="33"/>
-    </row>
-    <row r="478" spans="2:6">
-      <c r="B478" s="33"/>
-      <c r="C478" s="33"/>
-      <c r="D478" s="33"/>
-      <c r="E478" s="33"/>
-      <c r="F478" s="33"/>
-    </row>
-    <row r="479" spans="2:6">
-      <c r="B479" s="33"/>
-      <c r="C479" s="33"/>
-      <c r="D479" s="33"/>
-      <c r="E479" s="33"/>
-      <c r="F479" s="33"/>
-    </row>
-    <row r="480" spans="2:6">
-      <c r="B480" s="33"/>
-      <c r="C480" s="33"/>
-      <c r="D480" s="33"/>
-      <c r="E480" s="33"/>
-      <c r="F480" s="33"/>
-    </row>
-    <row r="481" spans="2:6">
-      <c r="B481" s="33"/>
-      <c r="C481" s="33"/>
-      <c r="D481" s="33"/>
-      <c r="E481" s="33"/>
-      <c r="F481" s="33"/>
-    </row>
-    <row r="482" spans="2:6">
-      <c r="B482" s="33"/>
-      <c r="C482" s="33"/>
-      <c r="D482" s="33"/>
-      <c r="E482" s="33"/>
-      <c r="F482" s="33"/>
-    </row>
-    <row r="483" spans="2:6">
-      <c r="B483" s="33"/>
-      <c r="C483" s="33"/>
-      <c r="D483" s="33"/>
-      <c r="E483" s="33"/>
-      <c r="F483" s="33"/>
-    </row>
-    <row r="484" spans="2:6">
-      <c r="B484" s="33"/>
-      <c r="C484" s="33"/>
-      <c r="D484" s="33"/>
-      <c r="E484" s="33"/>
-      <c r="F484" s="33"/>
-    </row>
-    <row r="485" spans="2:6">
-      <c r="B485" s="33"/>
-      <c r="C485" s="33"/>
-      <c r="D485" s="33"/>
-      <c r="E485" s="33"/>
-      <c r="F485" s="33"/>
-    </row>
-    <row r="486" spans="2:6">
-      <c r="B486" s="33"/>
-      <c r="C486" s="33"/>
-      <c r="D486" s="33"/>
-      <c r="E486" s="33"/>
-      <c r="F486" s="33"/>
-    </row>
-    <row r="487" spans="2:6">
-      <c r="B487" s="33"/>
-      <c r="C487" s="33"/>
-      <c r="D487" s="33"/>
-      <c r="E487" s="33"/>
-      <c r="F487" s="33"/>
-    </row>
-    <row r="488" spans="2:6">
-      <c r="B488" s="33"/>
-      <c r="C488" s="33"/>
-      <c r="D488" s="33"/>
-      <c r="E488" s="33"/>
-      <c r="F488" s="33"/>
-    </row>
-    <row r="489" spans="2:6">
-      <c r="B489" s="33"/>
-      <c r="C489" s="33"/>
-      <c r="D489" s="33"/>
-      <c r="E489" s="33"/>
-      <c r="F489" s="33"/>
-    </row>
-    <row r="490" spans="2:6">
-      <c r="B490" s="33"/>
-      <c r="C490" s="33"/>
-      <c r="D490" s="33"/>
-      <c r="E490" s="33"/>
-      <c r="F490" s="33"/>
-    </row>
-    <row r="491" spans="2:6">
-      <c r="B491" s="33"/>
-      <c r="C491" s="33"/>
-      <c r="D491" s="33"/>
-      <c r="E491" s="33"/>
-      <c r="F491" s="33"/>
-    </row>
-    <row r="492" spans="2:6">
-      <c r="B492" s="33"/>
-      <c r="C492" s="33"/>
-      <c r="D492" s="33"/>
-      <c r="E492" s="33"/>
-      <c r="F492" s="33"/>
-    </row>
-    <row r="493" spans="2:6">
-      <c r="B493" s="33"/>
-      <c r="C493" s="33"/>
-      <c r="D493" s="33"/>
-      <c r="E493" s="33"/>
-      <c r="F493" s="33"/>
-    </row>
-    <row r="494" spans="2:6">
-      <c r="B494" s="33"/>
-      <c r="C494" s="33"/>
-      <c r="D494" s="33"/>
-      <c r="E494" s="33"/>
-      <c r="F494" s="33"/>
-    </row>
-    <row r="495" spans="2:6">
-      <c r="B495" s="33"/>
-      <c r="C495" s="33"/>
-      <c r="D495" s="33"/>
-      <c r="E495" s="33"/>
-      <c r="F495" s="33"/>
-    </row>
-    <row r="496" spans="2:6">
-      <c r="B496" s="33"/>
-      <c r="C496" s="33"/>
-      <c r="D496" s="33"/>
-      <c r="E496" s="33"/>
-      <c r="F496" s="33"/>
-    </row>
-    <row r="497" spans="2:6">
-      <c r="B497" s="33"/>
-      <c r="C497" s="33"/>
-      <c r="D497" s="33"/>
-      <c r="E497" s="33"/>
-      <c r="F497" s="33"/>
-    </row>
-    <row r="498" spans="2:6">
-      <c r="B498" s="33"/>
-      <c r="C498" s="33"/>
-      <c r="D498" s="33"/>
-      <c r="E498" s="33"/>
-      <c r="F498" s="33"/>
-    </row>
-    <row r="499" spans="2:6">
-      <c r="B499" s="33"/>
-      <c r="C499" s="33"/>
-      <c r="D499" s="33"/>
-      <c r="E499" s="33"/>
-      <c r="F499" s="33"/>
-    </row>
-    <row r="500" spans="2:6">
-      <c r="B500" s="33"/>
-      <c r="C500" s="33"/>
-      <c r="D500" s="33"/>
-      <c r="E500" s="33"/>
-      <c r="F500" s="33"/>
-    </row>
-    <row r="501" spans="2:6">
-      <c r="B501" s="33"/>
-      <c r="C501" s="33"/>
-      <c r="D501" s="33"/>
-      <c r="E501" s="33"/>
-      <c r="F501" s="33"/>
-    </row>
-    <row r="502" spans="2:6">
-      <c r="B502" s="33"/>
-      <c r="C502" s="33"/>
-      <c r="D502" s="33"/>
-      <c r="E502" s="33"/>
-      <c r="F502" s="33"/>
-    </row>
-    <row r="503" spans="2:6">
-      <c r="B503" s="33"/>
-      <c r="C503" s="33"/>
-      <c r="D503" s="33"/>
-      <c r="E503" s="33"/>
-      <c r="F503" s="33"/>
-    </row>
-    <row r="504" spans="2:6">
-      <c r="B504" s="33"/>
-      <c r="C504" s="33"/>
-      <c r="D504" s="33"/>
-      <c r="E504" s="33"/>
-      <c r="F504" s="33"/>
-    </row>
-    <row r="505" spans="2:6">
-      <c r="B505" s="33"/>
-      <c r="C505" s="33"/>
-      <c r="D505" s="33"/>
-      <c r="E505" s="33"/>
-      <c r="F505" s="33"/>
-    </row>
-    <row r="506" spans="2:6">
-      <c r="B506" s="33"/>
-      <c r="C506" s="33"/>
-      <c r="D506" s="33"/>
-      <c r="E506" s="33"/>
-      <c r="F506" s="33"/>
-    </row>
-    <row r="507" spans="2:6">
-      <c r="B507" s="33"/>
-      <c r="C507" s="33"/>
-      <c r="D507" s="33"/>
-      <c r="E507" s="33"/>
-      <c r="F507" s="33"/>
-    </row>
-    <row r="508" spans="2:6">
-      <c r="B508" s="33"/>
-      <c r="C508" s="33"/>
-      <c r="D508" s="33"/>
-      <c r="E508" s="33"/>
-      <c r="F508" s="33"/>
-    </row>
-    <row r="509" spans="2:6">
-      <c r="B509" s="33"/>
-      <c r="C509" s="33"/>
-      <c r="D509" s="33"/>
-      <c r="E509" s="33"/>
-      <c r="F509" s="33"/>
-    </row>
-    <row r="510" spans="2:6">
-      <c r="B510" s="33"/>
-      <c r="C510" s="33"/>
-      <c r="D510" s="33"/>
-      <c r="E510" s="33"/>
-      <c r="F510" s="33"/>
-    </row>
-    <row r="511" spans="2:6">
-      <c r="B511" s="33"/>
-      <c r="C511" s="33"/>
-      <c r="D511" s="33"/>
-      <c r="E511" s="33"/>
-      <c r="F511" s="33"/>
-    </row>
-    <row r="512" spans="2:6">
-      <c r="B512" s="33"/>
-      <c r="C512" s="33"/>
-      <c r="D512" s="33"/>
-      <c r="E512" s="33"/>
-      <c r="F512" s="33"/>
-    </row>
-    <row r="513" spans="2:6">
-      <c r="B513" s="33"/>
-      <c r="C513" s="33"/>
-      <c r="D513" s="33"/>
-      <c r="E513" s="33"/>
-      <c r="F513" s="33"/>
-    </row>
-    <row r="514" spans="2:6">
-      <c r="B514" s="33"/>
-      <c r="C514" s="33"/>
-      <c r="D514" s="33"/>
-      <c r="E514" s="33"/>
-      <c r="F514" s="33"/>
-    </row>
-    <row r="515" spans="2:6">
-      <c r="B515" s="33"/>
-      <c r="C515" s="33"/>
-      <c r="D515" s="33"/>
-      <c r="E515" s="33"/>
-      <c r="F515" s="33"/>
-    </row>
-    <row r="516" spans="2:6">
-      <c r="B516" s="33"/>
-      <c r="C516" s="33"/>
-      <c r="D516" s="33"/>
-      <c r="E516" s="33"/>
-      <c r="F516" s="33"/>
-    </row>
-    <row r="517" spans="2:6">
-      <c r="B517" s="33"/>
-      <c r="C517" s="33"/>
-      <c r="D517" s="33"/>
-      <c r="E517" s="33"/>
-      <c r="F517" s="33"/>
-    </row>
-    <row r="518" spans="2:6">
-      <c r="B518" s="33"/>
-      <c r="C518" s="33"/>
-      <c r="D518" s="33"/>
-      <c r="E518" s="33"/>
-      <c r="F518" s="33"/>
-    </row>
-    <row r="519" spans="2:6">
-      <c r="B519" s="33"/>
-      <c r="C519" s="33"/>
-      <c r="D519" s="33"/>
-      <c r="E519" s="33"/>
-      <c r="F519" s="33"/>
-    </row>
-    <row r="520" spans="2:6">
-      <c r="B520" s="33"/>
-      <c r="C520" s="33"/>
-      <c r="D520" s="33"/>
-      <c r="E520" s="33"/>
-      <c r="F520" s="33"/>
-    </row>
-    <row r="521" spans="2:6">
-      <c r="B521" s="33"/>
-      <c r="C521" s="33"/>
-      <c r="D521" s="33"/>
-      <c r="E521" s="33"/>
-      <c r="F521" s="33"/>
-    </row>
-    <row r="522" spans="2:6">
-      <c r="B522" s="33"/>
-      <c r="C522" s="33"/>
-      <c r="D522" s="33"/>
-      <c r="E522" s="33"/>
-      <c r="F522" s="33"/>
-    </row>
-    <row r="523" spans="2:6">
-      <c r="B523" s="33"/>
-      <c r="C523" s="33"/>
-      <c r="D523" s="33"/>
-      <c r="E523" s="33"/>
-      <c r="F523" s="33"/>
-    </row>
-    <row r="524" spans="2:6">
-      <c r="B524" s="33"/>
-      <c r="C524" s="33"/>
-      <c r="D524" s="33"/>
-      <c r="E524" s="33"/>
-      <c r="F524" s="33"/>
-    </row>
-    <row r="525" spans="2:6">
-      <c r="B525" s="33"/>
-      <c r="C525" s="33"/>
-      <c r="D525" s="33"/>
-      <c r="E525" s="33"/>
-      <c r="F525" s="33"/>
-    </row>
-    <row r="526" spans="2:6">
-      <c r="B526" s="33"/>
-      <c r="C526" s="33"/>
-      <c r="D526" s="33"/>
-      <c r="E526" s="33"/>
-      <c r="F526" s="33"/>
-    </row>
-    <row r="527" spans="2:6">
-      <c r="B527" s="33"/>
-      <c r="C527" s="33"/>
-      <c r="D527" s="33"/>
-      <c r="E527" s="33"/>
-      <c r="F527" s="33"/>
-    </row>
-    <row r="528" spans="2:6">
-      <c r="B528" s="33"/>
-      <c r="C528" s="33"/>
-      <c r="D528" s="33"/>
-      <c r="E528" s="33"/>
-      <c r="F528" s="33"/>
-    </row>
-    <row r="529" spans="2:6">
-      <c r="B529" s="33"/>
-      <c r="C529" s="33"/>
-      <c r="D529" s="33"/>
-      <c r="E529" s="33"/>
-      <c r="F529" s="33"/>
-    </row>
-    <row r="530" spans="2:6">
-      <c r="B530" s="33"/>
-      <c r="C530" s="33"/>
-      <c r="D530" s="33"/>
-      <c r="E530" s="33"/>
-      <c r="F530" s="33"/>
-    </row>
-    <row r="531" spans="2:6">
-      <c r="B531" s="33"/>
-      <c r="C531" s="33"/>
-      <c r="D531" s="33"/>
-      <c r="E531" s="33"/>
-      <c r="F531" s="33"/>
-    </row>
-    <row r="532" spans="2:6">
-      <c r="B532" s="33"/>
-      <c r="C532" s="33"/>
-      <c r="D532" s="33"/>
-      <c r="E532" s="33"/>
-      <c r="F532" s="33"/>
-    </row>
-    <row r="533" spans="2:6">
-      <c r="B533" s="33"/>
-      <c r="C533" s="33"/>
-      <c r="D533" s="33"/>
-      <c r="E533" s="33"/>
-      <c r="F533" s="33"/>
-    </row>
-    <row r="534" spans="2:6">
-      <c r="B534" s="33"/>
-      <c r="C534" s="33"/>
-      <c r="D534" s="33"/>
-      <c r="E534" s="33"/>
-      <c r="F534" s="33"/>
-    </row>
-    <row r="535" spans="2:6">
-      <c r="B535" s="33"/>
-      <c r="C535" s="33"/>
-      <c r="D535" s="33"/>
-      <c r="E535" s="33"/>
-      <c r="F535" s="33"/>
-    </row>
-    <row r="536" spans="2:6">
-      <c r="B536" s="33"/>
-      <c r="C536" s="33"/>
-      <c r="D536" s="33"/>
-      <c r="E536" s="33"/>
-      <c r="F536" s="33"/>
-    </row>
-    <row r="537" spans="2:6">
-      <c r="B537" s="33"/>
-      <c r="C537" s="33"/>
-      <c r="D537" s="33"/>
-      <c r="E537" s="33"/>
-      <c r="F537" s="33"/>
-    </row>
-    <row r="538" spans="2:6">
-      <c r="B538" s="33"/>
-      <c r="C538" s="33"/>
-      <c r="D538" s="33"/>
-      <c r="E538" s="33"/>
-      <c r="F538" s="33"/>
-    </row>
-    <row r="539" spans="2:6">
-      <c r="B539" s="33"/>
-      <c r="C539" s="33"/>
-      <c r="D539" s="33"/>
-      <c r="E539" s="33"/>
-      <c r="F539" s="33"/>
-    </row>
-    <row r="540" spans="2:6">
-      <c r="B540" s="33"/>
-      <c r="C540" s="33"/>
-      <c r="D540" s="33"/>
-      <c r="E540" s="33"/>
-      <c r="F540" s="33"/>
-    </row>
-    <row r="541" spans="2:6">
-      <c r="B541" s="33"/>
-      <c r="C541" s="33"/>
-      <c r="D541" s="33"/>
-      <c r="E541" s="33"/>
-      <c r="F541" s="33"/>
-    </row>
-    <row r="542" spans="2:6">
-      <c r="B542" s="33"/>
-      <c r="C542" s="33"/>
-      <c r="D542" s="33"/>
-      <c r="E542" s="33"/>
-      <c r="F542" s="33"/>
-    </row>
-    <row r="543" spans="2:6">
-      <c r="B543" s="33"/>
-      <c r="C543" s="33"/>
-      <c r="D543" s="33"/>
-      <c r="E543" s="33"/>
-      <c r="F543" s="33"/>
-    </row>
-    <row r="544" spans="2:6">
-      <c r="B544" s="33"/>
-      <c r="C544" s="33"/>
-      <c r="D544" s="33"/>
-      <c r="E544" s="33"/>
-      <c r="F544" s="33"/>
-    </row>
-    <row r="545" spans="2:6">
-      <c r="B545" s="33"/>
-      <c r="C545" s="33"/>
-      <c r="D545" s="33"/>
-      <c r="E545" s="33"/>
-      <c r="F545" s="33"/>
-    </row>
-    <row r="546" spans="2:6">
-      <c r="B546" s="33"/>
-      <c r="C546" s="33"/>
-      <c r="D546" s="33"/>
-      <c r="E546" s="33"/>
-      <c r="F546" s="33"/>
-    </row>
-    <row r="547" spans="2:6">
-      <c r="B547" s="33"/>
-      <c r="C547" s="33"/>
-      <c r="D547" s="33"/>
-      <c r="E547" s="33"/>
-      <c r="F547" s="33"/>
-    </row>
-    <row r="548" spans="2:6">
-      <c r="B548" s="33"/>
-      <c r="C548" s="33"/>
-      <c r="D548" s="33"/>
-      <c r="E548" s="33"/>
-      <c r="F548" s="33"/>
-    </row>
-    <row r="549" spans="2:6">
-      <c r="B549" s="33"/>
-      <c r="C549" s="33"/>
-      <c r="D549" s="33"/>
-      <c r="E549" s="33"/>
-      <c r="F549" s="33"/>
-    </row>
-    <row r="550" spans="2:6">
-      <c r="B550" s="33"/>
-      <c r="C550" s="33"/>
-      <c r="D550" s="33"/>
-      <c r="E550" s="33"/>
-      <c r="F550" s="33"/>
-    </row>
-    <row r="551" spans="2:6">
-      <c r="B551" s="33"/>
-      <c r="C551" s="33"/>
-      <c r="D551" s="33"/>
-      <c r="E551" s="33"/>
-      <c r="F551" s="33"/>
-    </row>
-    <row r="552" spans="2:6">
-      <c r="B552" s="33"/>
-      <c r="C552" s="33"/>
-      <c r="D552" s="33"/>
-      <c r="E552" s="33"/>
-      <c r="F552" s="33"/>
-    </row>
-    <row r="553" spans="2:6">
-      <c r="B553" s="33"/>
-      <c r="C553" s="33"/>
-      <c r="D553" s="33"/>
-      <c r="E553" s="33"/>
-      <c r="F553" s="33"/>
-    </row>
-    <row r="554" spans="2:6">
-      <c r="B554" s="33"/>
-      <c r="C554" s="33"/>
-      <c r="D554" s="33"/>
-      <c r="E554" s="33"/>
-      <c r="F554" s="33"/>
-    </row>
-    <row r="555" spans="2:6">
-      <c r="B555" s="33"/>
-      <c r="C555" s="33"/>
-      <c r="D555" s="33"/>
-      <c r="E555" s="33"/>
-      <c r="F555" s="33"/>
-    </row>
-    <row r="556" spans="2:6">
-      <c r="B556" s="33"/>
-      <c r="C556" s="33"/>
-      <c r="D556" s="33"/>
-      <c r="E556" s="33"/>
-      <c r="F556" s="33"/>
-    </row>
-    <row r="557" spans="2:6">
-      <c r="B557" s="33"/>
-      <c r="C557" s="33"/>
-      <c r="D557" s="33"/>
-      <c r="E557" s="33"/>
-      <c r="F557" s="33"/>
-    </row>
-    <row r="558" spans="2:6">
-      <c r="B558" s="33"/>
-      <c r="C558" s="33"/>
-      <c r="D558" s="33"/>
-      <c r="E558" s="33"/>
-      <c r="F558" s="33"/>
-    </row>
-    <row r="559" spans="2:6">
-      <c r="B559" s="33"/>
-      <c r="C559" s="33"/>
-      <c r="D559" s="33"/>
-      <c r="E559" s="33"/>
-      <c r="F559" s="33"/>
-    </row>
-    <row r="560" spans="2:6">
-      <c r="B560" s="33"/>
-      <c r="C560" s="33"/>
-      <c r="D560" s="33"/>
-      <c r="E560" s="33"/>
-      <c r="F560" s="33"/>
-    </row>
-    <row r="561" spans="2:6">
-      <c r="B561" s="33"/>
-      <c r="C561" s="33"/>
-      <c r="D561" s="33"/>
-      <c r="E561" s="33"/>
-      <c r="F561" s="33"/>
-    </row>
-    <row r="562" spans="2:6">
-      <c r="B562" s="33"/>
-      <c r="C562" s="33"/>
-      <c r="D562" s="33"/>
-      <c r="E562" s="33"/>
-      <c r="F562" s="33"/>
-    </row>
-    <row r="563" spans="2:6">
-      <c r="B563" s="33"/>
-      <c r="C563" s="33"/>
-      <c r="D563" s="33"/>
-      <c r="E563" s="33"/>
-      <c r="F563" s="33"/>
-    </row>
-    <row r="564" spans="2:6">
-      <c r="B564" s="33"/>
-      <c r="C564" s="33"/>
-      <c r="D564" s="33"/>
-      <c r="E564" s="33"/>
-      <c r="F564" s="33"/>
-    </row>
-    <row r="565" spans="2:6">
-      <c r="B565" s="33"/>
-      <c r="C565" s="33"/>
-      <c r="D565" s="33"/>
-      <c r="E565" s="33"/>
-      <c r="F565" s="33"/>
-    </row>
-    <row r="566" spans="2:6">
-      <c r="B566" s="33"/>
-      <c r="C566" s="33"/>
-      <c r="D566" s="33"/>
-      <c r="E566" s="33"/>
-      <c r="F566" s="33"/>
-    </row>
-    <row r="567" spans="2:6">
-      <c r="B567" s="33"/>
-      <c r="C567" s="33"/>
-      <c r="D567" s="33"/>
-      <c r="E567" s="33"/>
-      <c r="F567" s="33"/>
-    </row>
-    <row r="568" spans="2:6">
-      <c r="B568" s="33"/>
-      <c r="C568" s="33"/>
-      <c r="D568" s="33"/>
-      <c r="E568" s="33"/>
-      <c r="F568" s="33"/>
-    </row>
-    <row r="569" spans="2:6">
-      <c r="B569" s="33"/>
-      <c r="C569" s="33"/>
-      <c r="D569" s="33"/>
-      <c r="E569" s="33"/>
-      <c r="F569" s="33"/>
-    </row>
-    <row r="570" spans="2:6">
-      <c r="B570" s="33"/>
-      <c r="C570" s="33"/>
-      <c r="D570" s="33"/>
-      <c r="E570" s="33"/>
-      <c r="F570" s="33"/>
-    </row>
-    <row r="571" spans="2:6">
-      <c r="B571" s="33"/>
-      <c r="C571" s="33"/>
-      <c r="D571" s="33"/>
-      <c r="E571" s="33"/>
-      <c r="F571" s="33"/>
-    </row>
-    <row r="572" spans="2:6">
-      <c r="B572" s="33"/>
-      <c r="C572" s="33"/>
-      <c r="D572" s="33"/>
-      <c r="E572" s="33"/>
-      <c r="F572" s="33"/>
-    </row>
-    <row r="573" spans="2:6">
-      <c r="B573" s="33"/>
-      <c r="C573" s="33"/>
-      <c r="D573" s="33"/>
-      <c r="E573" s="33"/>
-      <c r="F573" s="33"/>
-    </row>
-    <row r="574" spans="2:6">
-      <c r="B574" s="33"/>
-      <c r="C574" s="33"/>
-      <c r="D574" s="33"/>
-      <c r="E574" s="33"/>
-      <c r="F574" s="33"/>
-    </row>
-    <row r="575" spans="2:6">
-      <c r="B575" s="33"/>
-      <c r="C575" s="33"/>
-      <c r="D575" s="33"/>
-      <c r="E575" s="33"/>
-      <c r="F575" s="33"/>
-    </row>
-    <row r="576" spans="2:6">
-      <c r="B576" s="33"/>
-      <c r="C576" s="33"/>
-      <c r="D576" s="33"/>
-      <c r="E576" s="33"/>
-      <c r="F576" s="33"/>
-    </row>
-    <row r="577" spans="2:6">
-      <c r="B577" s="33"/>
-      <c r="C577" s="33"/>
-      <c r="D577" s="33"/>
-      <c r="E577" s="33"/>
-      <c r="F577" s="33"/>
-    </row>
-    <row r="578" spans="2:6">
-      <c r="B578" s="33"/>
-      <c r="C578" s="33"/>
-      <c r="D578" s="33"/>
-      <c r="E578" s="33"/>
-      <c r="F578" s="33"/>
-    </row>
-    <row r="579" spans="2:6">
-      <c r="B579" s="33"/>
-      <c r="C579" s="33"/>
-      <c r="D579" s="33"/>
-      <c r="E579" s="33"/>
-      <c r="F579" s="33"/>
-    </row>
-    <row r="580" spans="2:6">
-      <c r="B580" s="33"/>
-      <c r="C580" s="33"/>
-      <c r="D580" s="33"/>
-      <c r="E580" s="33"/>
-      <c r="F580" s="33"/>
-    </row>
-    <row r="581" spans="2:6">
-      <c r="B581" s="33"/>
-      <c r="C581" s="33"/>
-      <c r="D581" s="33"/>
-      <c r="E581" s="33"/>
-      <c r="F581" s="33"/>
-    </row>
-    <row r="582" spans="2:6">
-      <c r="B582" s="33"/>
-      <c r="C582" s="33"/>
-      <c r="D582" s="33"/>
-      <c r="E582" s="33"/>
-      <c r="F582" s="33"/>
-    </row>
-    <row r="583" spans="2:6">
-      <c r="B583" s="33"/>
-      <c r="C583" s="33"/>
-      <c r="D583" s="33"/>
-      <c r="E583" s="33"/>
-      <c r="F583" s="33"/>
-    </row>
-    <row r="584" spans="2:6">
-      <c r="B584" s="33"/>
-      <c r="C584" s="33"/>
-      <c r="D584" s="33"/>
-      <c r="E584" s="33"/>
-      <c r="F584" s="33"/>
-    </row>
-    <row r="585" spans="2:6">
-      <c r="B585" s="33"/>
-      <c r="C585" s="33"/>
-      <c r="D585" s="33"/>
-      <c r="E585" s="33"/>
-      <c r="F585" s="33"/>
-    </row>
-    <row r="586" spans="2:6">
-      <c r="B586" s="33"/>
-      <c r="C586" s="33"/>
-      <c r="D586" s="33"/>
-      <c r="E586" s="33"/>
-      <c r="F586" s="33"/>
-    </row>
-    <row r="587" spans="2:6">
-      <c r="B587" s="33"/>
-      <c r="C587" s="33"/>
-      <c r="D587" s="33"/>
-      <c r="E587" s="33"/>
-      <c r="F587" s="33"/>
-    </row>
-    <row r="588" spans="2:6">
-      <c r="B588" s="33"/>
-      <c r="C588" s="33"/>
-      <c r="D588" s="33"/>
-      <c r="E588" s="33"/>
-      <c r="F588" s="33"/>
-    </row>
-    <row r="589" spans="2:6">
-      <c r="B589" s="33"/>
-      <c r="C589" s="33"/>
-      <c r="D589" s="33"/>
-      <c r="E589" s="33"/>
-      <c r="F589" s="33"/>
-    </row>
-    <row r="590" spans="2:6">
-      <c r="B590" s="33"/>
-      <c r="C590" s="33"/>
-      <c r="D590" s="33"/>
-      <c r="E590" s="33"/>
-      <c r="F590" s="33"/>
-    </row>
-    <row r="591" spans="2:6">
-      <c r="B591" s="33"/>
-      <c r="C591" s="33"/>
-      <c r="D591" s="33"/>
-      <c r="E591" s="33"/>
-      <c r="F591" s="33"/>
-    </row>
-    <row r="592" spans="2:6">
-      <c r="B592" s="33"/>
-      <c r="C592" s="33"/>
-      <c r="D592" s="33"/>
-      <c r="E592" s="33"/>
-      <c r="F592" s="33"/>
-    </row>
-    <row r="593" spans="2:6">
-      <c r="B593" s="33"/>
-      <c r="C593" s="33"/>
-      <c r="D593" s="33"/>
-      <c r="E593" s="33"/>
-      <c r="F593" s="33"/>
-    </row>
-    <row r="594" spans="2:6">
-      <c r="B594" s="33"/>
-      <c r="C594" s="33"/>
-      <c r="D594" s="33"/>
-      <c r="E594" s="33"/>
-      <c r="F594" s="33"/>
-    </row>
-    <row r="595" spans="2:6">
-      <c r="B595" s="33"/>
-      <c r="C595" s="33"/>
-      <c r="D595" s="33"/>
-      <c r="E595" s="33"/>
-      <c r="F595" s="33"/>
-    </row>
-    <row r="596" spans="2:6">
-      <c r="B596" s="33"/>
-      <c r="C596" s="33"/>
-      <c r="D596" s="33"/>
-      <c r="E596" s="33"/>
-      <c r="F596" s="33"/>
-    </row>
-    <row r="597" spans="2:6">
-      <c r="B597" s="33"/>
-      <c r="C597" s="33"/>
-      <c r="D597" s="33"/>
-      <c r="E597" s="33"/>
-      <c r="F597" s="33"/>
-    </row>
-    <row r="598" spans="2:6">
-      <c r="B598" s="33"/>
-      <c r="C598" s="33"/>
-      <c r="D598" s="33"/>
-      <c r="E598" s="33"/>
-      <c r="F598" s="33"/>
-    </row>
-    <row r="599" spans="2:6">
-      <c r="B599" s="33"/>
-      <c r="C599" s="33"/>
-      <c r="D599" s="33"/>
-      <c r="E599" s="33"/>
-      <c r="F599" s="33"/>
-    </row>
-    <row r="600" spans="2:6">
-      <c r="B600" s="33"/>
-      <c r="C600" s="33"/>
-      <c r="D600" s="33"/>
-      <c r="E600" s="33"/>
-      <c r="F600" s="33"/>
-    </row>
+    <row r="113" s="33" customFormat="1"/>
+    <row r="114" s="33" customFormat="1"/>
+    <row r="115" s="33" customFormat="1"/>
+    <row r="116" s="33" customFormat="1"/>
+    <row r="117" s="33" customFormat="1"/>
+    <row r="118" s="33" customFormat="1"/>
+    <row r="119" s="33" customFormat="1"/>
+    <row r="120" s="33" customFormat="1"/>
+    <row r="121" s="33" customFormat="1"/>
+    <row r="122" s="33" customFormat="1"/>
+    <row r="123" s="33" customFormat="1"/>
+    <row r="124" s="33" customFormat="1"/>
+    <row r="125" s="33" customFormat="1"/>
+    <row r="126" s="33" customFormat="1"/>
+    <row r="127" s="33" customFormat="1"/>
+    <row r="128" s="33" customFormat="1"/>
+    <row r="129" s="33" customFormat="1"/>
+    <row r="130" s="33" customFormat="1"/>
+    <row r="131" s="33" customFormat="1"/>
+    <row r="132" s="33" customFormat="1"/>
+    <row r="133" s="33" customFormat="1"/>
+    <row r="134" s="33" customFormat="1"/>
+    <row r="135" s="33" customFormat="1"/>
+    <row r="136" s="33" customFormat="1"/>
+    <row r="137" s="33" customFormat="1"/>
+    <row r="138" s="33" customFormat="1"/>
+    <row r="139" s="33" customFormat="1"/>
+    <row r="140" s="33" customFormat="1"/>
+    <row r="141" s="33" customFormat="1"/>
+    <row r="142" s="33" customFormat="1"/>
+    <row r="143" s="33" customFormat="1"/>
+    <row r="144" s="33" customFormat="1"/>
+    <row r="145" s="33" customFormat="1"/>
+    <row r="146" s="33" customFormat="1"/>
+    <row r="147" s="33" customFormat="1"/>
+    <row r="148" s="33" customFormat="1"/>
+    <row r="149" s="33" customFormat="1"/>
+    <row r="150" s="33" customFormat="1"/>
+    <row r="151" s="33" customFormat="1"/>
+    <row r="152" s="33" customFormat="1"/>
+    <row r="153" s="33" customFormat="1"/>
+    <row r="154" s="33" customFormat="1"/>
+    <row r="155" s="33" customFormat="1"/>
+    <row r="156" s="33" customFormat="1"/>
+    <row r="157" s="33" customFormat="1"/>
+    <row r="158" s="33" customFormat="1"/>
+    <row r="159" s="33" customFormat="1"/>
+    <row r="160" s="33" customFormat="1"/>
+    <row r="161" s="33" customFormat="1"/>
+    <row r="162" s="33" customFormat="1"/>
+    <row r="163" s="33" customFormat="1"/>
+    <row r="164" s="33" customFormat="1"/>
+    <row r="165" s="33" customFormat="1"/>
+    <row r="166" s="33" customFormat="1"/>
+    <row r="167" s="33" customFormat="1"/>
+    <row r="168" s="33" customFormat="1"/>
+    <row r="169" s="33" customFormat="1"/>
+    <row r="170" s="33" customFormat="1"/>
+    <row r="171" s="33" customFormat="1"/>
+    <row r="172" s="33" customFormat="1"/>
+    <row r="173" s="33" customFormat="1"/>
+    <row r="174" s="33" customFormat="1"/>
+    <row r="175" s="33" customFormat="1"/>
+    <row r="176" s="33" customFormat="1"/>
+    <row r="177" s="33" customFormat="1"/>
+    <row r="178" s="33" customFormat="1"/>
+    <row r="179" s="33" customFormat="1"/>
+    <row r="180" s="33" customFormat="1"/>
+    <row r="181" s="33" customFormat="1"/>
+    <row r="182" s="33" customFormat="1"/>
+    <row r="183" s="33" customFormat="1"/>
+    <row r="184" s="33" customFormat="1"/>
+    <row r="185" s="33" customFormat="1"/>
+    <row r="186" s="33" customFormat="1"/>
+    <row r="187" s="33" customFormat="1"/>
+    <row r="188" s="33" customFormat="1"/>
+    <row r="189" s="33" customFormat="1"/>
+    <row r="190" s="33" customFormat="1"/>
+    <row r="191" s="33" customFormat="1"/>
+    <row r="192" s="33" customFormat="1"/>
+    <row r="193" s="33" customFormat="1"/>
+    <row r="194" s="33" customFormat="1"/>
+    <row r="195" s="33" customFormat="1"/>
+    <row r="196" s="33" customFormat="1"/>
+    <row r="197" s="33" customFormat="1"/>
+    <row r="198" s="33" customFormat="1"/>
+    <row r="199" s="33" customFormat="1"/>
+    <row r="200" s="33" customFormat="1"/>
+    <row r="201" s="33" customFormat="1"/>
+    <row r="202" s="33" customFormat="1"/>
+    <row r="203" s="33" customFormat="1"/>
+    <row r="204" s="33" customFormat="1"/>
+    <row r="205" s="33" customFormat="1"/>
+    <row r="206" s="33" customFormat="1"/>
+    <row r="207" s="33" customFormat="1"/>
+    <row r="208" s="33" customFormat="1"/>
+    <row r="209" s="33" customFormat="1"/>
+    <row r="210" s="33" customFormat="1"/>
+    <row r="211" s="33" customFormat="1"/>
+    <row r="212" s="33" customFormat="1"/>
+    <row r="213" s="33" customFormat="1"/>
+    <row r="214" s="33" customFormat="1"/>
+    <row r="215" s="33" customFormat="1"/>
+    <row r="216" s="33" customFormat="1"/>
+    <row r="217" s="33" customFormat="1"/>
+    <row r="218" s="33" customFormat="1"/>
+    <row r="219" s="33" customFormat="1"/>
+    <row r="220" s="33" customFormat="1"/>
+    <row r="221" s="33" customFormat="1"/>
+    <row r="222" s="33" customFormat="1"/>
+    <row r="223" s="33" customFormat="1"/>
+    <row r="224" s="33" customFormat="1"/>
+    <row r="225" s="33" customFormat="1"/>
+    <row r="226" s="33" customFormat="1"/>
+    <row r="227" s="33" customFormat="1"/>
+    <row r="228" s="33" customFormat="1"/>
+    <row r="229" s="33" customFormat="1"/>
+    <row r="230" s="33" customFormat="1"/>
+    <row r="231" s="33" customFormat="1"/>
+    <row r="232" s="33" customFormat="1"/>
+    <row r="233" s="33" customFormat="1"/>
+    <row r="234" s="33" customFormat="1"/>
+    <row r="235" s="33" customFormat="1"/>
+    <row r="236" s="33" customFormat="1"/>
+    <row r="237" s="33" customFormat="1"/>
+    <row r="238" s="33" customFormat="1"/>
+    <row r="239" s="33" customFormat="1"/>
+    <row r="240" s="33" customFormat="1"/>
+    <row r="241" s="33" customFormat="1"/>
+    <row r="242" s="33" customFormat="1"/>
+    <row r="243" s="33" customFormat="1"/>
+    <row r="244" s="33" customFormat="1"/>
+    <row r="245" s="33" customFormat="1"/>
+    <row r="246" s="33" customFormat="1"/>
+    <row r="247" s="33" customFormat="1"/>
+    <row r="248" s="33" customFormat="1"/>
+    <row r="249" s="33" customFormat="1"/>
+    <row r="250" s="33" customFormat="1"/>
+    <row r="251" s="33" customFormat="1"/>
+    <row r="252" s="33" customFormat="1"/>
+    <row r="253" s="33" customFormat="1"/>
+    <row r="254" s="33" customFormat="1"/>
+    <row r="255" s="33" customFormat="1"/>
+    <row r="256" s="33" customFormat="1"/>
+    <row r="257" s="33" customFormat="1"/>
+    <row r="258" s="33" customFormat="1"/>
+    <row r="259" s="33" customFormat="1"/>
+    <row r="260" s="33" customFormat="1"/>
+    <row r="261" s="33" customFormat="1"/>
+    <row r="262" s="33" customFormat="1"/>
+    <row r="263" s="33" customFormat="1"/>
+    <row r="264" s="33" customFormat="1"/>
+    <row r="265" s="33" customFormat="1"/>
+    <row r="266" s="33" customFormat="1"/>
+    <row r="267" s="33" customFormat="1"/>
+    <row r="268" s="33" customFormat="1"/>
+    <row r="269" s="33" customFormat="1"/>
+    <row r="270" s="33" customFormat="1"/>
+    <row r="271" s="33" customFormat="1"/>
+    <row r="272" s="33" customFormat="1"/>
+    <row r="273" s="33" customFormat="1"/>
+    <row r="274" s="33" customFormat="1"/>
+    <row r="275" s="33" customFormat="1"/>
+    <row r="276" s="33" customFormat="1"/>
+    <row r="277" s="33" customFormat="1"/>
+    <row r="278" s="33" customFormat="1"/>
+    <row r="279" s="33" customFormat="1"/>
+    <row r="280" s="33" customFormat="1"/>
+    <row r="281" s="33" customFormat="1"/>
+    <row r="282" s="33" customFormat="1"/>
+    <row r="283" s="33" customFormat="1"/>
+    <row r="284" s="33" customFormat="1"/>
+    <row r="285" s="33" customFormat="1"/>
+    <row r="286" s="33" customFormat="1"/>
+    <row r="287" s="33" customFormat="1"/>
+    <row r="288" s="33" customFormat="1"/>
+    <row r="289" s="33" customFormat="1"/>
+    <row r="290" s="33" customFormat="1"/>
+    <row r="291" s="33" customFormat="1"/>
+    <row r="292" s="33" customFormat="1"/>
+    <row r="293" s="33" customFormat="1"/>
+    <row r="294" s="33" customFormat="1"/>
+    <row r="295" s="33" customFormat="1"/>
+    <row r="296" s="33" customFormat="1"/>
+    <row r="297" s="33" customFormat="1"/>
+    <row r="298" s="33" customFormat="1"/>
+    <row r="299" s="33" customFormat="1"/>
+    <row r="300" s="33" customFormat="1"/>
+    <row r="301" s="33" customFormat="1"/>
+    <row r="302" s="33" customFormat="1"/>
+    <row r="303" s="33" customFormat="1"/>
+    <row r="304" s="33" customFormat="1"/>
+    <row r="305" s="33" customFormat="1"/>
+    <row r="306" s="33" customFormat="1"/>
+    <row r="307" s="33" customFormat="1"/>
+    <row r="308" s="33" customFormat="1"/>
+    <row r="309" s="33" customFormat="1"/>
+    <row r="310" s="33" customFormat="1"/>
+    <row r="311" s="33" customFormat="1"/>
+    <row r="312" s="33" customFormat="1"/>
+    <row r="313" s="33" customFormat="1"/>
+    <row r="314" s="33" customFormat="1"/>
+    <row r="315" s="33" customFormat="1"/>
+    <row r="316" s="33" customFormat="1"/>
+    <row r="317" s="33" customFormat="1"/>
+    <row r="318" s="33" customFormat="1"/>
+    <row r="319" s="33" customFormat="1"/>
+    <row r="320" s="33" customFormat="1"/>
+    <row r="321" s="33" customFormat="1"/>
+    <row r="322" s="33" customFormat="1"/>
+    <row r="323" s="33" customFormat="1"/>
+    <row r="324" s="33" customFormat="1"/>
+    <row r="325" s="33" customFormat="1"/>
+    <row r="326" s="33" customFormat="1"/>
+    <row r="327" s="33" customFormat="1"/>
+    <row r="328" s="33" customFormat="1"/>
+    <row r="329" s="33" customFormat="1"/>
+    <row r="330" s="33" customFormat="1"/>
+    <row r="331" s="33" customFormat="1"/>
+    <row r="332" s="33" customFormat="1"/>
+    <row r="333" s="33" customFormat="1"/>
+    <row r="334" s="33" customFormat="1"/>
+    <row r="335" s="33" customFormat="1"/>
+    <row r="336" s="33" customFormat="1"/>
+    <row r="337" s="33" customFormat="1"/>
+    <row r="338" s="33" customFormat="1"/>
+    <row r="339" s="33" customFormat="1"/>
+    <row r="340" s="33" customFormat="1"/>
+    <row r="341" s="33" customFormat="1"/>
+    <row r="342" s="33" customFormat="1"/>
+    <row r="343" s="33" customFormat="1"/>
+    <row r="344" s="33" customFormat="1"/>
+    <row r="345" s="33" customFormat="1"/>
+    <row r="346" s="33" customFormat="1"/>
+    <row r="347" s="33" customFormat="1"/>
+    <row r="348" s="33" customFormat="1"/>
+    <row r="349" s="33" customFormat="1"/>
+    <row r="350" s="33" customFormat="1"/>
+    <row r="351" s="33" customFormat="1"/>
+    <row r="352" s="33" customFormat="1"/>
+    <row r="353" s="33" customFormat="1"/>
+    <row r="354" s="33" customFormat="1"/>
+    <row r="355" s="33" customFormat="1"/>
+    <row r="356" s="33" customFormat="1"/>
+    <row r="357" s="33" customFormat="1"/>
+    <row r="358" s="33" customFormat="1"/>
+    <row r="359" s="33" customFormat="1"/>
+    <row r="360" s="33" customFormat="1"/>
+    <row r="361" s="33" customFormat="1"/>
+    <row r="362" s="33" customFormat="1"/>
+    <row r="363" s="33" customFormat="1"/>
+    <row r="364" s="33" customFormat="1"/>
+    <row r="365" s="33" customFormat="1"/>
+    <row r="366" s="33" customFormat="1"/>
+    <row r="367" s="33" customFormat="1"/>
+    <row r="368" s="33" customFormat="1"/>
+    <row r="369" s="33" customFormat="1"/>
+    <row r="370" s="33" customFormat="1"/>
+    <row r="371" s="33" customFormat="1"/>
+    <row r="372" s="33" customFormat="1"/>
+    <row r="373" s="33" customFormat="1"/>
+    <row r="374" s="33" customFormat="1"/>
+    <row r="375" s="33" customFormat="1"/>
+    <row r="376" s="33" customFormat="1"/>
+    <row r="377" s="33" customFormat="1"/>
+    <row r="378" s="33" customFormat="1"/>
+    <row r="379" s="33" customFormat="1"/>
+    <row r="380" s="33" customFormat="1"/>
+    <row r="381" s="33" customFormat="1"/>
+    <row r="382" s="33" customFormat="1"/>
+    <row r="383" s="33" customFormat="1"/>
+    <row r="384" s="33" customFormat="1"/>
+    <row r="385" s="33" customFormat="1"/>
+    <row r="386" s="33" customFormat="1"/>
+    <row r="387" s="33" customFormat="1"/>
+    <row r="388" s="33" customFormat="1"/>
+    <row r="389" s="33" customFormat="1"/>
+    <row r="390" s="33" customFormat="1"/>
+    <row r="391" s="33" customFormat="1"/>
+    <row r="392" s="33" customFormat="1"/>
+    <row r="393" s="33" customFormat="1"/>
+    <row r="394" s="33" customFormat="1"/>
+    <row r="395" s="33" customFormat="1"/>
+    <row r="396" s="33" customFormat="1"/>
+    <row r="397" s="33" customFormat="1"/>
+    <row r="398" s="33" customFormat="1"/>
+    <row r="399" s="33" customFormat="1"/>
+    <row r="400" s="33" customFormat="1"/>
+    <row r="401" s="33" customFormat="1"/>
+    <row r="402" s="33" customFormat="1"/>
+    <row r="403" s="33" customFormat="1"/>
+    <row r="404" s="33" customFormat="1"/>
+    <row r="405" s="33" customFormat="1"/>
+    <row r="406" s="33" customFormat="1"/>
+    <row r="407" s="33" customFormat="1"/>
+    <row r="408" s="33" customFormat="1"/>
+    <row r="409" s="33" customFormat="1"/>
+    <row r="410" s="33" customFormat="1"/>
+    <row r="411" s="33" customFormat="1"/>
+    <row r="412" s="33" customFormat="1"/>
+    <row r="413" s="33" customFormat="1"/>
+    <row r="414" s="33" customFormat="1"/>
+    <row r="415" s="33" customFormat="1"/>
+    <row r="416" s="33" customFormat="1"/>
+    <row r="417" s="33" customFormat="1"/>
+    <row r="418" s="33" customFormat="1"/>
+    <row r="419" s="33" customFormat="1"/>
+    <row r="420" s="33" customFormat="1"/>
+    <row r="421" s="33" customFormat="1"/>
+    <row r="422" s="33" customFormat="1"/>
+    <row r="423" s="33" customFormat="1"/>
+    <row r="424" s="33" customFormat="1"/>
+    <row r="425" s="33" customFormat="1"/>
+    <row r="426" s="33" customFormat="1"/>
+    <row r="427" s="33" customFormat="1"/>
+    <row r="428" s="33" customFormat="1"/>
+    <row r="429" s="33" customFormat="1"/>
+    <row r="430" s="33" customFormat="1"/>
+    <row r="431" s="33" customFormat="1"/>
+    <row r="432" s="33" customFormat="1"/>
+    <row r="433" s="33" customFormat="1"/>
+    <row r="434" s="33" customFormat="1"/>
+    <row r="435" s="33" customFormat="1"/>
+    <row r="436" s="33" customFormat="1"/>
+    <row r="437" s="33" customFormat="1"/>
+    <row r="438" s="33" customFormat="1"/>
+    <row r="439" s="33" customFormat="1"/>
+    <row r="440" s="33" customFormat="1"/>
+    <row r="441" s="33" customFormat="1"/>
+    <row r="442" s="33" customFormat="1"/>
+    <row r="443" s="33" customFormat="1"/>
+    <row r="444" s="33" customFormat="1"/>
+    <row r="445" s="33" customFormat="1"/>
+    <row r="446" s="33" customFormat="1"/>
+    <row r="447" s="33" customFormat="1"/>
+    <row r="448" s="33" customFormat="1"/>
+    <row r="449" s="33" customFormat="1"/>
+    <row r="450" s="33" customFormat="1"/>
+    <row r="451" s="33" customFormat="1"/>
+    <row r="452" s="33" customFormat="1"/>
+    <row r="453" s="33" customFormat="1"/>
+    <row r="454" s="33" customFormat="1"/>
+    <row r="455" s="33" customFormat="1"/>
+    <row r="456" s="33" customFormat="1"/>
+    <row r="457" s="33" customFormat="1"/>
+    <row r="458" s="33" customFormat="1"/>
+    <row r="459" s="33" customFormat="1"/>
+    <row r="460" s="33" customFormat="1"/>
+    <row r="461" s="33" customFormat="1"/>
+    <row r="462" s="33" customFormat="1"/>
+    <row r="463" s="33" customFormat="1"/>
+    <row r="464" s="33" customFormat="1"/>
+    <row r="465" s="33" customFormat="1"/>
+    <row r="466" s="33" customFormat="1"/>
+    <row r="467" s="33" customFormat="1"/>
+    <row r="468" s="33" customFormat="1"/>
+    <row r="469" s="33" customFormat="1"/>
+    <row r="470" s="33" customFormat="1"/>
+    <row r="471" s="33" customFormat="1"/>
+    <row r="472" s="33" customFormat="1"/>
+    <row r="473" s="33" customFormat="1"/>
+    <row r="474" s="33" customFormat="1"/>
+    <row r="475" s="33" customFormat="1"/>
+    <row r="476" s="33" customFormat="1"/>
+    <row r="477" s="33" customFormat="1"/>
+    <row r="478" s="33" customFormat="1"/>
+    <row r="479" s="33" customFormat="1"/>
+    <row r="480" s="33" customFormat="1"/>
+    <row r="481" s="33" customFormat="1"/>
+    <row r="482" s="33" customFormat="1"/>
+    <row r="483" s="33" customFormat="1"/>
+    <row r="484" s="33" customFormat="1"/>
+    <row r="485" s="33" customFormat="1"/>
+    <row r="486" s="33" customFormat="1"/>
+    <row r="487" s="33" customFormat="1"/>
+    <row r="488" s="33" customFormat="1"/>
+    <row r="489" s="33" customFormat="1"/>
+    <row r="490" s="33" customFormat="1"/>
+    <row r="491" s="33" customFormat="1"/>
+    <row r="492" s="33" customFormat="1"/>
+    <row r="493" s="33" customFormat="1"/>
+    <row r="494" s="33" customFormat="1"/>
+    <row r="495" s="33" customFormat="1"/>
+    <row r="496" s="33" customFormat="1"/>
+    <row r="497" s="33" customFormat="1"/>
+    <row r="498" s="33" customFormat="1"/>
+    <row r="499" s="33" customFormat="1"/>
+    <row r="500" s="33" customFormat="1"/>
+    <row r="501" s="33" customFormat="1"/>
+    <row r="502" s="33" customFormat="1"/>
+    <row r="503" s="33" customFormat="1"/>
+    <row r="504" s="33" customFormat="1"/>
+    <row r="505" s="33" customFormat="1"/>
+    <row r="506" s="33" customFormat="1"/>
+    <row r="507" s="33" customFormat="1"/>
+    <row r="508" s="33" customFormat="1"/>
+    <row r="509" s="33" customFormat="1"/>
+    <row r="510" s="33" customFormat="1"/>
+    <row r="511" s="33" customFormat="1"/>
+    <row r="512" s="33" customFormat="1"/>
+    <row r="513" s="33" customFormat="1"/>
+    <row r="514" s="33" customFormat="1"/>
+    <row r="515" s="33" customFormat="1"/>
+    <row r="516" s="33" customFormat="1"/>
+    <row r="517" s="33" customFormat="1"/>
+    <row r="518" s="33" customFormat="1"/>
+    <row r="519" s="33" customFormat="1"/>
+    <row r="520" s="33" customFormat="1"/>
+    <row r="521" s="33" customFormat="1"/>
+    <row r="522" s="33" customFormat="1"/>
+    <row r="523" s="33" customFormat="1"/>
+    <row r="524" s="33" customFormat="1"/>
+    <row r="525" s="33" customFormat="1"/>
+    <row r="526" s="33" customFormat="1"/>
+    <row r="527" s="33" customFormat="1"/>
+    <row r="528" s="33" customFormat="1"/>
+    <row r="529" s="33" customFormat="1"/>
+    <row r="530" s="33" customFormat="1"/>
+    <row r="531" s="33" customFormat="1"/>
+    <row r="532" s="33" customFormat="1"/>
+    <row r="533" s="33" customFormat="1"/>
+    <row r="534" s="33" customFormat="1"/>
+    <row r="535" s="33" customFormat="1"/>
+    <row r="536" s="33" customFormat="1"/>
+    <row r="537" s="33" customFormat="1"/>
+    <row r="538" s="33" customFormat="1"/>
+    <row r="539" s="33" customFormat="1"/>
+    <row r="540" s="33" customFormat="1"/>
+    <row r="541" s="33" customFormat="1"/>
+    <row r="542" s="33" customFormat="1"/>
+    <row r="543" s="33" customFormat="1"/>
+    <row r="544" s="33" customFormat="1"/>
+    <row r="545" s="33" customFormat="1"/>
+    <row r="546" s="33" customFormat="1"/>
+    <row r="547" s="33" customFormat="1"/>
+    <row r="548" s="33" customFormat="1"/>
+    <row r="549" s="33" customFormat="1"/>
+    <row r="550" s="33" customFormat="1"/>
+    <row r="551" s="33" customFormat="1"/>
+    <row r="552" s="33" customFormat="1"/>
+    <row r="553" s="33" customFormat="1"/>
+    <row r="554" s="33" customFormat="1"/>
+    <row r="555" s="33" customFormat="1"/>
+    <row r="556" s="33" customFormat="1"/>
+    <row r="557" s="33" customFormat="1"/>
+    <row r="558" s="33" customFormat="1"/>
+    <row r="559" s="33" customFormat="1"/>
+    <row r="560" s="33" customFormat="1"/>
+    <row r="561" s="33" customFormat="1"/>
+    <row r="562" s="33" customFormat="1"/>
+    <row r="563" s="33" customFormat="1"/>
+    <row r="564" s="33" customFormat="1"/>
+    <row r="565" s="33" customFormat="1"/>
+    <row r="566" s="33" customFormat="1"/>
+    <row r="567" s="33" customFormat="1"/>
+    <row r="568" s="33" customFormat="1"/>
+    <row r="569" s="33" customFormat="1"/>
+    <row r="570" s="33" customFormat="1"/>
+    <row r="571" s="33" customFormat="1"/>
+    <row r="572" s="33" customFormat="1"/>
+    <row r="573" s="33" customFormat="1"/>
+    <row r="574" s="33" customFormat="1"/>
+    <row r="575" s="33" customFormat="1"/>
+    <row r="576" s="33" customFormat="1"/>
+    <row r="577" s="33" customFormat="1"/>
+    <row r="578" s="33" customFormat="1"/>
+    <row r="579" s="33" customFormat="1"/>
+    <row r="580" s="33" customFormat="1"/>
+    <row r="581" s="33" customFormat="1"/>
+    <row r="582" s="33" customFormat="1"/>
+    <row r="583" s="33" customFormat="1"/>
+    <row r="584" s="33" customFormat="1"/>
+    <row r="585" s="33" customFormat="1"/>
+    <row r="586" s="33" customFormat="1"/>
+    <row r="587" s="33" customFormat="1"/>
+    <row r="588" s="33" customFormat="1"/>
+    <row r="589" s="33" customFormat="1"/>
+    <row r="590" s="33" customFormat="1"/>
+    <row r="591" s="33" customFormat="1"/>
+    <row r="592" s="33" customFormat="1"/>
+    <row r="593" s="33" customFormat="1"/>
+    <row r="594" s="33" customFormat="1"/>
+    <row r="595" s="33" customFormat="1"/>
+    <row r="596" s="33" customFormat="1"/>
+    <row r="597" s="33" customFormat="1"/>
+    <row r="598" s="33" customFormat="1"/>
+    <row r="599" s="33" customFormat="1"/>
+    <row r="600" s="33" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -11948,7 +9017,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="17" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -12013,7 +9082,7 @@
         <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -12024,7 +9093,7 @@
         <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -12035,7 +9104,7 @@
         <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -12043,10 +9112,10 @@
         <v>85</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C14" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -12156,128 +9225,128 @@
         <v>62</v>
       </c>
       <c r="C24" t="s">
-        <v>109</v>
+        <v>293</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>62</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>294</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>62</v>
       </c>
       <c r="C26" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="9" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>62</v>
       </c>
       <c r="C27" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>62</v>
       </c>
       <c r="C28" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>62</v>
       </c>
       <c r="C29" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>62</v>
       </c>
       <c r="C30" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>62</v>
       </c>
       <c r="C31" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="9" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>62</v>
       </c>
       <c r="C32" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>62</v>
       </c>
       <c r="C33" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="9" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>62</v>
       </c>
       <c r="C34" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>62</v>
       </c>
       <c r="C35" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -12312,7 +9381,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="17" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -12371,7 +9440,7 @@
         <v>69</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -12379,10 +9448,10 @@
         <v>81</v>
       </c>
       <c r="B12" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -12390,10 +9459,10 @@
         <v>81</v>
       </c>
       <c r="B13" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -12412,10 +9481,10 @@
         <v>85</v>
       </c>
       <c r="B15" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -12423,10 +9492,10 @@
         <v>85</v>
       </c>
       <c r="B16" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -12445,10 +9514,10 @@
         <v>90</v>
       </c>
       <c r="B18" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -12456,10 +9525,10 @@
         <v>90</v>
       </c>
       <c r="B19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C19" s="39" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -12467,10 +9536,10 @@
         <v>90</v>
       </c>
       <c r="B20" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C20" s="39" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -12478,43 +9547,43 @@
         <v>90</v>
       </c>
       <c r="B21" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C21" s="39" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1">
       <c r="A22" s="9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B22" t="s">
         <v>69</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B23" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C23" s="39" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B24" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C24" s="39" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -12522,10 +9591,10 @@
         <v>107</v>
       </c>
       <c r="B25" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C25" s="39" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -12533,10 +9602,10 @@
         <v>97</v>
       </c>
       <c r="B26" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C26" s="39" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -12544,10 +9613,10 @@
         <v>99</v>
       </c>
       <c r="B27" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C27" s="39" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -12555,10 +9624,10 @@
         <v>100</v>
       </c>
       <c r="B28" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C28" s="39" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -12566,10 +9635,10 @@
         <v>101</v>
       </c>
       <c r="B29" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C29" s="39" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -12577,10 +9646,10 @@
         <v>102</v>
       </c>
       <c r="B30" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C30" s="39" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -12588,10 +9657,10 @@
         <v>103</v>
       </c>
       <c r="B31" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C31" s="39" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -12599,10 +9668,10 @@
         <v>104</v>
       </c>
       <c r="B32" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C32" s="39" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -12610,10 +9679,10 @@
         <v>105</v>
       </c>
       <c r="B33" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C33" s="39" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -12621,10 +9690,10 @@
         <v>97</v>
       </c>
       <c r="B34" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C34" s="39" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -12632,10 +9701,10 @@
         <v>99</v>
       </c>
       <c r="B35" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C35" s="39" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -12643,10 +9712,10 @@
         <v>100</v>
       </c>
       <c r="B36" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C36" s="39" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -12654,10 +9723,10 @@
         <v>101</v>
       </c>
       <c r="B37" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C37" s="39" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -12665,10 +9734,10 @@
         <v>102</v>
       </c>
       <c r="B38" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C38" s="39" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -12676,10 +9745,10 @@
         <v>103</v>
       </c>
       <c r="B39" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C39" s="39" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -12687,10 +9756,10 @@
         <v>104</v>
       </c>
       <c r="B40" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C40" s="39" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -12698,10 +9767,10 @@
         <v>105</v>
       </c>
       <c r="B41" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C41" s="39" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -12769,7 +9838,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="17" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -12867,7 +9936,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="17" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -12921,13 +9990,13 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="B11" t="s">
+        <v>219</v>
+      </c>
+      <c r="C11" s="39" t="s">
         <v>220</v>
-      </c>
-      <c r="B11" t="s">
-        <v>221</v>
-      </c>
-      <c r="C11" s="39" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -12981,7 +10050,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="17" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="4"/>
@@ -13019,35 +10088,35 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
+        <v>262</v>
+      </c>
+      <c r="C9" t="s">
+        <v>265</v>
+      </c>
+      <c r="D9" t="s">
         <v>264</v>
-      </c>
-      <c r="C9" t="s">
-        <v>267</v>
-      </c>
-      <c r="D9" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
+        <v>263</v>
+      </c>
+      <c r="C10" t="s">
         <v>265</v>
       </c>
-      <c r="C10" t="s">
-        <v>267</v>
-      </c>
       <c r="D10" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C11" t="s">
         <v>69</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Amstrad CPC 664/MC0005A/Data CPC 664 MC0005A.xlsx
+++ b/Assets/Data/Amstrad CPC 664/MC0005A/Data CPC 664 MC0005A.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbewe\AppData\Local\Classic-Repair-Toolbox\Data\Amstrad CPC 664\MC0005A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dennis\AppData\Local\Classic-Repair-Toolbox\Data\Amstrad CPC 664\MC0005A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31483DDF-384B-42F0-A9B3-0EB6C6A29365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF674B62-E010-443A-9B44-BEF4413D00A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Board schematics" sheetId="5" r:id="rId1"/>
@@ -22,10 +22,9 @@
     <sheet name="Board local files" sheetId="9" r:id="rId7"/>
     <sheet name="Board links" sheetId="10" r:id="rId8"/>
     <sheet name="Credits" sheetId="13" r:id="rId9"/>
-    <sheet name="Version match" sheetId="14" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Component images'!$A$8:$G$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Component images'!$A$8:$J$82</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="296">
   <si>
     <t>Name</t>
   </si>
@@ -197,15 +196,6 @@
   </si>
   <si>
     <t>Part-number</t>
-  </si>
-  <si>
-    <t>CRT version(s) where this Excel will work</t>
-  </si>
-  <si>
-    <t>Version</t>
-  </si>
-  <si>
-    <t>2026-February-21</t>
   </si>
   <si>
     <t># Hardware: Amstrad CPC 664</t>
@@ -1010,6 +1000,15 @@
     <t>Commodore shared files/Component local files/74LS373.PDF</t>
   </si>
   <si>
+    <t>T/DIV</t>
+  </si>
+  <si>
+    <t>V/DIV</t>
+  </si>
+  <si>
+    <t>T.LVL</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve"># Revision date: </t>
     </r>
@@ -1022,7 +1021,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>2026-March-26</t>
+      <t>2026-March-30</t>
     </r>
   </si>
 </sst>
@@ -1158,7 +1157,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1316,6 +1315,9 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1336,9 +1338,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1376,7 +1378,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1482,7 +1484,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1624,7 +1626,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1634,24 +1636,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBB56770-8233-4B8D-A81F-EDDC9713B054}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:F33"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="38.7109375" style="27" customWidth="1"/>
+    <col min="1" max="1" width="38.6640625" style="27" customWidth="1"/>
     <col min="2" max="2" width="89" style="33" customWidth="1"/>
     <col min="3" max="4" width="14" style="33" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" style="33" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" style="33" customWidth="1"/>
-    <col min="7" max="16384" width="8.85546875" style="33"/>
+    <col min="5" max="5" width="16.44140625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" style="33" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="33"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="9" customFormat="1" ht="21">
       <c r="A1" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="8" customFormat="1" ht="21">
       <c r="A2" s="8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="8" customFormat="1" ht="21">
@@ -1668,7 +1670,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="17" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -1705,7 +1707,7 @@
       <c r="E8" s="54"/>
       <c r="F8" s="54"/>
     </row>
-    <row r="9" spans="1:6" s="4" customFormat="1" ht="30">
+    <row r="9" spans="1:6" s="4" customFormat="1" ht="28.8">
       <c r="A9" s="13" t="s">
         <v>22</v>
       </c>
@@ -1727,10 +1729,10 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>9</v>
@@ -1747,10 +1749,10 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="33" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C11" s="33" t="s">
         <v>9</v>
@@ -1767,10 +1769,10 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>9</v>
@@ -1787,10 +1789,10 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>9</v>
@@ -1874,78 +1876,29 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{498C4FBD-A6C4-430E-A90E-452D1A8F7A52}">
-  <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="83.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" s="6" customFormat="1" ht="21">
-      <c r="A1" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" s="7" customFormat="1" ht="21">
-      <c r="A2" s="31" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="17" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="21" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="13" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1251FF9-425C-410E-B269-C7726F9C2504}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:G200"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.109375" style="1" customWidth="1"/>
     <col min="5" max="6" width="10" style="1" customWidth="1"/>
-    <col min="7" max="7" width="42.28515625" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.85546875" style="1"/>
+    <col min="7" max="7" width="42.33203125" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21">
       <c r="A1" s="8" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="31" customFormat="1" ht="21">
       <c r="A2" s="31" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -1954,7 +1907,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="17" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1976,7 +1929,7 @@
       <c r="F7" s="10"/>
       <c r="G7" s="10"/>
     </row>
-    <row r="8" spans="1:7" s="6" customFormat="1" ht="30">
+    <row r="8" spans="1:7" s="6" customFormat="1" ht="28.8">
       <c r="A8" s="13" t="s">
         <v>3</v>
       </c>
@@ -2001,50 +1954,50 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="49" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C11" s="1">
         <v>40022</v>
@@ -2056,181 +2009,181 @@
         <v>24</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="C13" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G13" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="49" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C15" s="1">
         <v>8255</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="49" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C16" s="1">
         <v>6845</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="D17" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G17" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="9" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>24</v>
@@ -2238,36 +2191,36 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G21" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>24</v>
@@ -2275,16 +2228,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>24</v>
@@ -2292,196 +2245,196 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C25" s="1">
         <v>4164</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C26" s="1">
         <v>4164</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C27" s="1">
         <v>4164</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C28" s="1">
         <v>4164</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C29" s="1">
         <v>4164</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C30" s="1">
         <v>4164</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C31" s="1">
         <v>4164</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C32" s="1">
         <v>4164</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>24</v>
@@ -2489,19 +2442,19 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -3337,69 +3290,72 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35D2A4B1-8E0B-46C6-8B83-02048610537D}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:I1340"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <dimension ref="A1:L2833"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7109375" style="28" customWidth="1"/>
-    <col min="4" max="4" width="24.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="22.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="95.85546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="73.7109375" style="44" customWidth="1"/>
-    <col min="8" max="16384" width="8.85546875" style="1"/>
+    <col min="2" max="2" width="7.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="3.6640625" style="28" customWidth="1"/>
+    <col min="4" max="4" width="24.109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="6.88671875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="5.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="95.88671875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="73.6640625" style="44" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="21">
+    <row r="1" spans="1:12" ht="21">
       <c r="A1" s="8" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="22"/>
     </row>
-    <row r="2" spans="1:9" s="2" customFormat="1" ht="21">
+    <row r="2" spans="1:12" s="2" customFormat="1" ht="21">
       <c r="A2" s="31" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="22"/>
-      <c r="G2" s="45"/>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="J2" s="45"/>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="11"/>
       <c r="B3" s="11"/>
       <c r="C3" s="23"/>
       <c r="D3" s="9"/>
-      <c r="F3" s="9"/>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="I3" s="9"/>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="17" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="24"/>
       <c r="D4" s="9"/>
-      <c r="F4" s="9"/>
       <c r="I4" s="9"/>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="L4" s="9"/>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="21" t="s">
         <v>30</v>
       </c>
       <c r="B5" s="21"/>
       <c r="C5" s="25"/>
       <c r="D5" s="9"/>
-      <c r="F5" s="9"/>
       <c r="I5" s="9"/>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="L5" s="9"/>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="11"/>
       <c r="B6" s="11"/>
       <c r="C6" s="23"/>
       <c r="D6" s="9"/>
-      <c r="F6" s="9"/>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="I6" s="9"/>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="14" t="s">
         <v>19</v>
       </c>
@@ -3408,9 +3364,12 @@
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
-      <c r="G7" s="46"/>
-    </row>
-    <row r="8" spans="1:9" s="6" customFormat="1" ht="30">
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="46"/>
+    </row>
+    <row r="8" spans="1:12" s="6" customFormat="1" ht="28.8">
       <c r="A8" s="13" t="s">
         <v>3</v>
       </c>
@@ -3427,79 +3386,88 @@
         <v>47</v>
       </c>
       <c r="F8" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="I8" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="G8" s="47" t="s">
+      <c r="J8" s="47" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="G9" s="44" t="s">
-        <v>256</v>
-      </c>
-      <c r="I9" s="9"/>
-    </row>
-    <row r="10" spans="1:9" ht="30">
+      <c r="I9" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J9" s="44" t="s">
+        <v>253</v>
+      </c>
+      <c r="L9" s="9"/>
+    </row>
+    <row r="10" spans="1:12" ht="28.8">
       <c r="A10" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="G10" s="44" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="135">
+        <v>192</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="J10" s="44" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="115.2">
       <c r="A11" s="9" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="27"/>
       <c r="D11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="G11" s="44" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="30">
+      <c r="I11" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="J11" s="44" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="28.8">
       <c r="A12" s="50" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B12" s="50"/>
       <c r="C12" s="52"/>
       <c r="D12" s="41" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E12" s="41" t="s">
-        <v>226</v>
-      </c>
-      <c r="F12" s="41" t="s">
-        <v>236</v>
-      </c>
-      <c r="G12" s="53" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" s="41" customFormat="1">
+        <v>223</v>
+      </c>
+      <c r="I12" s="41" t="s">
+        <v>233</v>
+      </c>
+      <c r="J12" s="53" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" s="41" customFormat="1">
       <c r="A13" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="28"/>
@@ -3507,368 +3475,371 @@
         <v>26</v>
       </c>
       <c r="E13" s="1"/>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J13" s="44"/>
+    </row>
+    <row r="14" spans="1:12" ht="57.6">
+      <c r="A14" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="G13" s="44"/>
-    </row>
-    <row r="14" spans="1:9" ht="60">
-      <c r="A14" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G14" s="44" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="30">
+      <c r="I14" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="J14" s="44" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="28.8">
       <c r="A15" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="G15" s="44" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="60">
+        <v>192</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="J15" s="44" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="57.6">
       <c r="A16" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G16" s="44" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="30">
+      <c r="I16" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="J16" s="44" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="28.8">
       <c r="A17" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="G17" s="44" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>192</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="J17" s="44" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="75">
+      <c r="I18" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="57.6">
       <c r="A19" s="9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B19" s="9"/>
       <c r="C19" s="27"/>
       <c r="D19" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="G19" s="44" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="30">
+      <c r="I19" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="J19" s="44" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="28.8">
       <c r="A20" s="9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="27">
         <v>14</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E20" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="J20" s="44" t="s">
         <v>255</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="G20" s="44" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="9" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B21" s="9"/>
       <c r="C21" s="27"/>
       <c r="D21" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="60">
+      <c r="I21" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="57.6">
       <c r="A22" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G22" s="44" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="30">
+      <c r="I22" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="J22" s="44" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="28.8">
       <c r="A23" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="G23" s="44" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>192</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="J23" s="44" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+      <c r="I24" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="35" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B25" s="12"/>
       <c r="C25" s="23"/>
       <c r="D25" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F25" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="G25" s="1"/>
-    </row>
-    <row r="26" spans="1:7">
+      <c r="I25" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" s="9" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B26" s="9"/>
       <c r="C26" s="27"/>
       <c r="D26" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="67.5" customHeight="1">
+      <c r="I26" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="67.5" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G27" s="44" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="30">
+      <c r="I27" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="J27" s="44" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="28.8">
       <c r="A28" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="G28" s="44" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>192</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="J28" s="44" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+      <c r="I29" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="150">
+      <c r="I30" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="144">
       <c r="A31" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B31" s="9"/>
       <c r="C31" s="27"/>
       <c r="D31" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="G31" s="44" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="30">
+      <c r="I31" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J31" s="44" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="28.8">
       <c r="A32" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B32" s="9"/>
       <c r="C32" s="27">
         <v>4</v>
       </c>
       <c r="D32" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="J32" s="44" t="s">
         <v>177</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="G32" s="44" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B33" s="9"/>
       <c r="C33" s="27">
         <v>13</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="G33" s="44" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="30">
+        <v>148</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J33" s="44" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="28.8">
       <c r="A34" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B34" s="9"/>
       <c r="C34" s="27">
         <v>14</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="G34" s="44" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>175</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="J34" s="44" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B35" s="9"/>
       <c r="C35" s="27">
         <v>19</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="G35" s="44" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>168</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J35" s="44" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B36" s="9"/>
       <c r="C36" s="27">
         <v>24</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="G36" s="44" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="60">
+        <v>125</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="J36" s="44" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="57.6">
       <c r="A37" s="50" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B37" s="50"/>
       <c r="C37" s="52"/>
@@ -3876,98 +3847,98 @@
         <v>26</v>
       </c>
       <c r="E37" s="41"/>
-      <c r="F37" s="41" t="s">
-        <v>186</v>
-      </c>
-      <c r="G37" s="53" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+      <c r="I37" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="J37" s="53" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" s="50" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B38" s="50"/>
       <c r="C38" s="52">
         <v>3</v>
       </c>
       <c r="D38" s="41" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E38" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="F38" s="41" t="s">
-        <v>216</v>
-      </c>
-      <c r="G38" s="53" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>251</v>
+      </c>
+      <c r="I38" s="41" t="s">
+        <v>213</v>
+      </c>
+      <c r="J38" s="53" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" s="50" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B39" s="50"/>
       <c r="C39" s="52">
         <v>4</v>
       </c>
       <c r="D39" s="41" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E39" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="F39" s="41" t="s">
-        <v>214</v>
-      </c>
-      <c r="G39" s="53" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>251</v>
+      </c>
+      <c r="I39" s="41" t="s">
+        <v>211</v>
+      </c>
+      <c r="J39" s="53" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" s="50" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B40" s="50"/>
       <c r="C40" s="52">
         <v>15</v>
       </c>
       <c r="D40" s="41" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E40" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="F40" s="41" t="s">
-        <v>211</v>
-      </c>
-      <c r="G40" s="53" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="75">
+        <v>251</v>
+      </c>
+      <c r="I40" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="J40" s="53" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="72">
       <c r="A41" s="50" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B41" s="50"/>
       <c r="C41" s="52"/>
       <c r="D41" s="41" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E41" s="41" t="s">
-        <v>207</v>
-      </c>
-      <c r="F41" s="41" t="s">
-        <v>235</v>
-      </c>
-      <c r="G41" s="53" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="60">
+        <v>204</v>
+      </c>
+      <c r="I41" s="41" t="s">
+        <v>232</v>
+      </c>
+      <c r="J41" s="53" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="57.6">
       <c r="A42" s="50" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B42" s="50"/>
       <c r="C42" s="52"/>
@@ -3975,98 +3946,98 @@
         <v>26</v>
       </c>
       <c r="E42" s="41"/>
-      <c r="F42" s="41" t="s">
-        <v>186</v>
-      </c>
-      <c r="G42" s="53" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+      <c r="I42" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="J42" s="53" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43" s="50" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B43" s="50"/>
       <c r="C43" s="52">
         <v>3</v>
       </c>
       <c r="D43" s="41" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E43" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="F43" s="41" t="s">
-        <v>216</v>
-      </c>
-      <c r="G43" s="53" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>251</v>
+      </c>
+      <c r="I43" s="41" t="s">
+        <v>213</v>
+      </c>
+      <c r="J43" s="53" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
       <c r="A44" s="50" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B44" s="50"/>
       <c r="C44" s="52">
         <v>4</v>
       </c>
       <c r="D44" s="41" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E44" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="F44" s="41" t="s">
-        <v>214</v>
-      </c>
-      <c r="G44" s="53" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>251</v>
+      </c>
+      <c r="I44" s="41" t="s">
+        <v>211</v>
+      </c>
+      <c r="J44" s="53" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45" s="50" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B45" s="50"/>
       <c r="C45" s="52">
         <v>15</v>
       </c>
       <c r="D45" s="41" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E45" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="F45" s="41" t="s">
-        <v>211</v>
-      </c>
-      <c r="G45" s="53" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="75">
+        <v>251</v>
+      </c>
+      <c r="I45" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="J45" s="53" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="72">
       <c r="A46" s="50" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B46" s="50"/>
       <c r="C46" s="52"/>
       <c r="D46" s="41" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E46" s="41" t="s">
-        <v>207</v>
-      </c>
-      <c r="F46" s="41" t="s">
-        <v>235</v>
-      </c>
-      <c r="G46" s="53" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="60">
+        <v>204</v>
+      </c>
+      <c r="I46" s="41" t="s">
+        <v>232</v>
+      </c>
+      <c r="J46" s="53" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="57.6">
       <c r="A47" s="50" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B47" s="50"/>
       <c r="C47" s="52"/>
@@ -4074,98 +4045,98 @@
         <v>26</v>
       </c>
       <c r="E47" s="41"/>
-      <c r="F47" s="41" t="s">
-        <v>186</v>
-      </c>
-      <c r="G47" s="53" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+      <c r="I47" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="J47" s="53" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
       <c r="A48" s="50" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B48" s="50"/>
       <c r="C48" s="52">
         <v>3</v>
       </c>
       <c r="D48" s="41" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E48" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="F48" s="41" t="s">
-        <v>216</v>
-      </c>
-      <c r="G48" s="53" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+        <v>251</v>
+      </c>
+      <c r="I48" s="41" t="s">
+        <v>213</v>
+      </c>
+      <c r="J48" s="53" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49" s="50" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B49" s="50"/>
       <c r="C49" s="52">
         <v>4</v>
       </c>
       <c r="D49" s="41" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E49" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="F49" s="41" t="s">
-        <v>214</v>
-      </c>
-      <c r="G49" s="53" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
+        <v>251</v>
+      </c>
+      <c r="I49" s="41" t="s">
+        <v>211</v>
+      </c>
+      <c r="J49" s="53" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50" s="50" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B50" s="50"/>
       <c r="C50" s="52">
         <v>15</v>
       </c>
       <c r="D50" s="41" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E50" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="F50" s="41" t="s">
-        <v>211</v>
-      </c>
-      <c r="G50" s="53" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="75">
+        <v>251</v>
+      </c>
+      <c r="I50" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="J50" s="53" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="72">
       <c r="A51" s="50" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B51" s="50"/>
       <c r="C51" s="52"/>
       <c r="D51" s="41" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E51" s="41" t="s">
-        <v>207</v>
-      </c>
-      <c r="F51" s="41" t="s">
-        <v>235</v>
-      </c>
-      <c r="G51" s="53" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="60">
+        <v>204</v>
+      </c>
+      <c r="I51" s="41" t="s">
+        <v>232</v>
+      </c>
+      <c r="J51" s="53" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="57.6">
       <c r="A52" s="50" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B52" s="50"/>
       <c r="C52" s="52"/>
@@ -4173,98 +4144,98 @@
         <v>26</v>
       </c>
       <c r="E52" s="41"/>
-      <c r="F52" s="41" t="s">
-        <v>186</v>
-      </c>
-      <c r="G52" s="53" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+      <c r="I52" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="J52" s="53" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
       <c r="A53" s="50" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B53" s="50"/>
       <c r="C53" s="52">
         <v>3</v>
       </c>
       <c r="D53" s="41" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E53" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="F53" s="41" t="s">
-        <v>216</v>
-      </c>
-      <c r="G53" s="53" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+        <v>251</v>
+      </c>
+      <c r="I53" s="41" t="s">
+        <v>213</v>
+      </c>
+      <c r="J53" s="53" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
       <c r="A54" s="50" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B54" s="50"/>
       <c r="C54" s="52">
         <v>4</v>
       </c>
       <c r="D54" s="41" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E54" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="F54" s="41" t="s">
-        <v>214</v>
-      </c>
-      <c r="G54" s="53" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
+        <v>251</v>
+      </c>
+      <c r="I54" s="41" t="s">
+        <v>211</v>
+      </c>
+      <c r="J54" s="53" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
       <c r="A55" s="50" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B55" s="50"/>
       <c r="C55" s="52">
         <v>15</v>
       </c>
       <c r="D55" s="41" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E55" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="F55" s="41" t="s">
-        <v>211</v>
-      </c>
-      <c r="G55" s="53" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="75">
+        <v>251</v>
+      </c>
+      <c r="I55" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="J55" s="53" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="72">
       <c r="A56" s="50" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B56" s="50"/>
       <c r="C56" s="52"/>
       <c r="D56" s="41" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E56" s="41" t="s">
-        <v>207</v>
-      </c>
-      <c r="F56" s="41" t="s">
-        <v>235</v>
-      </c>
-      <c r="G56" s="53" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="60">
+        <v>204</v>
+      </c>
+      <c r="I56" s="41" t="s">
+        <v>232</v>
+      </c>
+      <c r="J56" s="53" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="57.6">
       <c r="A57" s="50" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B57" s="50"/>
       <c r="C57" s="52"/>
@@ -4272,98 +4243,98 @@
         <v>26</v>
       </c>
       <c r="E57" s="41"/>
-      <c r="F57" s="41" t="s">
-        <v>186</v>
-      </c>
-      <c r="G57" s="53" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
+      <c r="I57" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="J57" s="53" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
       <c r="A58" s="50" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B58" s="50"/>
       <c r="C58" s="52">
         <v>3</v>
       </c>
       <c r="D58" s="41" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E58" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="F58" s="41" t="s">
-        <v>216</v>
-      </c>
-      <c r="G58" s="53" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
+        <v>251</v>
+      </c>
+      <c r="I58" s="41" t="s">
+        <v>213</v>
+      </c>
+      <c r="J58" s="53" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
       <c r="A59" s="50" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B59" s="50"/>
       <c r="C59" s="52">
         <v>4</v>
       </c>
       <c r="D59" s="41" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E59" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="F59" s="41" t="s">
-        <v>214</v>
-      </c>
-      <c r="G59" s="53" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
+        <v>251</v>
+      </c>
+      <c r="I59" s="41" t="s">
+        <v>211</v>
+      </c>
+      <c r="J59" s="53" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
       <c r="A60" s="50" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B60" s="50"/>
       <c r="C60" s="52">
         <v>15</v>
       </c>
       <c r="D60" s="41" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E60" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="F60" s="41" t="s">
-        <v>211</v>
-      </c>
-      <c r="G60" s="53" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="75">
+        <v>251</v>
+      </c>
+      <c r="I60" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="J60" s="53" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="72">
       <c r="A61" s="50" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B61" s="50"/>
       <c r="C61" s="52"/>
       <c r="D61" s="41" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E61" s="41" t="s">
-        <v>207</v>
-      </c>
-      <c r="F61" s="41" t="s">
-        <v>235</v>
-      </c>
-      <c r="G61" s="53" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="60">
+        <v>204</v>
+      </c>
+      <c r="I61" s="41" t="s">
+        <v>232</v>
+      </c>
+      <c r="J61" s="53" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="57.6">
       <c r="A62" s="50" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B62" s="50"/>
       <c r="C62" s="52"/>
@@ -4371,98 +4342,98 @@
         <v>26</v>
       </c>
       <c r="E62" s="41"/>
-      <c r="F62" s="41" t="s">
-        <v>186</v>
-      </c>
-      <c r="G62" s="53" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
+      <c r="I62" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="J62" s="53" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
       <c r="A63" s="50" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B63" s="50"/>
       <c r="C63" s="52">
         <v>3</v>
       </c>
       <c r="D63" s="41" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E63" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="F63" s="41" t="s">
-        <v>216</v>
-      </c>
-      <c r="G63" s="53" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
+        <v>251</v>
+      </c>
+      <c r="I63" s="41" t="s">
+        <v>213</v>
+      </c>
+      <c r="J63" s="53" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
       <c r="A64" s="50" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B64" s="50"/>
       <c r="C64" s="52">
         <v>4</v>
       </c>
       <c r="D64" s="41" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E64" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="F64" s="41" t="s">
-        <v>214</v>
-      </c>
-      <c r="G64" s="53" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
+        <v>251</v>
+      </c>
+      <c r="I64" s="41" t="s">
+        <v>211</v>
+      </c>
+      <c r="J64" s="53" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
       <c r="A65" s="50" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B65" s="50"/>
       <c r="C65" s="52">
         <v>15</v>
       </c>
       <c r="D65" s="41" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E65" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="F65" s="41" t="s">
-        <v>211</v>
-      </c>
-      <c r="G65" s="53" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="75">
+        <v>251</v>
+      </c>
+      <c r="I65" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="J65" s="53" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="72">
       <c r="A66" s="50" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B66" s="50"/>
       <c r="C66" s="52"/>
       <c r="D66" s="41" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E66" s="41" t="s">
-        <v>207</v>
-      </c>
-      <c r="F66" s="41" t="s">
-        <v>235</v>
-      </c>
-      <c r="G66" s="53" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="60">
+        <v>204</v>
+      </c>
+      <c r="I66" s="41" t="s">
+        <v>232</v>
+      </c>
+      <c r="J66" s="53" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="57.6">
       <c r="A67" s="50" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B67" s="50"/>
       <c r="C67" s="52"/>
@@ -4470,98 +4441,98 @@
         <v>26</v>
       </c>
       <c r="E67" s="41"/>
-      <c r="F67" s="41" t="s">
-        <v>186</v>
-      </c>
-      <c r="G67" s="53" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
+      <c r="I67" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="J67" s="53" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
       <c r="A68" s="50" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B68" s="50"/>
       <c r="C68" s="52">
         <v>3</v>
       </c>
       <c r="D68" s="41" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E68" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="F68" s="41" t="s">
-        <v>216</v>
-      </c>
-      <c r="G68" s="53" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7">
+        <v>251</v>
+      </c>
+      <c r="I68" s="41" t="s">
+        <v>213</v>
+      </c>
+      <c r="J68" s="53" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
       <c r="A69" s="50" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B69" s="50"/>
       <c r="C69" s="52">
         <v>4</v>
       </c>
       <c r="D69" s="41" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E69" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="F69" s="41" t="s">
-        <v>214</v>
-      </c>
-      <c r="G69" s="53" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7">
+        <v>251</v>
+      </c>
+      <c r="I69" s="41" t="s">
+        <v>211</v>
+      </c>
+      <c r="J69" s="53" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
       <c r="A70" s="50" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B70" s="50"/>
       <c r="C70" s="52">
         <v>15</v>
       </c>
       <c r="D70" s="41" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E70" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="F70" s="41" t="s">
-        <v>211</v>
-      </c>
-      <c r="G70" s="53" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="75">
+        <v>251</v>
+      </c>
+      <c r="I70" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="J70" s="53" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="72">
       <c r="A71" s="50" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B71" s="50"/>
       <c r="C71" s="52"/>
       <c r="D71" s="41" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E71" s="41" t="s">
-        <v>207</v>
-      </c>
-      <c r="F71" s="41" t="s">
-        <v>235</v>
-      </c>
-      <c r="G71" s="53" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="60">
+        <v>204</v>
+      </c>
+      <c r="I71" s="41" t="s">
+        <v>232</v>
+      </c>
+      <c r="J71" s="53" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="57.6">
       <c r="A72" s="50" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B72" s="50"/>
       <c r="C72" s="52"/>
@@ -4569,112 +4540,112 @@
         <v>26</v>
       </c>
       <c r="E72" s="41"/>
-      <c r="F72" s="41" t="s">
-        <v>186</v>
-      </c>
-      <c r="G72" s="53" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7">
+      <c r="I72" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="J72" s="53" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
       <c r="A73" s="50" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B73" s="50"/>
       <c r="C73" s="52">
         <v>3</v>
       </c>
       <c r="D73" s="41" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E73" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="F73" s="41" t="s">
-        <v>216</v>
-      </c>
-      <c r="G73" s="53" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7">
+        <v>251</v>
+      </c>
+      <c r="I73" s="41" t="s">
+        <v>213</v>
+      </c>
+      <c r="J73" s="53" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
       <c r="A74" s="50" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B74" s="50"/>
       <c r="C74" s="52">
         <v>4</v>
       </c>
       <c r="D74" s="41" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E74" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="F74" s="41" t="s">
-        <v>214</v>
-      </c>
-      <c r="G74" s="53" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7">
+        <v>251</v>
+      </c>
+      <c r="I74" s="41" t="s">
+        <v>211</v>
+      </c>
+      <c r="J74" s="53" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
       <c r="A75" s="50" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B75" s="50"/>
       <c r="C75" s="52">
         <v>15</v>
       </c>
       <c r="D75" s="41" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E75" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="F75" s="41" t="s">
-        <v>211</v>
-      </c>
-      <c r="G75" s="53" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="75">
+        <v>251</v>
+      </c>
+      <c r="I75" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="J75" s="53" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="72">
       <c r="A76" s="50" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B76" s="50"/>
       <c r="C76" s="52"/>
       <c r="D76" s="41" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E76" s="41" t="s">
-        <v>207</v>
-      </c>
-      <c r="F76" s="41" t="s">
-        <v>235</v>
-      </c>
-      <c r="G76" s="53" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="60">
+        <v>204</v>
+      </c>
+      <c r="I76" s="41" t="s">
+        <v>232</v>
+      </c>
+      <c r="J76" s="53" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="57.6">
       <c r="A77" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F77" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="G77" s="44" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7">
+      <c r="I77" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="J77" s="44" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10">
       <c r="A78" s="51" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B78"/>
       <c r="C78" s="1"/>
@@ -4682,40 +4653,40 @@
         <v>26</v>
       </c>
       <c r="E78"/>
-      <c r="F78" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="G78" s="40"/>
-    </row>
-    <row r="79" spans="1:7">
+      <c r="I78" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="J78" s="40"/>
+    </row>
+    <row r="79" spans="1:10">
       <c r="A79" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F79" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7">
+      <c r="I79" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
       <c r="A80" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C80" s="28">
         <v>1</v>
       </c>
       <c r="D80" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="J80" s="44" t="s">
         <v>170</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="G80" s="44" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="173" spans="5:5">
@@ -4730,253 +4701,253 @@
     <row r="176" spans="5:5">
       <c r="E176" s="40"/>
     </row>
-    <row r="177" spans="5:7">
+    <row r="177" spans="5:10">
       <c r="E177" s="40"/>
     </row>
-    <row r="178" spans="5:7">
+    <row r="178" spans="5:10">
       <c r="E178" s="40"/>
     </row>
-    <row r="179" spans="5:7">
+    <row r="179" spans="5:10">
       <c r="E179" s="40"/>
     </row>
-    <row r="189" spans="5:7">
+    <row r="189" spans="5:10">
       <c r="E189" s="40"/>
     </row>
-    <row r="191" spans="5:7">
+    <row r="191" spans="5:10">
       <c r="E191" s="40"/>
-      <c r="G191" s="48"/>
-    </row>
-    <row r="192" spans="5:7">
-      <c r="G192" s="48"/>
-    </row>
-    <row r="193" spans="5:7">
+      <c r="J191" s="48"/>
+    </row>
+    <row r="192" spans="5:10">
+      <c r="J192" s="48"/>
+    </row>
+    <row r="193" spans="5:10">
       <c r="E193" s="41"/>
-      <c r="G193" s="48"/>
-    </row>
-    <row r="194" spans="5:7">
+      <c r="J193" s="48"/>
+    </row>
+    <row r="194" spans="5:10">
       <c r="E194" s="40"/>
-      <c r="G194" s="48"/>
-    </row>
-    <row r="195" spans="5:7">
+      <c r="J194" s="48"/>
+    </row>
+    <row r="195" spans="5:10">
       <c r="E195" s="40"/>
-      <c r="G195" s="48"/>
-    </row>
-    <row r="196" spans="5:7">
+      <c r="J195" s="48"/>
+    </row>
+    <row r="196" spans="5:10">
       <c r="E196" s="40"/>
-      <c r="G196" s="48"/>
-    </row>
-    <row r="197" spans="5:7">
+      <c r="J196" s="48"/>
+    </row>
+    <row r="197" spans="5:10">
       <c r="E197" s="40"/>
-      <c r="G197" s="48"/>
-    </row>
-    <row r="198" spans="5:7">
+      <c r="J197" s="48"/>
+    </row>
+    <row r="198" spans="5:10">
       <c r="E198" s="40"/>
-      <c r="G198" s="48"/>
-    </row>
-    <row r="199" spans="5:7">
+      <c r="J198" s="48"/>
+    </row>
+    <row r="199" spans="5:10">
       <c r="E199" s="42"/>
-      <c r="G199" s="48"/>
-    </row>
-    <row r="200" spans="5:7">
+      <c r="J199" s="48"/>
+    </row>
+    <row r="200" spans="5:10">
       <c r="E200" s="40"/>
-      <c r="G200" s="48"/>
-    </row>
-    <row r="201" spans="5:7">
+      <c r="J200" s="48"/>
+    </row>
+    <row r="201" spans="5:10">
       <c r="E201" s="40"/>
-      <c r="G201" s="48"/>
-    </row>
-    <row r="202" spans="5:7">
+      <c r="J201" s="48"/>
+    </row>
+    <row r="202" spans="5:10">
       <c r="E202" s="40"/>
-      <c r="G202" s="48"/>
-    </row>
-    <row r="203" spans="5:7">
+      <c r="J202" s="48"/>
+    </row>
+    <row r="203" spans="5:10">
       <c r="E203" s="40"/>
-      <c r="G203" s="48"/>
-    </row>
-    <row r="204" spans="5:7">
+      <c r="J203" s="48"/>
+    </row>
+    <row r="204" spans="5:10">
       <c r="E204" s="40"/>
-      <c r="G204" s="48"/>
-    </row>
-    <row r="205" spans="5:7">
+      <c r="J204" s="48"/>
+    </row>
+    <row r="205" spans="5:10">
       <c r="E205" s="40"/>
-      <c r="G205" s="48"/>
-    </row>
-    <row r="206" spans="5:7">
+      <c r="J205" s="48"/>
+    </row>
+    <row r="206" spans="5:10">
       <c r="E206" s="40"/>
-      <c r="G206" s="48"/>
-    </row>
-    <row r="207" spans="5:7">
+      <c r="J206" s="48"/>
+    </row>
+    <row r="207" spans="5:10">
       <c r="E207" s="40"/>
-      <c r="G207" s="48"/>
-    </row>
-    <row r="208" spans="5:7">
+      <c r="J207" s="48"/>
+    </row>
+    <row r="208" spans="5:10">
       <c r="E208" s="40"/>
-      <c r="G208" s="48"/>
-    </row>
-    <row r="209" spans="5:7">
+      <c r="J208" s="48"/>
+    </row>
+    <row r="209" spans="5:10">
       <c r="E209" s="40"/>
-      <c r="G209" s="48"/>
-    </row>
-    <row r="210" spans="5:7">
+      <c r="J209" s="48"/>
+    </row>
+    <row r="210" spans="5:10">
       <c r="E210" s="40"/>
-      <c r="G210" s="48"/>
-    </row>
-    <row r="211" spans="5:7">
+      <c r="J210" s="48"/>
+    </row>
+    <row r="211" spans="5:10">
       <c r="E211" s="40"/>
-      <c r="G211" s="48"/>
-    </row>
-    <row r="212" spans="5:7">
+      <c r="J211" s="48"/>
+    </row>
+    <row r="212" spans="5:10">
       <c r="E212" s="40"/>
-      <c r="G212" s="48"/>
-    </row>
-    <row r="213" spans="5:7">
+      <c r="J212" s="48"/>
+    </row>
+    <row r="213" spans="5:10">
       <c r="E213" s="40"/>
-      <c r="G213" s="48"/>
-    </row>
-    <row r="214" spans="5:7">
+      <c r="J213" s="48"/>
+    </row>
+    <row r="214" spans="5:10">
       <c r="E214" s="40"/>
-      <c r="G214" s="48"/>
-    </row>
-    <row r="215" spans="5:7">
+      <c r="J214" s="48"/>
+    </row>
+    <row r="215" spans="5:10">
       <c r="E215" s="40"/>
-      <c r="G215" s="48"/>
-    </row>
-    <row r="216" spans="5:7">
+      <c r="J215" s="48"/>
+    </row>
+    <row r="216" spans="5:10">
       <c r="E216" s="40"/>
-      <c r="G216" s="48"/>
-    </row>
-    <row r="217" spans="5:7">
+      <c r="J216" s="48"/>
+    </row>
+    <row r="217" spans="5:10">
       <c r="E217" s="40"/>
-      <c r="G217" s="48"/>
-    </row>
-    <row r="218" spans="5:7">
+      <c r="J217" s="48"/>
+    </row>
+    <row r="218" spans="5:10">
       <c r="E218" s="40"/>
-      <c r="G218" s="48"/>
-    </row>
-    <row r="219" spans="5:7">
+      <c r="J218" s="48"/>
+    </row>
+    <row r="219" spans="5:10">
       <c r="E219" s="40"/>
-      <c r="G219" s="48"/>
-    </row>
-    <row r="220" spans="5:7">
+      <c r="J219" s="48"/>
+    </row>
+    <row r="220" spans="5:10">
       <c r="E220" s="40"/>
-      <c r="G220" s="48"/>
-    </row>
-    <row r="221" spans="5:7">
+      <c r="J220" s="48"/>
+    </row>
+    <row r="221" spans="5:10">
       <c r="E221" s="40"/>
-      <c r="G221" s="48"/>
-    </row>
-    <row r="222" spans="5:7">
+      <c r="J221" s="48"/>
+    </row>
+    <row r="222" spans="5:10">
       <c r="E222" s="40"/>
-      <c r="G222" s="48"/>
-    </row>
-    <row r="223" spans="5:7">
+      <c r="J222" s="48"/>
+    </row>
+    <row r="223" spans="5:10">
       <c r="E223" s="40"/>
-      <c r="G223" s="48"/>
-    </row>
-    <row r="224" spans="5:7">
+      <c r="J223" s="48"/>
+    </row>
+    <row r="224" spans="5:10">
       <c r="E224" s="40"/>
-      <c r="G224" s="48"/>
-    </row>
-    <row r="225" spans="5:7">
+      <c r="J224" s="48"/>
+    </row>
+    <row r="225" spans="5:10">
       <c r="E225" s="40"/>
-      <c r="G225" s="48"/>
-    </row>
-    <row r="226" spans="5:7">
+      <c r="J225" s="48"/>
+    </row>
+    <row r="226" spans="5:10">
       <c r="E226" s="40"/>
-      <c r="G226" s="48"/>
-    </row>
-    <row r="227" spans="5:7">
+      <c r="J226" s="48"/>
+    </row>
+    <row r="227" spans="5:10">
       <c r="E227" s="40"/>
-      <c r="G227" s="48"/>
-    </row>
-    <row r="228" spans="5:7">
+      <c r="J227" s="48"/>
+    </row>
+    <row r="228" spans="5:10">
       <c r="E228" s="40"/>
-      <c r="G228" s="48"/>
-    </row>
-    <row r="229" spans="5:7">
+      <c r="J228" s="48"/>
+    </row>
+    <row r="229" spans="5:10">
       <c r="E229" s="40"/>
-      <c r="G229" s="48"/>
-    </row>
-    <row r="230" spans="5:7">
+      <c r="J229" s="48"/>
+    </row>
+    <row r="230" spans="5:10">
       <c r="E230" s="40"/>
-      <c r="G230" s="48"/>
-    </row>
-    <row r="231" spans="5:7">
+      <c r="J230" s="48"/>
+    </row>
+    <row r="231" spans="5:10">
       <c r="E231" s="40"/>
-      <c r="G231" s="48"/>
-    </row>
-    <row r="232" spans="5:7">
+      <c r="J231" s="48"/>
+    </row>
+    <row r="232" spans="5:10">
       <c r="E232" s="40"/>
-      <c r="G232" s="48"/>
-    </row>
-    <row r="233" spans="5:7">
+      <c r="J232" s="48"/>
+    </row>
+    <row r="233" spans="5:10">
       <c r="E233" s="40"/>
-      <c r="G233" s="48"/>
-    </row>
-    <row r="234" spans="5:7">
+      <c r="J233" s="48"/>
+    </row>
+    <row r="234" spans="5:10">
       <c r="E234" s="40"/>
-      <c r="G234" s="48"/>
-    </row>
-    <row r="235" spans="5:7">
+      <c r="J234" s="48"/>
+    </row>
+    <row r="235" spans="5:10">
       <c r="E235" s="40"/>
-      <c r="G235" s="48"/>
-    </row>
-    <row r="236" spans="5:7">
+      <c r="J235" s="48"/>
+    </row>
+    <row r="236" spans="5:10">
       <c r="E236" s="40"/>
-      <c r="G236" s="48"/>
-    </row>
-    <row r="237" spans="5:7">
+      <c r="J236" s="48"/>
+    </row>
+    <row r="237" spans="5:10">
       <c r="E237" s="40"/>
-      <c r="G237" s="48"/>
-    </row>
-    <row r="238" spans="5:7">
+      <c r="J237" s="48"/>
+    </row>
+    <row r="238" spans="5:10">
       <c r="E238" s="40"/>
-      <c r="G238" s="48"/>
-    </row>
-    <row r="246" spans="5:7">
+      <c r="J238" s="48"/>
+    </row>
+    <row r="246" spans="5:10">
       <c r="E246" s="40"/>
     </row>
-    <row r="255" spans="5:7">
-      <c r="G255" s="48"/>
-    </row>
-    <row r="256" spans="5:7">
-      <c r="G256" s="48"/>
-    </row>
-    <row r="257" spans="7:7">
-      <c r="G257" s="48"/>
-    </row>
-    <row r="258" spans="7:7">
-      <c r="G258" s="48"/>
-    </row>
-    <row r="259" spans="7:7">
-      <c r="G259" s="48"/>
-    </row>
-    <row r="260" spans="7:7">
-      <c r="G260" s="48"/>
-    </row>
-    <row r="261" spans="7:7">
-      <c r="G261" s="48"/>
-    </row>
-    <row r="262" spans="7:7">
-      <c r="G262" s="48"/>
-    </row>
-    <row r="263" spans="7:7">
-      <c r="G263" s="48"/>
-    </row>
-    <row r="264" spans="7:7">
-      <c r="G264" s="48"/>
-    </row>
-    <row r="265" spans="7:7">
-      <c r="G265" s="48"/>
-    </row>
-    <row r="266" spans="7:7">
-      <c r="G266" s="48"/>
-    </row>
-    <row r="267" spans="7:7">
-      <c r="G267" s="48"/>
-    </row>
-    <row r="268" spans="7:7">
-      <c r="G268" s="48"/>
+    <row r="255" spans="5:10">
+      <c r="J255" s="48"/>
+    </row>
+    <row r="256" spans="5:10">
+      <c r="J256" s="48"/>
+    </row>
+    <row r="257" spans="10:10">
+      <c r="J257" s="48"/>
+    </row>
+    <row r="258" spans="10:10">
+      <c r="J258" s="48"/>
+    </row>
+    <row r="259" spans="10:10">
+      <c r="J259" s="48"/>
+    </row>
+    <row r="260" spans="10:10">
+      <c r="J260" s="48"/>
+    </row>
+    <row r="261" spans="10:10">
+      <c r="J261" s="48"/>
+    </row>
+    <row r="262" spans="10:10">
+      <c r="J262" s="48"/>
+    </row>
+    <row r="263" spans="10:10">
+      <c r="J263" s="48"/>
+    </row>
+    <row r="264" spans="10:10">
+      <c r="J264" s="48"/>
+    </row>
+    <row r="265" spans="10:10">
+      <c r="J265" s="48"/>
+    </row>
+    <row r="266" spans="10:10">
+      <c r="J266" s="48"/>
+    </row>
+    <row r="267" spans="10:10">
+      <c r="J267" s="48"/>
+    </row>
+    <row r="268" spans="10:10">
+      <c r="J268" s="48"/>
     </row>
     <row r="298" spans="5:5">
       <c r="E298" s="40"/>
@@ -5047,174 +5018,174 @@
     <row r="358" spans="5:5">
       <c r="E358" s="40"/>
     </row>
-    <row r="369" spans="5:7">
+    <row r="369" spans="5:10">
       <c r="E369" s="40"/>
     </row>
-    <row r="379" spans="5:7">
+    <row r="379" spans="5:10">
       <c r="E379" s="40"/>
     </row>
-    <row r="381" spans="5:7">
-      <c r="G381" s="48"/>
-    </row>
-    <row r="382" spans="5:7">
-      <c r="G382" s="48"/>
-    </row>
-    <row r="383" spans="5:7">
-      <c r="G383" s="48"/>
-    </row>
-    <row r="384" spans="5:7">
-      <c r="G384" s="48"/>
-    </row>
-    <row r="385" spans="5:7">
-      <c r="G385" s="48"/>
-    </row>
-    <row r="386" spans="5:7">
-      <c r="G386" s="48"/>
-    </row>
-    <row r="387" spans="5:7">
-      <c r="G387" s="48"/>
-    </row>
-    <row r="388" spans="5:7">
-      <c r="G388" s="48"/>
-    </row>
-    <row r="389" spans="5:7">
-      <c r="G389" s="48"/>
-    </row>
-    <row r="390" spans="5:7">
-      <c r="G390" s="48"/>
-    </row>
-    <row r="391" spans="5:7">
-      <c r="G391" s="48"/>
-    </row>
-    <row r="392" spans="5:7">
-      <c r="G392" s="48"/>
-    </row>
-    <row r="393" spans="5:7">
-      <c r="G393" s="48"/>
-    </row>
-    <row r="394" spans="5:7">
-      <c r="G394" s="48"/>
-    </row>
-    <row r="395" spans="5:7">
-      <c r="G395" s="48"/>
-    </row>
-    <row r="396" spans="5:7">
-      <c r="G396" s="48"/>
-    </row>
-    <row r="397" spans="5:7">
-      <c r="G397" s="48"/>
-    </row>
-    <row r="398" spans="5:7">
-      <c r="G398" s="48"/>
-    </row>
-    <row r="399" spans="5:7">
-      <c r="G399" s="48"/>
-    </row>
-    <row r="400" spans="5:7">
+    <row r="381" spans="5:10">
+      <c r="J381" s="48"/>
+    </row>
+    <row r="382" spans="5:10">
+      <c r="J382" s="48"/>
+    </row>
+    <row r="383" spans="5:10">
+      <c r="J383" s="48"/>
+    </row>
+    <row r="384" spans="5:10">
+      <c r="J384" s="48"/>
+    </row>
+    <row r="385" spans="5:10">
+      <c r="J385" s="48"/>
+    </row>
+    <row r="386" spans="5:10">
+      <c r="J386" s="48"/>
+    </row>
+    <row r="387" spans="5:10">
+      <c r="J387" s="48"/>
+    </row>
+    <row r="388" spans="5:10">
+      <c r="J388" s="48"/>
+    </row>
+    <row r="389" spans="5:10">
+      <c r="J389" s="48"/>
+    </row>
+    <row r="390" spans="5:10">
+      <c r="J390" s="48"/>
+    </row>
+    <row r="391" spans="5:10">
+      <c r="J391" s="48"/>
+    </row>
+    <row r="392" spans="5:10">
+      <c r="J392" s="48"/>
+    </row>
+    <row r="393" spans="5:10">
+      <c r="J393" s="48"/>
+    </row>
+    <row r="394" spans="5:10">
+      <c r="J394" s="48"/>
+    </row>
+    <row r="395" spans="5:10">
+      <c r="J395" s="48"/>
+    </row>
+    <row r="396" spans="5:10">
+      <c r="J396" s="48"/>
+    </row>
+    <row r="397" spans="5:10">
+      <c r="J397" s="48"/>
+    </row>
+    <row r="398" spans="5:10">
+      <c r="J398" s="48"/>
+    </row>
+    <row r="399" spans="5:10">
+      <c r="J399" s="48"/>
+    </row>
+    <row r="400" spans="5:10">
       <c r="E400" s="40"/>
-      <c r="G400" s="48"/>
-    </row>
-    <row r="402" spans="5:7">
-      <c r="G402" s="48"/>
-    </row>
-    <row r="403" spans="5:7">
-      <c r="G403" s="48"/>
-    </row>
-    <row r="404" spans="5:7">
-      <c r="G404" s="48"/>
-    </row>
-    <row r="405" spans="5:7">
-      <c r="G405" s="48"/>
-    </row>
-    <row r="406" spans="5:7">
-      <c r="G406" s="48"/>
-    </row>
-    <row r="407" spans="5:7">
-      <c r="G407" s="48"/>
-    </row>
-    <row r="408" spans="5:7">
-      <c r="G408" s="48"/>
-    </row>
-    <row r="409" spans="5:7">
+      <c r="J400" s="48"/>
+    </row>
+    <row r="402" spans="5:10">
+      <c r="J402" s="48"/>
+    </row>
+    <row r="403" spans="5:10">
+      <c r="J403" s="48"/>
+    </row>
+    <row r="404" spans="5:10">
+      <c r="J404" s="48"/>
+    </row>
+    <row r="405" spans="5:10">
+      <c r="J405" s="48"/>
+    </row>
+    <row r="406" spans="5:10">
+      <c r="J406" s="48"/>
+    </row>
+    <row r="407" spans="5:10">
+      <c r="J407" s="48"/>
+    </row>
+    <row r="408" spans="5:10">
+      <c r="J408" s="48"/>
+    </row>
+    <row r="409" spans="5:10">
       <c r="E409" s="40"/>
-      <c r="G409" s="48"/>
-    </row>
-    <row r="410" spans="5:7">
-      <c r="G410" s="48"/>
-    </row>
-    <row r="411" spans="5:7">
-      <c r="G411" s="48"/>
-    </row>
-    <row r="412" spans="5:7">
-      <c r="G412" s="48"/>
-    </row>
-    <row r="413" spans="5:7">
-      <c r="G413" s="48"/>
-    </row>
-    <row r="414" spans="5:7">
-      <c r="G414" s="48"/>
-    </row>
-    <row r="415" spans="5:7">
-      <c r="G415" s="48"/>
-    </row>
-    <row r="416" spans="5:7">
-      <c r="G416" s="48"/>
-    </row>
-    <row r="417" spans="5:7">
+      <c r="J409" s="48"/>
+    </row>
+    <row r="410" spans="5:10">
+      <c r="J410" s="48"/>
+    </row>
+    <row r="411" spans="5:10">
+      <c r="J411" s="48"/>
+    </row>
+    <row r="412" spans="5:10">
+      <c r="J412" s="48"/>
+    </row>
+    <row r="413" spans="5:10">
+      <c r="J413" s="48"/>
+    </row>
+    <row r="414" spans="5:10">
+      <c r="J414" s="48"/>
+    </row>
+    <row r="415" spans="5:10">
+      <c r="J415" s="48"/>
+    </row>
+    <row r="416" spans="5:10">
+      <c r="J416" s="48"/>
+    </row>
+    <row r="417" spans="5:10">
       <c r="E417" s="40"/>
-      <c r="G417" s="48"/>
-    </row>
-    <row r="419" spans="5:7">
-      <c r="G419" s="48"/>
-    </row>
-    <row r="420" spans="5:7">
-      <c r="G420" s="48"/>
-    </row>
-    <row r="421" spans="5:7">
-      <c r="G421" s="48"/>
-    </row>
-    <row r="422" spans="5:7">
-      <c r="G422" s="48"/>
-    </row>
-    <row r="423" spans="5:7">
-      <c r="G423" s="48"/>
-    </row>
-    <row r="424" spans="5:7">
-      <c r="G424" s="48"/>
-    </row>
-    <row r="425" spans="5:7">
-      <c r="G425" s="48"/>
-    </row>
-    <row r="426" spans="5:7">
+      <c r="J417" s="48"/>
+    </row>
+    <row r="419" spans="5:10">
+      <c r="J419" s="48"/>
+    </row>
+    <row r="420" spans="5:10">
+      <c r="J420" s="48"/>
+    </row>
+    <row r="421" spans="5:10">
+      <c r="J421" s="48"/>
+    </row>
+    <row r="422" spans="5:10">
+      <c r="J422" s="48"/>
+    </row>
+    <row r="423" spans="5:10">
+      <c r="J423" s="48"/>
+    </row>
+    <row r="424" spans="5:10">
+      <c r="J424" s="48"/>
+    </row>
+    <row r="425" spans="5:10">
+      <c r="J425" s="48"/>
+    </row>
+    <row r="426" spans="5:10">
       <c r="E426" s="40"/>
-      <c r="G426" s="48"/>
-    </row>
-    <row r="427" spans="5:7">
-      <c r="G427" s="48"/>
-    </row>
-    <row r="428" spans="5:7">
-      <c r="G428" s="48"/>
-    </row>
-    <row r="429" spans="5:7">
-      <c r="G429" s="48"/>
-    </row>
-    <row r="430" spans="5:7">
-      <c r="G430" s="48"/>
-    </row>
-    <row r="431" spans="5:7">
-      <c r="G431" s="48"/>
-    </row>
-    <row r="432" spans="5:7">
-      <c r="G432" s="48"/>
-    </row>
-    <row r="433" spans="5:7">
-      <c r="G433" s="48"/>
-    </row>
-    <row r="434" spans="5:7">
+      <c r="J426" s="48"/>
+    </row>
+    <row r="427" spans="5:10">
+      <c r="J427" s="48"/>
+    </row>
+    <row r="428" spans="5:10">
+      <c r="J428" s="48"/>
+    </row>
+    <row r="429" spans="5:10">
+      <c r="J429" s="48"/>
+    </row>
+    <row r="430" spans="5:10">
+      <c r="J430" s="48"/>
+    </row>
+    <row r="431" spans="5:10">
+      <c r="J431" s="48"/>
+    </row>
+    <row r="432" spans="5:10">
+      <c r="J432" s="48"/>
+    </row>
+    <row r="433" spans="5:10">
+      <c r="J433" s="48"/>
+    </row>
+    <row r="434" spans="5:10">
       <c r="E434" s="40"/>
-      <c r="G434" s="48"/>
-    </row>
-    <row r="442" spans="5:7">
+      <c r="J434" s="48"/>
+    </row>
+    <row r="442" spans="5:10">
       <c r="E442" s="40"/>
     </row>
     <row r="449" spans="5:5">
@@ -5280,95 +5251,95 @@
     <row r="512" spans="5:5">
       <c r="E512" s="40"/>
     </row>
-    <row r="513" spans="5:7">
+    <row r="513" spans="5:10">
       <c r="E513" s="40"/>
     </row>
-    <row r="514" spans="5:7">
+    <row r="514" spans="5:10">
       <c r="E514" s="40"/>
     </row>
-    <row r="515" spans="5:7">
+    <row r="515" spans="5:10">
       <c r="E515" s="40"/>
     </row>
-    <row r="516" spans="5:7">
+    <row r="516" spans="5:10">
       <c r="E516" s="40"/>
     </row>
-    <row r="517" spans="5:7">
+    <row r="517" spans="5:10">
       <c r="E517" s="40"/>
     </row>
-    <row r="518" spans="5:7">
+    <row r="518" spans="5:10">
       <c r="E518" s="40"/>
     </row>
-    <row r="519" spans="5:7">
+    <row r="519" spans="5:10">
       <c r="E519" s="40"/>
     </row>
-    <row r="520" spans="5:7">
+    <row r="520" spans="5:10">
       <c r="E520" s="40"/>
     </row>
-    <row r="521" spans="5:7">
+    <row r="521" spans="5:10">
       <c r="E521" s="40"/>
     </row>
-    <row r="522" spans="5:7">
+    <row r="522" spans="5:10">
       <c r="E522" s="40"/>
     </row>
-    <row r="524" spans="5:7">
-      <c r="G524" s="48"/>
-    </row>
-    <row r="525" spans="5:7">
-      <c r="G525" s="48"/>
-    </row>
-    <row r="526" spans="5:7">
-      <c r="G526" s="48"/>
-    </row>
-    <row r="527" spans="5:7">
-      <c r="G527" s="48"/>
-    </row>
-    <row r="528" spans="5:7">
-      <c r="G528" s="48"/>
-    </row>
-    <row r="529" spans="5:7">
-      <c r="G529" s="48"/>
-    </row>
-    <row r="530" spans="5:7">
-      <c r="G530" s="48"/>
-    </row>
-    <row r="531" spans="5:7">
-      <c r="G531" s="48"/>
-    </row>
-    <row r="532" spans="5:7">
-      <c r="G532" s="48"/>
-    </row>
-    <row r="533" spans="5:7">
-      <c r="G533" s="48"/>
-    </row>
-    <row r="534" spans="5:7">
-      <c r="G534" s="48"/>
-    </row>
-    <row r="535" spans="5:7">
-      <c r="G535" s="48"/>
-    </row>
-    <row r="536" spans="5:7">
-      <c r="G536" s="48"/>
-    </row>
-    <row r="537" spans="5:7">
+    <row r="524" spans="5:10">
+      <c r="J524" s="48"/>
+    </row>
+    <row r="525" spans="5:10">
+      <c r="J525" s="48"/>
+    </row>
+    <row r="526" spans="5:10">
+      <c r="J526" s="48"/>
+    </row>
+    <row r="527" spans="5:10">
+      <c r="J527" s="48"/>
+    </row>
+    <row r="528" spans="5:10">
+      <c r="J528" s="48"/>
+    </row>
+    <row r="529" spans="5:10">
+      <c r="J529" s="48"/>
+    </row>
+    <row r="530" spans="5:10">
+      <c r="J530" s="48"/>
+    </row>
+    <row r="531" spans="5:10">
+      <c r="J531" s="48"/>
+    </row>
+    <row r="532" spans="5:10">
+      <c r="J532" s="48"/>
+    </row>
+    <row r="533" spans="5:10">
+      <c r="J533" s="48"/>
+    </row>
+    <row r="534" spans="5:10">
+      <c r="J534" s="48"/>
+    </row>
+    <row r="535" spans="5:10">
+      <c r="J535" s="48"/>
+    </row>
+    <row r="536" spans="5:10">
+      <c r="J536" s="48"/>
+    </row>
+    <row r="537" spans="5:10">
       <c r="E537" s="40"/>
-      <c r="G537" s="48"/>
-    </row>
-    <row r="539" spans="5:7">
+      <c r="J537" s="48"/>
+    </row>
+    <row r="539" spans="5:10">
       <c r="E539" s="40"/>
     </row>
-    <row r="540" spans="5:7">
+    <row r="540" spans="5:10">
       <c r="E540" s="40"/>
     </row>
-    <row r="541" spans="5:7">
+    <row r="541" spans="5:10">
       <c r="E541" s="40"/>
     </row>
-    <row r="542" spans="5:7">
+    <row r="542" spans="5:10">
       <c r="E542" s="40"/>
     </row>
-    <row r="543" spans="5:7">
+    <row r="543" spans="5:10">
       <c r="E543" s="40"/>
     </row>
-    <row r="544" spans="5:7">
+    <row r="544" spans="5:10">
       <c r="E544" s="40"/>
     </row>
     <row r="545" spans="5:5">
@@ -5467,428 +5438,428 @@
     <row r="576" spans="5:5">
       <c r="E576" s="40"/>
     </row>
-    <row r="577" spans="5:7">
+    <row r="577" spans="5:10">
       <c r="E577" s="40"/>
     </row>
-    <row r="578" spans="5:7">
+    <row r="578" spans="5:10">
       <c r="E578" s="40"/>
     </row>
-    <row r="579" spans="5:7">
+    <row r="579" spans="5:10">
       <c r="E579" s="40"/>
     </row>
-    <row r="580" spans="5:7">
+    <row r="580" spans="5:10">
       <c r="E580" s="40"/>
     </row>
-    <row r="581" spans="5:7">
+    <row r="581" spans="5:10">
       <c r="E581" s="40"/>
     </row>
-    <row r="582" spans="5:7">
+    <row r="582" spans="5:10">
       <c r="E582" s="40"/>
     </row>
-    <row r="583" spans="5:7">
+    <row r="583" spans="5:10">
       <c r="E583" s="40"/>
     </row>
-    <row r="584" spans="5:7">
+    <row r="584" spans="5:10">
       <c r="E584" s="40"/>
     </row>
-    <row r="585" spans="5:7">
+    <row r="585" spans="5:10">
       <c r="E585" s="40"/>
     </row>
-    <row r="586" spans="5:7">
+    <row r="586" spans="5:10">
       <c r="E586" s="40"/>
     </row>
-    <row r="588" spans="5:7">
+    <row r="588" spans="5:10">
       <c r="E588" s="40"/>
-      <c r="G588" s="48"/>
-    </row>
-    <row r="589" spans="5:7">
+      <c r="J588" s="48"/>
+    </row>
+    <row r="589" spans="5:10">
       <c r="E589" s="40"/>
-      <c r="G589" s="48"/>
-    </row>
-    <row r="590" spans="5:7">
+      <c r="J589" s="48"/>
+    </row>
+    <row r="590" spans="5:10">
       <c r="E590" s="40"/>
-      <c r="G590" s="48"/>
-    </row>
-    <row r="591" spans="5:7">
+      <c r="J590" s="48"/>
+    </row>
+    <row r="591" spans="5:10">
       <c r="E591" s="40"/>
-      <c r="G591" s="48"/>
-    </row>
-    <row r="592" spans="5:7">
+      <c r="J591" s="48"/>
+    </row>
+    <row r="592" spans="5:10">
       <c r="E592" s="40"/>
-      <c r="G592" s="48"/>
-    </row>
-    <row r="593" spans="5:7">
+      <c r="J592" s="48"/>
+    </row>
+    <row r="593" spans="5:10">
       <c r="E593" s="40"/>
-      <c r="G593" s="48"/>
-    </row>
-    <row r="594" spans="5:7">
+      <c r="J593" s="48"/>
+    </row>
+    <row r="594" spans="5:10">
       <c r="E594" s="40"/>
-      <c r="G594" s="48"/>
-    </row>
-    <row r="595" spans="5:7">
+      <c r="J594" s="48"/>
+    </row>
+    <row r="595" spans="5:10">
       <c r="E595" s="40"/>
-      <c r="G595" s="48"/>
-    </row>
-    <row r="596" spans="5:7">
+      <c r="J595" s="48"/>
+    </row>
+    <row r="596" spans="5:10">
       <c r="E596" s="40"/>
-      <c r="G596" s="48"/>
-    </row>
-    <row r="597" spans="5:7">
+      <c r="J596" s="48"/>
+    </row>
+    <row r="597" spans="5:10">
       <c r="E597" s="40"/>
-      <c r="G597" s="48"/>
-    </row>
-    <row r="598" spans="5:7">
+      <c r="J597" s="48"/>
+    </row>
+    <row r="598" spans="5:10">
       <c r="E598" s="40"/>
-      <c r="G598" s="48"/>
-    </row>
-    <row r="599" spans="5:7">
+      <c r="J598" s="48"/>
+    </row>
+    <row r="599" spans="5:10">
       <c r="E599" s="40"/>
-      <c r="G599" s="48"/>
-    </row>
-    <row r="600" spans="5:7">
+      <c r="J599" s="48"/>
+    </row>
+    <row r="600" spans="5:10">
       <c r="E600" s="40"/>
-      <c r="G600" s="48"/>
-    </row>
-    <row r="601" spans="5:7">
+      <c r="J600" s="48"/>
+    </row>
+    <row r="601" spans="5:10">
       <c r="E601" s="40"/>
-      <c r="G601" s="48"/>
-    </row>
-    <row r="602" spans="5:7">
+      <c r="J601" s="48"/>
+    </row>
+    <row r="602" spans="5:10">
       <c r="E602" s="40"/>
-      <c r="G602" s="48"/>
-    </row>
-    <row r="603" spans="5:7">
+      <c r="J602" s="48"/>
+    </row>
+    <row r="603" spans="5:10">
       <c r="E603" s="40"/>
-      <c r="G603" s="48"/>
-    </row>
-    <row r="604" spans="5:7">
+      <c r="J603" s="48"/>
+    </row>
+    <row r="604" spans="5:10">
       <c r="E604" s="40"/>
-      <c r="G604" s="48"/>
-    </row>
-    <row r="605" spans="5:7">
+      <c r="J604" s="48"/>
+    </row>
+    <row r="605" spans="5:10">
       <c r="E605" s="40"/>
-      <c r="G605" s="48"/>
-    </row>
-    <row r="606" spans="5:7">
+      <c r="J605" s="48"/>
+    </row>
+    <row r="606" spans="5:10">
       <c r="E606" s="40"/>
-      <c r="G606" s="48"/>
-    </row>
-    <row r="607" spans="5:7">
+      <c r="J606" s="48"/>
+    </row>
+    <row r="607" spans="5:10">
       <c r="E607" s="40"/>
-      <c r="G607" s="48"/>
-    </row>
-    <row r="608" spans="5:7">
+      <c r="J607" s="48"/>
+    </row>
+    <row r="608" spans="5:10">
       <c r="E608" s="40"/>
-      <c r="G608" s="48"/>
-    </row>
-    <row r="609" spans="5:7">
+      <c r="J608" s="48"/>
+    </row>
+    <row r="609" spans="5:10">
       <c r="E609" s="40"/>
-      <c r="G609" s="48"/>
-    </row>
-    <row r="610" spans="5:7">
+      <c r="J609" s="48"/>
+    </row>
+    <row r="610" spans="5:10">
       <c r="E610" s="40"/>
-      <c r="G610" s="48"/>
-    </row>
-    <row r="611" spans="5:7">
+      <c r="J610" s="48"/>
+    </row>
+    <row r="611" spans="5:10">
       <c r="E611" s="40"/>
-      <c r="G611" s="48"/>
-    </row>
-    <row r="612" spans="5:7">
+      <c r="J611" s="48"/>
+    </row>
+    <row r="612" spans="5:10">
       <c r="E612" s="40"/>
-      <c r="G612" s="48"/>
-    </row>
-    <row r="613" spans="5:7">
+      <c r="J612" s="48"/>
+    </row>
+    <row r="613" spans="5:10">
       <c r="E613" s="40"/>
-      <c r="G613" s="48"/>
-    </row>
-    <row r="614" spans="5:7">
+      <c r="J613" s="48"/>
+    </row>
+    <row r="614" spans="5:10">
       <c r="E614" s="40"/>
-      <c r="G614" s="48"/>
-    </row>
-    <row r="615" spans="5:7">
+      <c r="J614" s="48"/>
+    </row>
+    <row r="615" spans="5:10">
       <c r="E615" s="40"/>
-      <c r="G615" s="48"/>
-    </row>
-    <row r="616" spans="5:7">
+      <c r="J615" s="48"/>
+    </row>
+    <row r="616" spans="5:10">
       <c r="E616" s="40"/>
-      <c r="G616" s="48"/>
-    </row>
-    <row r="617" spans="5:7">
+      <c r="J616" s="48"/>
+    </row>
+    <row r="617" spans="5:10">
       <c r="E617" s="40"/>
-      <c r="G617" s="48"/>
-    </row>
-    <row r="618" spans="5:7">
+      <c r="J617" s="48"/>
+    </row>
+    <row r="618" spans="5:10">
       <c r="E618" s="40"/>
-      <c r="G618" s="48"/>
-    </row>
-    <row r="619" spans="5:7">
+      <c r="J618" s="48"/>
+    </row>
+    <row r="619" spans="5:10">
       <c r="E619" s="40"/>
-      <c r="G619" s="48"/>
-    </row>
-    <row r="620" spans="5:7">
+      <c r="J619" s="48"/>
+    </row>
+    <row r="620" spans="5:10">
       <c r="E620" s="40"/>
-      <c r="G620" s="48"/>
-    </row>
-    <row r="621" spans="5:7">
+      <c r="J620" s="48"/>
+    </row>
+    <row r="621" spans="5:10">
       <c r="E621" s="40"/>
-      <c r="G621" s="48"/>
-    </row>
-    <row r="622" spans="5:7">
+      <c r="J621" s="48"/>
+    </row>
+    <row r="622" spans="5:10">
       <c r="E622" s="40"/>
-      <c r="G622" s="48"/>
-    </row>
-    <row r="623" spans="5:7">
+      <c r="J622" s="48"/>
+    </row>
+    <row r="623" spans="5:10">
       <c r="E623" s="40"/>
-      <c r="G623" s="48"/>
-    </row>
-    <row r="624" spans="5:7">
+      <c r="J623" s="48"/>
+    </row>
+    <row r="624" spans="5:10">
       <c r="E624" s="40"/>
-      <c r="G624" s="48"/>
-    </row>
-    <row r="625" spans="5:7">
+      <c r="J624" s="48"/>
+    </row>
+    <row r="625" spans="5:10">
       <c r="E625" s="40"/>
-      <c r="G625" s="48"/>
-    </row>
-    <row r="626" spans="5:7">
+      <c r="J625" s="48"/>
+    </row>
+    <row r="626" spans="5:10">
       <c r="E626" s="40"/>
-      <c r="G626" s="48"/>
-    </row>
-    <row r="627" spans="5:7">
+      <c r="J626" s="48"/>
+    </row>
+    <row r="627" spans="5:10">
       <c r="E627" s="40"/>
-      <c r="G627" s="48"/>
-    </row>
-    <row r="628" spans="5:7">
+      <c r="J627" s="48"/>
+    </row>
+    <row r="628" spans="5:10">
       <c r="E628" s="40"/>
-      <c r="G628" s="48"/>
-    </row>
-    <row r="629" spans="5:7">
+      <c r="J628" s="48"/>
+    </row>
+    <row r="629" spans="5:10">
       <c r="E629" s="40"/>
-      <c r="G629" s="48"/>
-    </row>
-    <row r="630" spans="5:7">
+      <c r="J629" s="48"/>
+    </row>
+    <row r="630" spans="5:10">
       <c r="E630" s="40"/>
-      <c r="G630" s="48"/>
-    </row>
-    <row r="631" spans="5:7">
+      <c r="J630" s="48"/>
+    </row>
+    <row r="631" spans="5:10">
       <c r="E631" s="40"/>
-      <c r="G631" s="48"/>
-    </row>
-    <row r="632" spans="5:7">
+      <c r="J631" s="48"/>
+    </row>
+    <row r="632" spans="5:10">
       <c r="E632" s="40"/>
-      <c r="G632" s="48"/>
-    </row>
-    <row r="633" spans="5:7">
+      <c r="J632" s="48"/>
+    </row>
+    <row r="633" spans="5:10">
       <c r="E633" s="40"/>
-      <c r="G633" s="48"/>
-    </row>
-    <row r="634" spans="5:7">
+      <c r="J633" s="48"/>
+    </row>
+    <row r="634" spans="5:10">
       <c r="E634" s="40"/>
-      <c r="G634" s="48"/>
-    </row>
-    <row r="635" spans="5:7">
+      <c r="J634" s="48"/>
+    </row>
+    <row r="635" spans="5:10">
       <c r="E635" s="40"/>
-      <c r="G635" s="48"/>
-    </row>
-    <row r="645" spans="5:7">
+      <c r="J635" s="48"/>
+    </row>
+    <row r="645" spans="5:10">
       <c r="E645" s="40"/>
     </row>
-    <row r="656" spans="5:7">
-      <c r="G656" s="48"/>
-    </row>
-    <row r="657" spans="7:7">
-      <c r="G657" s="48"/>
-    </row>
-    <row r="658" spans="7:7">
-      <c r="G658" s="48"/>
-    </row>
-    <row r="659" spans="7:7">
-      <c r="G659" s="48"/>
-    </row>
-    <row r="660" spans="7:7">
-      <c r="G660" s="48"/>
-    </row>
-    <row r="661" spans="7:7">
-      <c r="G661" s="48"/>
-    </row>
-    <row r="662" spans="7:7">
-      <c r="G662" s="48"/>
-    </row>
-    <row r="663" spans="7:7">
-      <c r="G663" s="48"/>
-    </row>
-    <row r="664" spans="7:7">
-      <c r="G664" s="48"/>
-    </row>
-    <row r="665" spans="7:7">
-      <c r="G665" s="48"/>
-    </row>
-    <row r="666" spans="7:7">
-      <c r="G666" s="48"/>
-    </row>
-    <row r="667" spans="7:7">
-      <c r="G667" s="48"/>
-    </row>
-    <row r="668" spans="7:7">
-      <c r="G668" s="48"/>
-    </row>
-    <row r="669" spans="7:7">
-      <c r="G669" s="48"/>
-    </row>
-    <row r="670" spans="7:7">
-      <c r="G670" s="48"/>
-    </row>
-    <row r="671" spans="7:7">
-      <c r="G671" s="48"/>
-    </row>
-    <row r="672" spans="7:7">
-      <c r="G672" s="48"/>
-    </row>
-    <row r="673" spans="5:7">
-      <c r="G673" s="48"/>
-    </row>
-    <row r="674" spans="5:7">
-      <c r="G674" s="48"/>
-    </row>
-    <row r="675" spans="5:7">
+    <row r="656" spans="5:10">
+      <c r="J656" s="48"/>
+    </row>
+    <row r="657" spans="10:10">
+      <c r="J657" s="48"/>
+    </row>
+    <row r="658" spans="10:10">
+      <c r="J658" s="48"/>
+    </row>
+    <row r="659" spans="10:10">
+      <c r="J659" s="48"/>
+    </row>
+    <row r="660" spans="10:10">
+      <c r="J660" s="48"/>
+    </row>
+    <row r="661" spans="10:10">
+      <c r="J661" s="48"/>
+    </row>
+    <row r="662" spans="10:10">
+      <c r="J662" s="48"/>
+    </row>
+    <row r="663" spans="10:10">
+      <c r="J663" s="48"/>
+    </row>
+    <row r="664" spans="10:10">
+      <c r="J664" s="48"/>
+    </row>
+    <row r="665" spans="10:10">
+      <c r="J665" s="48"/>
+    </row>
+    <row r="666" spans="10:10">
+      <c r="J666" s="48"/>
+    </row>
+    <row r="667" spans="10:10">
+      <c r="J667" s="48"/>
+    </row>
+    <row r="668" spans="10:10">
+      <c r="J668" s="48"/>
+    </row>
+    <row r="669" spans="10:10">
+      <c r="J669" s="48"/>
+    </row>
+    <row r="670" spans="10:10">
+      <c r="J670" s="48"/>
+    </row>
+    <row r="671" spans="10:10">
+      <c r="J671" s="48"/>
+    </row>
+    <row r="672" spans="10:10">
+      <c r="J672" s="48"/>
+    </row>
+    <row r="673" spans="5:10">
+      <c r="J673" s="48"/>
+    </row>
+    <row r="674" spans="5:10">
+      <c r="J674" s="48"/>
+    </row>
+    <row r="675" spans="5:10">
       <c r="E675" s="40"/>
-      <c r="G675" s="48"/>
-    </row>
-    <row r="685" spans="5:7">
+      <c r="J675" s="48"/>
+    </row>
+    <row r="685" spans="5:10">
       <c r="E685" s="40"/>
     </row>
-    <row r="696" spans="5:7">
+    <row r="696" spans="5:10">
       <c r="E696" s="40"/>
-      <c r="G696" s="48"/>
-    </row>
-    <row r="697" spans="5:7">
+      <c r="J696" s="48"/>
+    </row>
+    <row r="697" spans="5:10">
       <c r="E697" s="40"/>
-      <c r="G697" s="48"/>
-    </row>
-    <row r="698" spans="5:7">
+      <c r="J697" s="48"/>
+    </row>
+    <row r="698" spans="5:10">
       <c r="E698" s="40"/>
-      <c r="G698" s="48"/>
-    </row>
-    <row r="699" spans="5:7">
+      <c r="J698" s="48"/>
+    </row>
+    <row r="699" spans="5:10">
       <c r="E699" s="40"/>
-      <c r="G699" s="48"/>
-    </row>
-    <row r="700" spans="5:7">
+      <c r="J699" s="48"/>
+    </row>
+    <row r="700" spans="5:10">
       <c r="E700" s="40"/>
-      <c r="G700" s="48"/>
-    </row>
-    <row r="701" spans="5:7">
+      <c r="J700" s="48"/>
+    </row>
+    <row r="701" spans="5:10">
       <c r="E701" s="40"/>
-      <c r="G701" s="48"/>
-    </row>
-    <row r="702" spans="5:7">
+      <c r="J701" s="48"/>
+    </row>
+    <row r="702" spans="5:10">
       <c r="E702" s="40"/>
-      <c r="G702" s="48"/>
-    </row>
-    <row r="703" spans="5:7">
+      <c r="J702" s="48"/>
+    </row>
+    <row r="703" spans="5:10">
       <c r="E703" s="40"/>
-      <c r="G703" s="48"/>
-    </row>
-    <row r="704" spans="5:7">
+      <c r="J703" s="48"/>
+    </row>
+    <row r="704" spans="5:10">
       <c r="E704" s="40"/>
-      <c r="G704" s="48"/>
-    </row>
-    <row r="705" spans="5:7">
+      <c r="J704" s="48"/>
+    </row>
+    <row r="705" spans="5:10">
       <c r="E705" s="40"/>
-      <c r="G705" s="48"/>
-    </row>
-    <row r="706" spans="5:7">
+      <c r="J705" s="48"/>
+    </row>
+    <row r="706" spans="5:10">
       <c r="E706" s="40"/>
-      <c r="G706" s="48"/>
-    </row>
-    <row r="707" spans="5:7">
+      <c r="J706" s="48"/>
+    </row>
+    <row r="707" spans="5:10">
       <c r="E707" s="40"/>
-      <c r="G707" s="48"/>
-    </row>
-    <row r="708" spans="5:7">
+      <c r="J707" s="48"/>
+    </row>
+    <row r="708" spans="5:10">
       <c r="E708" s="40"/>
-      <c r="G708" s="48"/>
-    </row>
-    <row r="709" spans="5:7">
+      <c r="J708" s="48"/>
+    </row>
+    <row r="709" spans="5:10">
       <c r="E709" s="40"/>
-      <c r="G709" s="48"/>
-    </row>
-    <row r="710" spans="5:7">
+      <c r="J709" s="48"/>
+    </row>
+    <row r="710" spans="5:10">
       <c r="E710" s="40"/>
-      <c r="G710" s="48"/>
-    </row>
-    <row r="711" spans="5:7">
+      <c r="J710" s="48"/>
+    </row>
+    <row r="711" spans="5:10">
       <c r="E711" s="40"/>
-      <c r="G711" s="48"/>
-    </row>
-    <row r="713" spans="5:7">
+      <c r="J711" s="48"/>
+    </row>
+    <row r="713" spans="5:10">
       <c r="E713" s="40"/>
-      <c r="G713" s="48"/>
-    </row>
-    <row r="714" spans="5:7">
+      <c r="J713" s="48"/>
+    </row>
+    <row r="714" spans="5:10">
       <c r="E714" s="40"/>
-      <c r="G714" s="48"/>
-    </row>
-    <row r="715" spans="5:7">
+      <c r="J714" s="48"/>
+    </row>
+    <row r="715" spans="5:10">
       <c r="E715" s="40"/>
-      <c r="G715" s="48"/>
-    </row>
-    <row r="716" spans="5:7">
+      <c r="J715" s="48"/>
+    </row>
+    <row r="716" spans="5:10">
       <c r="E716" s="40"/>
-      <c r="G716" s="48"/>
-    </row>
-    <row r="717" spans="5:7">
+      <c r="J716" s="48"/>
+    </row>
+    <row r="717" spans="5:10">
       <c r="E717" s="40"/>
-      <c r="G717" s="48"/>
-    </row>
-    <row r="718" spans="5:7">
+      <c r="J717" s="48"/>
+    </row>
+    <row r="718" spans="5:10">
       <c r="E718" s="40"/>
-      <c r="G718" s="48"/>
-    </row>
-    <row r="719" spans="5:7">
+      <c r="J718" s="48"/>
+    </row>
+    <row r="719" spans="5:10">
       <c r="E719" s="40"/>
-      <c r="G719" s="48"/>
-    </row>
-    <row r="720" spans="5:7">
+      <c r="J719" s="48"/>
+    </row>
+    <row r="720" spans="5:10">
       <c r="E720" s="40"/>
-      <c r="G720" s="48"/>
-    </row>
-    <row r="721" spans="5:7">
+      <c r="J720" s="48"/>
+    </row>
+    <row r="721" spans="5:10">
       <c r="E721" s="40"/>
-      <c r="G721" s="48"/>
-    </row>
-    <row r="722" spans="5:7">
+      <c r="J721" s="48"/>
+    </row>
+    <row r="722" spans="5:10">
       <c r="E722" s="40"/>
-      <c r="G722" s="48"/>
-    </row>
-    <row r="723" spans="5:7">
+      <c r="J722" s="48"/>
+    </row>
+    <row r="723" spans="5:10">
       <c r="E723" s="40"/>
-      <c r="G723" s="48"/>
-    </row>
-    <row r="724" spans="5:7">
+      <c r="J723" s="48"/>
+    </row>
+    <row r="724" spans="5:10">
       <c r="E724" s="40"/>
-      <c r="G724" s="48"/>
-    </row>
-    <row r="725" spans="5:7">
+      <c r="J724" s="48"/>
+    </row>
+    <row r="725" spans="5:10">
       <c r="E725" s="40"/>
-      <c r="G725" s="48"/>
-    </row>
-    <row r="726" spans="5:7">
+      <c r="J725" s="48"/>
+    </row>
+    <row r="726" spans="5:10">
       <c r="E726" s="40"/>
-      <c r="G726" s="48"/>
-    </row>
-    <row r="729" spans="5:7">
+      <c r="J726" s="48"/>
+    </row>
+    <row r="729" spans="5:10">
       <c r="E729" s="40"/>
     </row>
-    <row r="733" spans="5:7">
+    <row r="733" spans="5:10">
       <c r="E733" s="40"/>
     </row>
-    <row r="734" spans="5:7">
+    <row r="734" spans="5:10">
       <c r="E734" s="40"/>
     </row>
-    <row r="735" spans="5:7">
+    <row r="735" spans="5:10">
       <c r="E735" s="40"/>
     </row>
-    <row r="736" spans="5:7">
+    <row r="736" spans="5:10">
       <c r="E736" s="40"/>
     </row>
     <row r="739" spans="5:5">
@@ -6182,8 +6153,19 @@
     <row r="920" spans="5:5">
       <c r="E920" s="40"/>
     </row>
-    <row r="929" spans="5:5">
+    <row r="929" spans="5:8">
       <c r="E929" s="40"/>
+    </row>
+    <row r="940" spans="5:8">
+      <c r="F940" s="40"/>
+      <c r="H940" s="40"/>
+    </row>
+    <row r="941" spans="5:8">
+      <c r="F941" s="40"/>
+    </row>
+    <row r="942" spans="5:8">
+      <c r="F942" s="40"/>
+      <c r="H942" s="40"/>
     </row>
     <row r="946" spans="5:5">
       <c r="E946" s="40"/>
@@ -6197,7 +6179,10 @@
     <row r="997" spans="5:5">
       <c r="E997" s="40"/>
     </row>
-    <row r="1014" spans="5:5">
+    <row r="1011" spans="5:8">
+      <c r="H1011" s="55"/>
+    </row>
+    <row r="1014" spans="5:8">
       <c r="E1014" s="40"/>
     </row>
     <row r="1031" spans="5:5">
@@ -6230,48 +6215,48 @@
     <row r="1184" spans="5:5">
       <c r="E1184" s="40"/>
     </row>
-    <row r="1194" spans="7:7">
-      <c r="G1194" s="48"/>
-    </row>
-    <row r="1195" spans="7:7">
-      <c r="G1195" s="48"/>
-    </row>
-    <row r="1196" spans="7:7">
-      <c r="G1196" s="48"/>
-    </row>
-    <row r="1197" spans="7:7">
-      <c r="G1197" s="48"/>
-    </row>
-    <row r="1198" spans="7:7">
-      <c r="G1198" s="48"/>
-    </row>
-    <row r="1199" spans="7:7">
-      <c r="G1199" s="48"/>
-    </row>
-    <row r="1200" spans="7:7">
-      <c r="G1200" s="48"/>
-    </row>
-    <row r="1201" spans="5:7">
-      <c r="G1201" s="48"/>
-    </row>
-    <row r="1202" spans="5:7">
-      <c r="G1202" s="48"/>
-    </row>
-    <row r="1203" spans="5:7">
-      <c r="G1203" s="48"/>
-    </row>
-    <row r="1204" spans="5:7">
-      <c r="G1204" s="48"/>
-    </row>
-    <row r="1205" spans="5:7">
-      <c r="G1205" s="48"/>
-    </row>
-    <row r="1206" spans="5:7">
-      <c r="G1206" s="48"/>
-    </row>
-    <row r="1207" spans="5:7">
+    <row r="1194" spans="10:10">
+      <c r="J1194" s="48"/>
+    </row>
+    <row r="1195" spans="10:10">
+      <c r="J1195" s="48"/>
+    </row>
+    <row r="1196" spans="10:10">
+      <c r="J1196" s="48"/>
+    </row>
+    <row r="1197" spans="10:10">
+      <c r="J1197" s="48"/>
+    </row>
+    <row r="1198" spans="10:10">
+      <c r="J1198" s="48"/>
+    </row>
+    <row r="1199" spans="10:10">
+      <c r="J1199" s="48"/>
+    </row>
+    <row r="1200" spans="10:10">
+      <c r="J1200" s="48"/>
+    </row>
+    <row r="1201" spans="5:10">
+      <c r="J1201" s="48"/>
+    </row>
+    <row r="1202" spans="5:10">
+      <c r="J1202" s="48"/>
+    </row>
+    <row r="1203" spans="5:10">
+      <c r="J1203" s="48"/>
+    </row>
+    <row r="1204" spans="5:10">
+      <c r="J1204" s="48"/>
+    </row>
+    <row r="1205" spans="5:10">
+      <c r="J1205" s="48"/>
+    </row>
+    <row r="1206" spans="5:10">
+      <c r="J1206" s="48"/>
+    </row>
+    <row r="1207" spans="5:10">
       <c r="E1207" s="40"/>
-      <c r="G1207" s="48"/>
+      <c r="J1207" s="48"/>
     </row>
     <row r="1228" spans="5:5">
       <c r="E1228" s="40"/>
@@ -6288,69 +6273,69 @@
     <row r="1289" spans="5:5">
       <c r="E1289" s="40"/>
     </row>
-    <row r="1297" spans="5:7">
+    <row r="1297" spans="5:10">
       <c r="E1297" s="40"/>
     </row>
-    <row r="1306" spans="5:7">
-      <c r="G1306" s="48"/>
-    </row>
-    <row r="1307" spans="5:7">
-      <c r="G1307" s="48"/>
-    </row>
-    <row r="1308" spans="5:7">
-      <c r="G1308" s="48"/>
-    </row>
-    <row r="1309" spans="5:7">
-      <c r="G1309" s="48"/>
-    </row>
-    <row r="1310" spans="5:7">
-      <c r="G1310" s="48"/>
-    </row>
-    <row r="1311" spans="5:7">
-      <c r="G1311" s="48"/>
-    </row>
-    <row r="1312" spans="5:7">
-      <c r="G1312" s="48"/>
-    </row>
-    <row r="1313" spans="5:7">
-      <c r="G1313" s="48"/>
-    </row>
-    <row r="1314" spans="5:7">
-      <c r="G1314" s="48"/>
-    </row>
-    <row r="1315" spans="5:7">
-      <c r="G1315" s="48"/>
-    </row>
-    <row r="1316" spans="5:7">
-      <c r="G1316" s="48"/>
-    </row>
-    <row r="1317" spans="5:7">
-      <c r="G1317" s="48"/>
-    </row>
-    <row r="1318" spans="5:7">
-      <c r="G1318" s="48"/>
-    </row>
-    <row r="1319" spans="5:7">
-      <c r="G1319" s="48"/>
-    </row>
-    <row r="1320" spans="5:7">
-      <c r="G1320" s="48"/>
-    </row>
-    <row r="1321" spans="5:7">
-      <c r="G1321" s="48"/>
-    </row>
-    <row r="1322" spans="5:7">
-      <c r="G1322" s="48"/>
-    </row>
-    <row r="1323" spans="5:7">
-      <c r="G1323" s="48"/>
-    </row>
-    <row r="1324" spans="5:7">
-      <c r="G1324" s="48"/>
-    </row>
-    <row r="1325" spans="5:7">
+    <row r="1306" spans="5:10">
+      <c r="J1306" s="48"/>
+    </row>
+    <row r="1307" spans="5:10">
+      <c r="J1307" s="48"/>
+    </row>
+    <row r="1308" spans="5:10">
+      <c r="J1308" s="48"/>
+    </row>
+    <row r="1309" spans="5:10">
+      <c r="J1309" s="48"/>
+    </row>
+    <row r="1310" spans="5:10">
+      <c r="J1310" s="48"/>
+    </row>
+    <row r="1311" spans="5:10">
+      <c r="J1311" s="48"/>
+    </row>
+    <row r="1312" spans="5:10">
+      <c r="J1312" s="48"/>
+    </row>
+    <row r="1313" spans="5:10">
+      <c r="J1313" s="48"/>
+    </row>
+    <row r="1314" spans="5:10">
+      <c r="J1314" s="48"/>
+    </row>
+    <row r="1315" spans="5:10">
+      <c r="J1315" s="48"/>
+    </row>
+    <row r="1316" spans="5:10">
+      <c r="J1316" s="48"/>
+    </row>
+    <row r="1317" spans="5:10">
+      <c r="J1317" s="48"/>
+    </row>
+    <row r="1318" spans="5:10">
+      <c r="J1318" s="48"/>
+    </row>
+    <row r="1319" spans="5:10">
+      <c r="J1319" s="48"/>
+    </row>
+    <row r="1320" spans="5:10">
+      <c r="J1320" s="48"/>
+    </row>
+    <row r="1321" spans="5:10">
+      <c r="J1321" s="48"/>
+    </row>
+    <row r="1322" spans="5:10">
+      <c r="J1322" s="48"/>
+    </row>
+    <row r="1323" spans="5:10">
+      <c r="J1323" s="48"/>
+    </row>
+    <row r="1324" spans="5:10">
+      <c r="J1324" s="48"/>
+    </row>
+    <row r="1325" spans="5:10">
       <c r="E1325" s="40"/>
-      <c r="G1325" s="48"/>
+      <c r="J1325" s="48"/>
     </row>
     <row r="1333" spans="5:5">
       <c r="E1333" s="40"/>
@@ -6358,8 +6343,1133 @@
     <row r="1340" spans="5:5">
       <c r="E1340" s="40"/>
     </row>
+    <row r="1665" spans="6:8">
+      <c r="H1665" s="40"/>
+    </row>
+    <row r="1666" spans="6:8">
+      <c r="F1666" s="40"/>
+      <c r="H1666" s="40"/>
+    </row>
+    <row r="1667" spans="6:8">
+      <c r="F1667" s="40"/>
+      <c r="H1667" s="40"/>
+    </row>
+    <row r="1668" spans="6:8">
+      <c r="F1668" s="40"/>
+      <c r="H1668" s="40"/>
+    </row>
+    <row r="1669" spans="6:8">
+      <c r="F1669" s="40"/>
+      <c r="H1669" s="40"/>
+    </row>
+    <row r="1670" spans="6:8">
+      <c r="F1670" s="40"/>
+      <c r="H1670" s="40"/>
+    </row>
+    <row r="1671" spans="6:8">
+      <c r="F1671" s="40"/>
+      <c r="H1671" s="40"/>
+    </row>
+    <row r="1672" spans="6:8">
+      <c r="F1672" s="40"/>
+      <c r="H1672" s="40"/>
+    </row>
+    <row r="1673" spans="6:8">
+      <c r="H1673" s="40"/>
+    </row>
+    <row r="1675" spans="6:8">
+      <c r="H1675" s="40"/>
+    </row>
+    <row r="1677" spans="6:8">
+      <c r="H1677" s="40"/>
+    </row>
+    <row r="1679" spans="6:8">
+      <c r="H1679" s="40"/>
+    </row>
+    <row r="1681" spans="6:8">
+      <c r="H1681" s="40"/>
+    </row>
+    <row r="1682" spans="6:8">
+      <c r="F1682" s="40"/>
+      <c r="H1682" s="40"/>
+    </row>
+    <row r="1683" spans="6:8">
+      <c r="H1683" s="40"/>
+    </row>
+    <row r="1684" spans="6:8">
+      <c r="F1684" s="40"/>
+      <c r="H1684" s="42"/>
+    </row>
+    <row r="1685" spans="6:8">
+      <c r="H1685" s="40"/>
+    </row>
+    <row r="1686" spans="6:8">
+      <c r="F1686" s="41"/>
+      <c r="H1686" s="42"/>
+    </row>
+    <row r="1687" spans="6:8">
+      <c r="F1687" s="40"/>
+      <c r="H1687" s="40"/>
+    </row>
+    <row r="1688" spans="6:8">
+      <c r="F1688" s="40"/>
+      <c r="H1688" s="42"/>
+    </row>
+    <row r="1689" spans="6:8">
+      <c r="F1689" s="40"/>
+      <c r="H1689" s="40"/>
+    </row>
+    <row r="1690" spans="6:8">
+      <c r="F1690" s="40"/>
+      <c r="H1690" s="42"/>
+    </row>
+    <row r="1691" spans="6:8">
+      <c r="F1691" s="40"/>
+      <c r="H1691" s="40"/>
+    </row>
+    <row r="1692" spans="6:8">
+      <c r="F1692" s="42"/>
+      <c r="H1692" s="42"/>
+    </row>
+    <row r="1693" spans="6:8">
+      <c r="F1693" s="40"/>
+      <c r="G1693" s="40"/>
+      <c r="H1693" s="40"/>
+    </row>
+    <row r="1694" spans="6:8">
+      <c r="F1694" s="40"/>
+      <c r="G1694" s="40"/>
+      <c r="H1694" s="40"/>
+    </row>
+    <row r="1695" spans="6:8">
+      <c r="F1695" s="40"/>
+      <c r="G1695" s="40"/>
+      <c r="H1695" s="40"/>
+    </row>
+    <row r="1696" spans="6:8">
+      <c r="F1696" s="40"/>
+      <c r="G1696" s="40"/>
+      <c r="H1696" s="40"/>
+    </row>
+    <row r="1697" spans="6:8">
+      <c r="F1697" s="40"/>
+      <c r="G1697" s="40"/>
+      <c r="H1697" s="40"/>
+    </row>
+    <row r="1698" spans="6:8">
+      <c r="F1698" s="40"/>
+      <c r="G1698" s="40"/>
+      <c r="H1698" s="40"/>
+    </row>
+    <row r="1699" spans="6:8">
+      <c r="F1699" s="40"/>
+      <c r="G1699" s="40"/>
+      <c r="H1699" s="40"/>
+    </row>
+    <row r="1700" spans="6:8">
+      <c r="F1700" s="40"/>
+      <c r="G1700" s="40"/>
+      <c r="H1700" s="40"/>
+    </row>
+    <row r="1701" spans="6:8">
+      <c r="F1701" s="40"/>
+      <c r="G1701" s="40"/>
+      <c r="H1701" s="40"/>
+    </row>
+    <row r="1702" spans="6:8">
+      <c r="F1702" s="40"/>
+      <c r="G1702" s="40"/>
+      <c r="H1702" s="40"/>
+    </row>
+    <row r="1703" spans="6:8">
+      <c r="F1703" s="40"/>
+      <c r="G1703" s="40"/>
+      <c r="H1703" s="40"/>
+    </row>
+    <row r="1704" spans="6:8">
+      <c r="F1704" s="40"/>
+      <c r="G1704" s="40"/>
+      <c r="H1704" s="40"/>
+    </row>
+    <row r="1705" spans="6:8">
+      <c r="F1705" s="40"/>
+      <c r="G1705" s="40"/>
+      <c r="H1705" s="40"/>
+    </row>
+    <row r="1706" spans="6:8">
+      <c r="F1706" s="40"/>
+      <c r="G1706" s="40"/>
+      <c r="H1706" s="40"/>
+    </row>
+    <row r="1707" spans="6:8">
+      <c r="F1707" s="40"/>
+      <c r="G1707" s="40"/>
+      <c r="H1707" s="40"/>
+    </row>
+    <row r="1708" spans="6:8">
+      <c r="F1708" s="40"/>
+      <c r="G1708" s="40"/>
+      <c r="H1708" s="40"/>
+    </row>
+    <row r="1709" spans="6:8">
+      <c r="F1709" s="40"/>
+      <c r="G1709" s="40"/>
+      <c r="H1709" s="40"/>
+    </row>
+    <row r="1710" spans="6:8">
+      <c r="F1710" s="40"/>
+      <c r="G1710" s="40"/>
+      <c r="H1710" s="40"/>
+    </row>
+    <row r="1711" spans="6:8">
+      <c r="F1711" s="40"/>
+      <c r="G1711" s="40"/>
+      <c r="H1711" s="40"/>
+    </row>
+    <row r="1712" spans="6:8">
+      <c r="F1712" s="40"/>
+      <c r="G1712" s="40"/>
+      <c r="H1712" s="40"/>
+    </row>
+    <row r="1713" spans="6:8">
+      <c r="F1713" s="40"/>
+      <c r="G1713" s="40"/>
+      <c r="H1713" s="40"/>
+    </row>
+    <row r="1714" spans="6:8">
+      <c r="F1714" s="40"/>
+      <c r="G1714" s="40"/>
+      <c r="H1714" s="40"/>
+    </row>
+    <row r="1715" spans="6:8">
+      <c r="F1715" s="40"/>
+      <c r="G1715" s="40"/>
+      <c r="H1715" s="40"/>
+    </row>
+    <row r="1716" spans="6:8">
+      <c r="F1716" s="40"/>
+      <c r="G1716" s="40"/>
+      <c r="H1716" s="40"/>
+    </row>
+    <row r="1717" spans="6:8">
+      <c r="F1717" s="40"/>
+      <c r="G1717" s="40"/>
+      <c r="H1717" s="40"/>
+    </row>
+    <row r="1718" spans="6:8">
+      <c r="F1718" s="40"/>
+      <c r="G1718" s="40"/>
+      <c r="H1718" s="40"/>
+    </row>
+    <row r="1719" spans="6:8">
+      <c r="F1719" s="40"/>
+      <c r="G1719" s="40"/>
+      <c r="H1719" s="40"/>
+    </row>
+    <row r="1720" spans="6:8">
+      <c r="F1720" s="40"/>
+      <c r="G1720" s="40"/>
+      <c r="H1720" s="40"/>
+    </row>
+    <row r="1721" spans="6:8">
+      <c r="F1721" s="40"/>
+      <c r="G1721" s="40"/>
+      <c r="H1721" s="40"/>
+    </row>
+    <row r="1722" spans="6:8">
+      <c r="F1722" s="40"/>
+      <c r="G1722" s="40"/>
+      <c r="H1722" s="40"/>
+    </row>
+    <row r="1723" spans="6:8">
+      <c r="F1723" s="40"/>
+      <c r="G1723" s="40"/>
+      <c r="H1723" s="40"/>
+    </row>
+    <row r="1724" spans="6:8">
+      <c r="F1724" s="40"/>
+      <c r="G1724" s="40"/>
+      <c r="H1724" s="40"/>
+    </row>
+    <row r="1725" spans="6:8">
+      <c r="F1725" s="40"/>
+      <c r="G1725" s="40"/>
+      <c r="H1725" s="40"/>
+    </row>
+    <row r="1726" spans="6:8">
+      <c r="F1726" s="40"/>
+      <c r="G1726" s="40"/>
+      <c r="H1726" s="40"/>
+    </row>
+    <row r="1727" spans="6:8">
+      <c r="F1727" s="40"/>
+      <c r="G1727" s="40"/>
+      <c r="H1727" s="40"/>
+    </row>
+    <row r="1728" spans="6:8">
+      <c r="F1728" s="40"/>
+      <c r="G1728" s="40"/>
+      <c r="H1728" s="40"/>
+    </row>
+    <row r="1729" spans="6:8">
+      <c r="F1729" s="40"/>
+      <c r="G1729" s="40"/>
+      <c r="H1729" s="40"/>
+    </row>
+    <row r="1730" spans="6:8">
+      <c r="F1730" s="40"/>
+      <c r="G1730" s="40"/>
+      <c r="H1730" s="40"/>
+    </row>
+    <row r="1731" spans="6:8">
+      <c r="F1731" s="40"/>
+      <c r="G1731" s="40"/>
+      <c r="H1731" s="40"/>
+    </row>
+    <row r="1732" spans="6:8">
+      <c r="G1732" s="40"/>
+    </row>
+    <row r="1733" spans="6:8">
+      <c r="F1733" s="40"/>
+      <c r="G1733" s="40"/>
+    </row>
+    <row r="1734" spans="6:8">
+      <c r="G1734" s="40"/>
+    </row>
+    <row r="1735" spans="6:8">
+      <c r="G1735" s="40"/>
+    </row>
+    <row r="1736" spans="6:8">
+      <c r="G1736" s="40"/>
+    </row>
+    <row r="1737" spans="6:8">
+      <c r="G1737" s="40"/>
+    </row>
+    <row r="1738" spans="6:8">
+      <c r="G1738" s="40"/>
+    </row>
+    <row r="1739" spans="6:8">
+      <c r="F1739" s="40"/>
+      <c r="G1739" s="40"/>
+      <c r="H1739" s="40"/>
+    </row>
+    <row r="1740" spans="6:8">
+      <c r="G1740" s="40"/>
+    </row>
+    <row r="1741" spans="6:8">
+      <c r="G1741" s="40"/>
+    </row>
+    <row r="1742" spans="6:8">
+      <c r="G1742" s="40"/>
+    </row>
+    <row r="1743" spans="6:8">
+      <c r="G1743" s="40"/>
+    </row>
+    <row r="1744" spans="6:8">
+      <c r="G1744" s="40"/>
+    </row>
+    <row r="1745" spans="7:7">
+      <c r="G1745" s="40"/>
+    </row>
+    <row r="1746" spans="7:7">
+      <c r="G1746" s="40"/>
+    </row>
+    <row r="1747" spans="7:7">
+      <c r="G1747" s="40"/>
+    </row>
+    <row r="1748" spans="7:7">
+      <c r="G1748" s="40"/>
+    </row>
+    <row r="1749" spans="7:7">
+      <c r="G1749" s="40"/>
+    </row>
+    <row r="1791" spans="6:6">
+      <c r="F1791" s="40"/>
+    </row>
+    <row r="1808" spans="8:8">
+      <c r="H1808" s="40"/>
+    </row>
+    <row r="1810" spans="6:8">
+      <c r="F1810" s="40"/>
+      <c r="H1810" s="40"/>
+    </row>
+    <row r="1811" spans="6:8">
+      <c r="F1811" s="40"/>
+      <c r="H1811" s="40"/>
+    </row>
+    <row r="1812" spans="6:8">
+      <c r="H1812" s="40"/>
+    </row>
+    <row r="1814" spans="6:8">
+      <c r="F1814" s="40"/>
+      <c r="H1814" s="40"/>
+    </row>
+    <row r="1815" spans="6:8">
+      <c r="F1815" s="40"/>
+      <c r="H1815" s="40"/>
+    </row>
+    <row r="1816" spans="6:8">
+      <c r="F1816" s="40"/>
+      <c r="H1816" s="40"/>
+    </row>
+    <row r="1817" spans="6:8">
+      <c r="F1817" s="40"/>
+      <c r="H1817" s="40"/>
+    </row>
+    <row r="1818" spans="6:8">
+      <c r="F1818" s="40"/>
+      <c r="H1818" s="40"/>
+    </row>
+    <row r="1819" spans="6:8">
+      <c r="F1819" s="40"/>
+      <c r="H1819" s="40"/>
+    </row>
+    <row r="1820" spans="6:8">
+      <c r="H1820" s="40"/>
+    </row>
+    <row r="1821" spans="6:8">
+      <c r="H1821" s="40"/>
+    </row>
+    <row r="1822" spans="6:8">
+      <c r="H1822" s="40"/>
+    </row>
+    <row r="1824" spans="6:8">
+      <c r="H1824" s="40"/>
+    </row>
+    <row r="1825" spans="6:8">
+      <c r="F1825" s="40"/>
+      <c r="H1825" s="40"/>
+    </row>
+    <row r="1826" spans="6:8">
+      <c r="F1826" s="40"/>
+      <c r="H1826" s="40"/>
+    </row>
+    <row r="1827" spans="6:8">
+      <c r="F1827" s="40"/>
+      <c r="H1827" s="40"/>
+    </row>
+    <row r="1828" spans="6:8">
+      <c r="F1828" s="40"/>
+      <c r="H1828" s="40"/>
+    </row>
+    <row r="1829" spans="6:8">
+      <c r="F1829" s="40"/>
+      <c r="H1829" s="40"/>
+    </row>
+    <row r="1830" spans="6:8">
+      <c r="F1830" s="40"/>
+      <c r="H1830" s="40"/>
+    </row>
+    <row r="1831" spans="6:8">
+      <c r="F1831" s="40"/>
+      <c r="H1831" s="40"/>
+    </row>
+    <row r="1832" spans="6:8">
+      <c r="H1832" s="40"/>
+    </row>
+    <row r="1833" spans="6:8">
+      <c r="F1833" s="40"/>
+      <c r="H1833" s="40"/>
+    </row>
+    <row r="1834" spans="6:8">
+      <c r="F1834" s="40"/>
+      <c r="H1834" s="40"/>
+    </row>
+    <row r="1835" spans="6:8">
+      <c r="F1835" s="40"/>
+      <c r="H1835" s="40"/>
+    </row>
+    <row r="1836" spans="6:8">
+      <c r="F1836" s="40"/>
+      <c r="H1836" s="40"/>
+    </row>
+    <row r="1838" spans="6:8">
+      <c r="H1838" s="40"/>
+    </row>
+    <row r="1840" spans="6:8">
+      <c r="F1840" s="40"/>
+      <c r="H1840" s="40"/>
+    </row>
+    <row r="1842" spans="6:8">
+      <c r="H1842" s="40"/>
+    </row>
+    <row r="1844" spans="6:8">
+      <c r="H1844" s="40"/>
+    </row>
+    <row r="1846" spans="6:8">
+      <c r="H1846" s="40"/>
+    </row>
+    <row r="1847" spans="6:8">
+      <c r="F1847" s="40"/>
+      <c r="H1847" s="40"/>
+    </row>
+    <row r="1848" spans="6:8">
+      <c r="H1848" s="40"/>
+    </row>
+    <row r="1850" spans="6:8">
+      <c r="H1850" s="40"/>
+    </row>
+    <row r="1851" spans="6:8">
+      <c r="F1851" s="40"/>
+      <c r="H1851" s="40"/>
+    </row>
+    <row r="1852" spans="6:8">
+      <c r="H1852" s="40"/>
+    </row>
+    <row r="1854" spans="6:8">
+      <c r="H1854" s="40"/>
+    </row>
+    <row r="1856" spans="6:8">
+      <c r="H1856" s="40"/>
+    </row>
+    <row r="1858" spans="6:8">
+      <c r="H1858" s="40"/>
+    </row>
+    <row r="1860" spans="6:8">
+      <c r="H1860" s="40"/>
+    </row>
+    <row r="1862" spans="6:8">
+      <c r="F1862" s="40"/>
+      <c r="H1862" s="40"/>
+    </row>
+    <row r="1872" spans="6:8">
+      <c r="F1872" s="40"/>
+    </row>
+    <row r="1889" spans="6:8">
+      <c r="H1889" s="40"/>
+    </row>
+    <row r="1891" spans="6:8">
+      <c r="H1891" s="40"/>
+    </row>
+    <row r="1893" spans="6:8">
+      <c r="F1893" s="40"/>
+      <c r="H1893" s="40"/>
+    </row>
+    <row r="1895" spans="6:8">
+      <c r="H1895" s="40"/>
+    </row>
+    <row r="1897" spans="6:8">
+      <c r="H1897" s="40"/>
+    </row>
+    <row r="1899" spans="6:8">
+      <c r="H1899" s="40"/>
+    </row>
+    <row r="1901" spans="6:8">
+      <c r="H1901" s="40"/>
+    </row>
+    <row r="1902" spans="6:8">
+      <c r="F1902" s="40"/>
+      <c r="H1902" s="40"/>
+    </row>
+    <row r="1903" spans="6:8">
+      <c r="H1903" s="40"/>
+    </row>
+    <row r="1905" spans="6:8">
+      <c r="H1905" s="40"/>
+    </row>
+    <row r="1907" spans="6:8">
+      <c r="H1907" s="40"/>
+    </row>
+    <row r="1909" spans="6:8">
+      <c r="H1909" s="40"/>
+    </row>
+    <row r="1910" spans="6:8">
+      <c r="F1910" s="40"/>
+      <c r="H1910" s="40"/>
+    </row>
+    <row r="1911" spans="6:8">
+      <c r="H1911" s="40"/>
+    </row>
+    <row r="1913" spans="6:8">
+      <c r="H1913" s="40"/>
+    </row>
+    <row r="1915" spans="6:8">
+      <c r="H1915" s="40"/>
+    </row>
+    <row r="1917" spans="6:8">
+      <c r="H1917" s="40"/>
+    </row>
+    <row r="1919" spans="6:8">
+      <c r="F1919" s="40"/>
+      <c r="H1919" s="40"/>
+    </row>
+    <row r="1927" spans="6:6">
+      <c r="F1927" s="40"/>
+    </row>
+    <row r="1935" spans="6:6">
+      <c r="F1935" s="40"/>
+    </row>
+    <row r="1942" spans="6:8">
+      <c r="F1942" s="40"/>
+      <c r="H1942" s="40"/>
+    </row>
+    <row r="1958" spans="6:8">
+      <c r="F1958" s="41"/>
+      <c r="H1958" s="41"/>
+    </row>
+    <row r="1959" spans="6:8">
+      <c r="F1959" s="41"/>
+    </row>
+    <row r="1962" spans="6:8">
+      <c r="F1962" s="41"/>
+      <c r="H1962" s="41"/>
+    </row>
+    <row r="1963" spans="6:8">
+      <c r="F1963" s="40"/>
+    </row>
+    <row r="1976" spans="6:8">
+      <c r="F1976" s="40"/>
+      <c r="H1976" s="40"/>
+    </row>
+    <row r="1991" spans="6:8">
+      <c r="F1991" s="41"/>
+      <c r="H1991" s="41"/>
+    </row>
+    <row r="1992" spans="6:8">
+      <c r="F1992" s="41"/>
+    </row>
+    <row r="1995" spans="6:8">
+      <c r="F1995" s="41"/>
+      <c r="H1995" s="41"/>
+    </row>
+    <row r="1996" spans="6:8">
+      <c r="F1996" s="40"/>
+    </row>
+    <row r="2009" spans="6:8">
+      <c r="F2009" s="40"/>
+      <c r="H2009" s="40"/>
+    </row>
+    <row r="2024" spans="6:8">
+      <c r="F2024" s="41"/>
+      <c r="H2024" s="41"/>
+    </row>
+    <row r="2025" spans="6:8">
+      <c r="F2025" s="41"/>
+    </row>
+    <row r="2028" spans="6:8">
+      <c r="F2028" s="41"/>
+      <c r="H2028" s="41"/>
+    </row>
+    <row r="2029" spans="6:8">
+      <c r="F2029" s="40"/>
+    </row>
+    <row r="2042" spans="6:8">
+      <c r="F2042" s="40"/>
+      <c r="H2042" s="40"/>
+    </row>
+    <row r="2050" spans="6:8">
+      <c r="F2050" s="40"/>
+      <c r="G2050" s="40"/>
+      <c r="H2050" s="40"/>
+    </row>
+    <row r="2057" spans="6:8">
+      <c r="F2057" s="41"/>
+      <c r="H2057" s="41"/>
+    </row>
+    <row r="2058" spans="6:8">
+      <c r="F2058" s="41"/>
+    </row>
+    <row r="2061" spans="6:8">
+      <c r="F2061" s="41"/>
+      <c r="H2061" s="41"/>
+    </row>
+    <row r="2062" spans="6:8">
+      <c r="F2062" s="40"/>
+    </row>
+    <row r="2075" spans="6:8">
+      <c r="F2075" s="40"/>
+      <c r="H2075" s="40"/>
+    </row>
+    <row r="2083" spans="6:8">
+      <c r="F2083" s="40"/>
+      <c r="G2083" s="40"/>
+      <c r="H2083" s="40"/>
+    </row>
+    <row r="2090" spans="6:8">
+      <c r="F2090" s="41"/>
+      <c r="H2090" s="41"/>
+    </row>
+    <row r="2091" spans="6:8">
+      <c r="F2091" s="41"/>
+    </row>
+    <row r="2094" spans="6:8">
+      <c r="F2094" s="41"/>
+      <c r="H2094" s="41"/>
+    </row>
+    <row r="2095" spans="6:8">
+      <c r="F2095" s="40"/>
+    </row>
+    <row r="2108" spans="6:8">
+      <c r="F2108" s="40"/>
+      <c r="H2108" s="40"/>
+    </row>
+    <row r="2116" spans="6:8">
+      <c r="F2116" s="40"/>
+      <c r="G2116" s="40"/>
+      <c r="H2116" s="40"/>
+    </row>
+    <row r="2123" spans="6:8">
+      <c r="F2123" s="41"/>
+      <c r="H2123" s="41"/>
+    </row>
+    <row r="2124" spans="6:8">
+      <c r="F2124" s="41"/>
+    </row>
+    <row r="2127" spans="6:8">
+      <c r="F2127" s="41"/>
+      <c r="H2127" s="41"/>
+    </row>
+    <row r="2128" spans="6:8">
+      <c r="F2128" s="40"/>
+    </row>
+    <row r="2141" spans="6:8">
+      <c r="F2141" s="40"/>
+      <c r="H2141" s="40"/>
+    </row>
+    <row r="2156" spans="6:8">
+      <c r="F2156" s="41"/>
+      <c r="H2156" s="41"/>
+    </row>
+    <row r="2157" spans="6:8">
+      <c r="F2157" s="41"/>
+    </row>
+    <row r="2160" spans="6:8">
+      <c r="F2160" s="41"/>
+      <c r="H2160" s="41"/>
+    </row>
+    <row r="2161" spans="6:8">
+      <c r="F2161" s="40"/>
+    </row>
+    <row r="2174" spans="6:8">
+      <c r="F2174" s="40"/>
+      <c r="H2174" s="40"/>
+    </row>
+    <row r="2189" spans="6:8">
+      <c r="F2189" s="41"/>
+      <c r="H2189" s="41"/>
+    </row>
+    <row r="2190" spans="6:8">
+      <c r="F2190" s="41"/>
+    </row>
+    <row r="2193" spans="6:8">
+      <c r="F2193" s="41"/>
+      <c r="H2193" s="41"/>
+    </row>
+    <row r="2194" spans="6:8">
+      <c r="F2194" s="40"/>
+    </row>
+    <row r="2207" spans="6:8">
+      <c r="F2207" s="40"/>
+      <c r="H2207" s="40"/>
+    </row>
+    <row r="2215" spans="6:8">
+      <c r="F2215" s="40"/>
+      <c r="G2215" s="40"/>
+      <c r="H2215" s="40"/>
+    </row>
+    <row r="2222" spans="6:8">
+      <c r="F2222" s="41"/>
+      <c r="H2222" s="41"/>
+    </row>
+    <row r="2223" spans="6:8">
+      <c r="F2223" s="41"/>
+    </row>
+    <row r="2226" spans="6:8">
+      <c r="F2226" s="41"/>
+      <c r="H2226" s="41"/>
+    </row>
+    <row r="2227" spans="6:8">
+      <c r="F2227" s="40"/>
+    </row>
+    <row r="2240" spans="6:8">
+      <c r="F2240" s="40"/>
+      <c r="H2240" s="40"/>
+    </row>
+    <row r="2248" spans="6:8">
+      <c r="F2248" s="40"/>
+      <c r="G2248" s="40"/>
+      <c r="H2248" s="40"/>
+    </row>
+    <row r="2255" spans="6:8">
+      <c r="F2255" s="41"/>
+      <c r="H2255" s="41"/>
+    </row>
+    <row r="2256" spans="6:8">
+      <c r="F2256" s="41"/>
+    </row>
+    <row r="2259" spans="6:8">
+      <c r="F2259" s="41"/>
+      <c r="H2259" s="41"/>
+    </row>
+    <row r="2260" spans="6:8">
+      <c r="F2260" s="40"/>
+    </row>
+    <row r="2273" spans="6:8">
+      <c r="F2273" s="40"/>
+      <c r="H2273" s="40"/>
+    </row>
+    <row r="2281" spans="6:8">
+      <c r="F2281" s="40"/>
+      <c r="G2281" s="40"/>
+      <c r="H2281" s="40"/>
+    </row>
+    <row r="2283" spans="6:8">
+      <c r="F2283" s="40"/>
+      <c r="G2283" s="40"/>
+      <c r="H2283" s="40"/>
+    </row>
+    <row r="2284" spans="6:8">
+      <c r="F2284" s="40"/>
+      <c r="G2284" s="40"/>
+      <c r="H2284" s="40"/>
+    </row>
+    <row r="2285" spans="6:8">
+      <c r="F2285" s="40"/>
+      <c r="G2285" s="40"/>
+      <c r="H2285" s="40"/>
+    </row>
+    <row r="2286" spans="6:8">
+      <c r="F2286" s="40"/>
+      <c r="G2286" s="40"/>
+      <c r="H2286" s="40"/>
+    </row>
+    <row r="2287" spans="6:8">
+      <c r="F2287" s="40"/>
+      <c r="G2287" s="40"/>
+      <c r="H2287" s="40"/>
+    </row>
+    <row r="2288" spans="6:8">
+      <c r="F2288" s="40"/>
+      <c r="G2288" s="40"/>
+      <c r="H2288" s="40"/>
+    </row>
+    <row r="2289" spans="6:8">
+      <c r="F2289" s="40"/>
+      <c r="G2289" s="40"/>
+      <c r="H2289" s="40"/>
+    </row>
+    <row r="2290" spans="6:8">
+      <c r="F2290" s="40"/>
+      <c r="G2290" s="40"/>
+      <c r="H2290" s="40"/>
+    </row>
+    <row r="2291" spans="6:8">
+      <c r="F2291" s="40"/>
+      <c r="G2291" s="40"/>
+      <c r="H2291" s="40"/>
+    </row>
+    <row r="2292" spans="6:8">
+      <c r="F2292" s="40"/>
+      <c r="G2292" s="40"/>
+      <c r="H2292" s="40"/>
+    </row>
+    <row r="2293" spans="6:8">
+      <c r="F2293" s="40"/>
+      <c r="G2293" s="40"/>
+      <c r="H2293" s="40"/>
+    </row>
+    <row r="2294" spans="6:8">
+      <c r="F2294" s="40"/>
+      <c r="G2294" s="40"/>
+      <c r="H2294" s="40"/>
+    </row>
+    <row r="2295" spans="6:8">
+      <c r="F2295" s="40"/>
+      <c r="G2295" s="40"/>
+      <c r="H2295" s="40"/>
+    </row>
+    <row r="2296" spans="6:8">
+      <c r="F2296" s="40"/>
+      <c r="G2296" s="40"/>
+      <c r="H2296" s="40"/>
+    </row>
+    <row r="2297" spans="6:8">
+      <c r="F2297" s="40"/>
+      <c r="G2297" s="40"/>
+      <c r="H2297" s="40"/>
+    </row>
+    <row r="2298" spans="6:8">
+      <c r="F2298" s="40"/>
+      <c r="G2298" s="40"/>
+      <c r="H2298" s="40"/>
+    </row>
+    <row r="2299" spans="6:8">
+      <c r="F2299" s="40"/>
+      <c r="G2299" s="40"/>
+      <c r="H2299" s="40"/>
+    </row>
+    <row r="2300" spans="6:8">
+      <c r="F2300" s="40"/>
+      <c r="G2300" s="40"/>
+      <c r="H2300" s="40"/>
+    </row>
+    <row r="2301" spans="6:8">
+      <c r="F2301" s="40"/>
+      <c r="G2301" s="40"/>
+      <c r="H2301" s="40"/>
+    </row>
+    <row r="2302" spans="6:8">
+      <c r="F2302" s="40"/>
+      <c r="G2302" s="40"/>
+      <c r="H2302" s="40"/>
+    </row>
+    <row r="2303" spans="6:8">
+      <c r="F2303" s="40"/>
+      <c r="G2303" s="40"/>
+      <c r="H2303" s="40"/>
+    </row>
+    <row r="2304" spans="6:8">
+      <c r="F2304" s="40"/>
+      <c r="G2304" s="40"/>
+      <c r="H2304" s="40"/>
+    </row>
+    <row r="2305" spans="6:8">
+      <c r="F2305" s="40"/>
+      <c r="G2305" s="40"/>
+      <c r="H2305" s="40"/>
+    </row>
+    <row r="2306" spans="6:8">
+      <c r="F2306" s="40"/>
+      <c r="G2306" s="40"/>
+      <c r="H2306" s="40"/>
+    </row>
+    <row r="2307" spans="6:8">
+      <c r="F2307" s="40"/>
+      <c r="G2307" s="40"/>
+      <c r="H2307" s="40"/>
+    </row>
+    <row r="2308" spans="6:8">
+      <c r="F2308" s="40"/>
+      <c r="G2308" s="40"/>
+      <c r="H2308" s="40"/>
+    </row>
+    <row r="2309" spans="6:8">
+      <c r="F2309" s="40"/>
+      <c r="G2309" s="40"/>
+      <c r="H2309" s="40"/>
+    </row>
+    <row r="2310" spans="6:8">
+      <c r="F2310" s="40"/>
+      <c r="G2310" s="40"/>
+      <c r="H2310" s="40"/>
+    </row>
+    <row r="2312" spans="6:8">
+      <c r="F2312" s="40"/>
+      <c r="G2312" s="40"/>
+      <c r="H2312" s="40"/>
+    </row>
+    <row r="2325" spans="6:8">
+      <c r="F2325" s="40"/>
+      <c r="G2325" s="40"/>
+      <c r="H2325" s="40"/>
+    </row>
+    <row r="2339" spans="6:8">
+      <c r="F2339" s="40"/>
+      <c r="G2339" s="40"/>
+      <c r="H2339" s="40"/>
+    </row>
+    <row r="2341" spans="6:8">
+      <c r="F2341" s="40"/>
+      <c r="G2341" s="40"/>
+      <c r="H2341" s="40"/>
+    </row>
+    <row r="2354" spans="6:8">
+      <c r="F2354" s="40"/>
+      <c r="G2354" s="40"/>
+      <c r="H2354" s="40"/>
+    </row>
+    <row r="2368" spans="6:8">
+      <c r="F2368" s="40"/>
+      <c r="G2368" s="40"/>
+      <c r="H2368" s="40"/>
+    </row>
+    <row r="2370" spans="6:8">
+      <c r="F2370" s="40"/>
+      <c r="G2370" s="40"/>
+      <c r="H2370" s="40"/>
+    </row>
+    <row r="2383" spans="6:8">
+      <c r="F2383" s="40"/>
+      <c r="G2383" s="40"/>
+      <c r="H2383" s="40"/>
+    </row>
+    <row r="2397" spans="6:8">
+      <c r="F2397" s="40"/>
+      <c r="G2397" s="40"/>
+      <c r="H2397" s="40"/>
+    </row>
+    <row r="2400" spans="6:8">
+      <c r="F2400" s="40"/>
+      <c r="G2400" s="40"/>
+      <c r="H2400" s="40"/>
+    </row>
+    <row r="2401" spans="6:8">
+      <c r="F2401" s="40"/>
+      <c r="G2401" s="40"/>
+      <c r="H2401" s="40"/>
+    </row>
+    <row r="2402" spans="6:8">
+      <c r="F2402" s="40"/>
+      <c r="G2402" s="40"/>
+      <c r="H2402" s="40"/>
+    </row>
+    <row r="2403" spans="6:8">
+      <c r="F2403" s="40"/>
+      <c r="G2403" s="40"/>
+      <c r="H2403" s="40"/>
+    </row>
+    <row r="2404" spans="6:8">
+      <c r="F2404" s="40"/>
+      <c r="G2404" s="40"/>
+      <c r="H2404" s="40"/>
+    </row>
+    <row r="2405" spans="6:8">
+      <c r="F2405" s="40"/>
+      <c r="G2405" s="40"/>
+      <c r="H2405" s="40"/>
+    </row>
+    <row r="2406" spans="6:8">
+      <c r="F2406" s="40"/>
+      <c r="G2406" s="40"/>
+      <c r="H2406" s="40"/>
+    </row>
+    <row r="2407" spans="6:8">
+      <c r="F2407" s="40"/>
+      <c r="G2407" s="40"/>
+      <c r="H2407" s="40"/>
+    </row>
+    <row r="2408" spans="6:8">
+      <c r="F2408" s="40"/>
+      <c r="G2408" s="40"/>
+      <c r="H2408" s="40"/>
+    </row>
+    <row r="2409" spans="6:8">
+      <c r="F2409" s="40"/>
+      <c r="G2409" s="40"/>
+      <c r="H2409" s="40"/>
+    </row>
+    <row r="2410" spans="6:8">
+      <c r="F2410" s="40"/>
+      <c r="G2410" s="40"/>
+      <c r="H2410" s="40"/>
+    </row>
+    <row r="2411" spans="6:8">
+      <c r="F2411" s="40"/>
+      <c r="G2411" s="40"/>
+      <c r="H2411" s="40"/>
+    </row>
+    <row r="2412" spans="6:8">
+      <c r="F2412" s="40"/>
+      <c r="G2412" s="40"/>
+      <c r="H2412" s="40"/>
+    </row>
+    <row r="2413" spans="6:8">
+      <c r="F2413" s="40"/>
+      <c r="G2413" s="40"/>
+      <c r="H2413" s="40"/>
+    </row>
+    <row r="2422" spans="6:8">
+      <c r="F2422" s="40"/>
+      <c r="G2422" s="40"/>
+      <c r="H2422" s="40"/>
+    </row>
+    <row r="2439" spans="6:8">
+      <c r="F2439" s="40"/>
+      <c r="G2439" s="40"/>
+      <c r="H2439" s="40"/>
+    </row>
+    <row r="2456" spans="6:8">
+      <c r="F2456" s="40"/>
+      <c r="G2456" s="40"/>
+      <c r="H2456" s="40"/>
+    </row>
+    <row r="2473" spans="6:8">
+      <c r="F2473" s="40"/>
+      <c r="G2473" s="40"/>
+      <c r="H2473" s="40"/>
+    </row>
+    <row r="2490" spans="6:6">
+      <c r="F2490" s="40"/>
+    </row>
+    <row r="2507" spans="6:6">
+      <c r="F2507" s="40"/>
+    </row>
+    <row r="2524" spans="6:6">
+      <c r="F2524" s="40"/>
+    </row>
+    <row r="2541" spans="6:6">
+      <c r="F2541" s="40"/>
+    </row>
+    <row r="2558" spans="6:6">
+      <c r="F2558" s="40"/>
+    </row>
+    <row r="2575" spans="6:6">
+      <c r="F2575" s="40"/>
+    </row>
+    <row r="2592" spans="6:6">
+      <c r="F2592" s="40"/>
+    </row>
+    <row r="2609" spans="6:8">
+      <c r="F2609" s="40"/>
+      <c r="H2609" s="40"/>
+    </row>
+    <row r="2626" spans="6:6">
+      <c r="F2626" s="40"/>
+    </row>
+    <row r="2660" spans="6:6">
+      <c r="F2660" s="40"/>
+    </row>
+    <row r="2677" spans="6:6">
+      <c r="F2677" s="40"/>
+    </row>
+    <row r="2700" spans="6:8">
+      <c r="F2700" s="40"/>
+      <c r="H2700" s="40"/>
+    </row>
+    <row r="2721" spans="6:8">
+      <c r="F2721" s="40"/>
+    </row>
+    <row r="2736" spans="6:8">
+      <c r="F2736" s="40"/>
+      <c r="G2736" s="40"/>
+      <c r="H2736" s="40"/>
+    </row>
+    <row r="2751" spans="6:8">
+      <c r="F2751" s="40"/>
+      <c r="H2751" s="40"/>
+    </row>
+    <row r="2766" spans="6:8">
+      <c r="F2766" s="40"/>
+      <c r="G2766" s="40"/>
+      <c r="H2766" s="40"/>
+    </row>
+    <row r="2782" spans="6:8">
+      <c r="F2782" s="40"/>
+      <c r="G2782" s="40"/>
+      <c r="H2782" s="40"/>
+    </row>
+    <row r="2790" spans="6:8">
+      <c r="F2790" s="40"/>
+      <c r="G2790" s="40"/>
+      <c r="H2790" s="40"/>
+    </row>
+    <row r="2818" spans="6:8">
+      <c r="F2818" s="40"/>
+      <c r="G2818" s="40"/>
+      <c r="H2818" s="40"/>
+    </row>
+    <row r="2826" spans="6:8">
+      <c r="F2826" s="40"/>
+      <c r="G2826" s="40"/>
+      <c r="H2826" s="40"/>
+    </row>
+    <row r="2833" spans="6:8">
+      <c r="F2833" s="40"/>
+      <c r="G2833" s="40"/>
+      <c r="H2833" s="40"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:G81">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:J81">
     <sortCondition ref="A9:A81"/>
     <sortCondition ref="C9:C81"/>
   </sortState>
@@ -6372,25 +7482,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECD30A18-04B8-42E0-9E13-F4ED24029528}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:H600"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="42.5703125" style="33" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" style="9" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" style="27" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" style="27" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" style="27" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" style="27" bestFit="1"/>
-    <col min="7" max="16384" width="8.85546875" style="33"/>
+    <col min="1" max="1" width="42.5546875" style="33" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" style="27" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" style="27" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="27" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" style="27" bestFit="1"/>
+    <col min="7" max="16384" width="8.88671875" style="33"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="9" customFormat="1" ht="21">
       <c r="A1" s="8" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="8" customFormat="1" ht="21">
       <c r="A2" s="31" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -6405,7 +7515,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="17" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B4" s="35"/>
       <c r="C4" s="35"/>
@@ -6469,10 +7579,10 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C9" s="12">
         <v>656</v>
@@ -6489,10 +7599,10 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C10" s="12">
         <v>610</v>
@@ -6509,10 +7619,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C11" s="12">
         <v>1240</v>
@@ -6529,10 +7639,10 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C12" s="12">
         <v>1911</v>
@@ -6549,10 +7659,10 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C13" s="12">
         <v>2103</v>
@@ -6569,10 +7679,10 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C14" s="12">
         <v>1248</v>
@@ -6589,10 +7699,10 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C15" s="12">
         <v>269</v>
@@ -6609,10 +7719,10 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C16" s="12">
         <v>2396</v>
@@ -6629,10 +7739,10 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C17" s="12">
         <v>1820</v>
@@ -6649,10 +7759,10 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C18" s="12">
         <v>315</v>
@@ -6669,10 +7779,10 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C19" s="12">
         <v>451</v>
@@ -6689,10 +7799,10 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C20" s="12">
         <v>1392</v>
@@ -6709,10 +7819,10 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C21" s="12">
         <v>2627</v>
@@ -6729,10 +7839,10 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C22" s="12">
         <v>269</v>
@@ -6749,10 +7859,10 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C23" s="12">
         <v>500</v>
@@ -6769,10 +7879,10 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C24" s="12">
         <v>501</v>
@@ -6789,10 +7899,10 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C25" s="12">
         <v>1217</v>
@@ -6809,10 +7919,10 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C26" s="12">
         <v>2148</v>
@@ -6829,10 +7939,10 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C27" s="12">
         <v>2008</v>
@@ -6849,10 +7959,10 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C28" s="12">
         <v>1816</v>
@@ -6869,10 +7979,10 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C29" s="12">
         <v>1813</v>
@@ -6889,10 +7999,10 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C30" s="12">
         <v>2894</v>
@@ -6909,10 +8019,10 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C31" s="12">
         <v>1733</v>
@@ -6929,10 +8039,10 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C32" s="12">
         <v>1735</v>
@@ -6949,10 +8059,10 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C33" s="12">
         <v>1733</v>
@@ -6969,10 +8079,10 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C34" s="12">
         <v>1737</v>
@@ -6989,10 +8099,10 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C35" s="12">
         <v>1733</v>
@@ -7009,10 +8119,10 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C36" s="12">
         <v>1730</v>
@@ -7029,10 +8139,10 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C37" s="12">
         <v>1733</v>
@@ -7049,10 +8159,10 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C38" s="12">
         <v>1733</v>
@@ -7069,10 +8179,10 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C39" s="12">
         <v>1426</v>
@@ -7089,10 +8199,10 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C40" s="12">
         <v>1591</v>
@@ -7109,10 +8219,10 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C41" s="12">
         <v>1985</v>
@@ -7129,10 +8239,10 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C42" s="12">
         <v>231</v>
@@ -7149,10 +8259,10 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C43" s="12">
         <v>147</v>
@@ -7169,10 +8279,10 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C44" s="12">
         <v>1416</v>
@@ -7189,10 +8299,10 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C45" s="12">
         <v>62</v>
@@ -7209,10 +8319,10 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C46" s="12">
         <v>162</v>
@@ -7229,10 +8339,10 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C47" s="12">
         <v>162</v>
@@ -7249,10 +8359,10 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C48" s="12">
         <v>160</v>
@@ -7269,10 +8379,10 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C49" s="12">
         <v>285</v>
@@ -7289,10 +8399,10 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C50" s="12">
         <v>359</v>
@@ -7309,10 +8419,10 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C51" s="12">
         <v>349</v>
@@ -7329,10 +8439,10 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C52" s="12">
         <v>349</v>
@@ -7349,10 +8459,10 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C53" s="12">
         <v>407</v>
@@ -7369,10 +8479,10 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C54" s="12">
         <v>611</v>
@@ -7389,10 +8499,10 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C55" s="12">
         <v>636</v>
@@ -7409,10 +8519,10 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C56" s="12">
         <v>610</v>
@@ -7429,10 +8539,10 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C57" s="12">
         <v>702</v>
@@ -7449,10 +8559,10 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C58" s="12">
         <v>901</v>
@@ -7469,10 +8579,10 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C59" s="12">
         <v>962</v>
@@ -7489,10 +8599,10 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C60" s="12">
         <v>1227</v>
@@ -7509,10 +8619,10 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C61" s="12">
         <v>1079</v>
@@ -7529,10 +8639,10 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C62" s="12">
         <v>1019</v>
@@ -7549,10 +8659,10 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C63" s="12">
         <v>964</v>
@@ -7569,10 +8679,10 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C64" s="12">
         <v>901</v>
@@ -7589,10 +8699,10 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C65" s="12">
         <v>1138</v>
@@ -7609,10 +8719,10 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C66" s="12">
         <v>1139</v>
@@ -7629,10 +8739,10 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C67" s="12">
         <v>1079</v>
@@ -7649,10 +8759,10 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C68" s="12">
         <v>1022</v>
@@ -7669,10 +8779,10 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C69" s="12">
         <v>1306</v>
@@ -7689,10 +8799,10 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C70" s="12">
         <v>1288</v>
@@ -7709,10 +8819,10 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C71" s="12">
         <v>1473</v>
@@ -7729,10 +8839,10 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C72" s="12">
         <v>1215</v>
@@ -7749,10 +8859,10 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C73" s="12">
         <v>697</v>
@@ -7769,10 +8879,10 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C74" s="12">
         <v>1048</v>
@@ -7789,10 +8899,10 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C75" s="12">
         <v>1313</v>
@@ -7809,10 +8919,10 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C76" s="12">
         <v>890</v>
@@ -7829,10 +8939,10 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C77" s="12">
         <v>1393</v>
@@ -7849,10 +8959,10 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C78" s="12">
         <v>970</v>
@@ -7869,10 +8979,10 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C79" s="12">
         <v>969</v>
@@ -7889,10 +8999,10 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C80" s="12">
         <v>889</v>
@@ -7909,10 +9019,10 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C81" s="12">
         <v>1051</v>
@@ -7929,10 +9039,10 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C82" s="12">
         <v>1217</v>
@@ -7949,10 +9059,10 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C83" s="12">
         <v>1305</v>
@@ -7969,10 +9079,10 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C84" s="12">
         <v>1466</v>
@@ -7989,10 +9099,10 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C85" s="12">
         <v>1308</v>
@@ -8009,10 +9119,10 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C86" s="12">
         <v>1309</v>
@@ -8029,10 +9139,10 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C87" s="12">
         <v>1364</v>
@@ -8049,10 +9159,10 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B88" s="12" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C88" s="12">
         <v>1238</v>
@@ -8069,10 +9179,10 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C89" s="12">
         <v>1142</v>
@@ -8089,10 +9199,10 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C90" s="12">
         <v>1069</v>
@@ -8109,10 +9219,10 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B91" s="12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C91" s="12">
         <v>1072</v>
@@ -8129,10 +9239,10 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B92" s="12" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C92" s="12">
         <v>1117</v>
@@ -8149,10 +9259,10 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B93" s="12" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C93" s="12">
         <v>915</v>
@@ -8169,10 +9279,10 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B94" s="12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C94" s="12">
         <v>783</v>
@@ -8189,10 +9299,10 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C95" s="12">
         <v>914</v>
@@ -8209,10 +9319,10 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C96" s="12">
         <v>817</v>
@@ -8229,10 +9339,10 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C97" s="12">
         <v>650</v>
@@ -8249,10 +9359,10 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B98" s="12" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C98" s="12">
         <v>586</v>
@@ -8269,10 +9379,10 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B99" s="12" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C99" s="12">
         <v>296</v>
@@ -8289,10 +9399,10 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B100" s="12" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C100" s="12">
         <v>467</v>
@@ -8309,10 +9419,10 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B101" s="12" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C101" s="12">
         <v>530</v>
@@ -8329,10 +9439,10 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B102" s="12" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C102" s="12">
         <v>586</v>
@@ -8349,10 +9459,10 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B103" s="12" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C103" s="12">
         <v>648</v>
@@ -8369,10 +9479,10 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B104" s="12" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C104" s="12">
         <v>409</v>
@@ -8389,10 +9499,10 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B105" s="12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C105" s="12">
         <v>408</v>
@@ -8409,10 +9519,10 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B106" s="12" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C106" s="12">
         <v>469</v>
@@ -8429,10 +9539,10 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B107" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C107" s="12">
         <v>529</v>
@@ -8449,10 +9559,10 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B108" s="12" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C108" s="12">
         <v>210</v>
@@ -8993,21 +10103,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F00A795-F924-4957-BF24-7CBCF1582012}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:C35"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" customWidth="1"/>
-    <col min="2" max="2" width="36.7109375" customWidth="1"/>
-    <col min="3" max="3" width="82.42578125" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" customWidth="1"/>
+    <col min="2" max="2" width="36.6640625" customWidth="1"/>
+    <col min="3" max="3" width="82.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="6" customFormat="1" ht="21">
       <c r="A1" s="8" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="7" customFormat="1" ht="21">
       <c r="A2" s="31" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -9017,7 +10127,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="17" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -9054,299 +10164,299 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="50" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="50" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C14" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
+        <v>100</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" t="s">
         <v>103</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C24" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C25" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" t="s">
         <v>111</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C26" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C27" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C28" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C29" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C30" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="9" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C31" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C32" t="s">
         <v>140</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C32" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C33" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C34" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C35" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -9359,21 +10469,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9014B11-7294-4050-ABF4-8B4EFBD7F103}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:C42"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" customWidth="1"/>
-    <col min="2" max="2" width="50.28515625" customWidth="1"/>
-    <col min="3" max="3" width="102.140625" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" customWidth="1"/>
+    <col min="2" max="2" width="50.33203125" customWidth="1"/>
+    <col min="3" max="3" width="102.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="6" customFormat="1" ht="21">
       <c r="A1" s="8" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="7" customFormat="1" ht="21">
       <c r="A2" s="31" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -9381,7 +10491,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="17" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -9412,365 +10522,365 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B12" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B13" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B15" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B16" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="39" t="s">
         <v>90</v>
-      </c>
-      <c r="B17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="39" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="50" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B18" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="50" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B19" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C19" s="39" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="50" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B20" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C20" s="39" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="50" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B21" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C21" s="39" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1">
       <c r="A22" s="9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B23" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C23" s="39" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B24" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C24" s="39" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B25" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C25" s="39" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="50" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B26" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C26" s="39" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="50" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B27" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C27" s="39" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="50" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B28" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C28" s="39" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="50" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B29" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C29" s="39" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="50" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B30" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C30" s="39" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="50" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B31" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C31" s="39" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="50" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B32" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C32" s="39" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="50" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B33" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C33" s="39" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="50" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B34" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C34" s="39" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="50" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B35" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C35" s="39" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="50" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B36" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C36" s="39" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="50" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B37" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C37" s="39" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="50" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B38" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C38" s="39" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="50" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B39" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C39" s="39" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="50" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B40" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C40" s="39" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="50" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B41" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C41" s="39" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -9815,21 +10925,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01DEE13-8567-47C0-98EF-B4590CF5D2FE}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
-    <col min="2" max="2" width="43.42578125" customWidth="1"/>
-    <col min="3" max="3" width="107.28515625" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" customWidth="1"/>
+    <col min="2" max="2" width="43.44140625" customWidth="1"/>
+    <col min="3" max="3" width="107.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="6" customFormat="1" ht="21">
       <c r="A1" s="8" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="7" customFormat="1" ht="21">
       <c r="A2" s="31" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -9838,7 +10948,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="17" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -9877,10 +10987,10 @@
         <v>40</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -9917,26 +11027,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{787D0651-AC56-4C79-A3A0-381B16C48D1E}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="25.7109375" customWidth="1"/>
-    <col min="2" max="2" width="44.42578125" customWidth="1"/>
-    <col min="3" max="3" width="86.5703125" customWidth="1"/>
+    <col min="1" max="1" width="25.6640625" customWidth="1"/>
+    <col min="2" max="2" width="44.44140625" customWidth="1"/>
+    <col min="3" max="3" width="86.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="6" customFormat="1" ht="21">
       <c r="A1" s="8" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="7" customFormat="1" ht="21">
       <c r="A2" s="31" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="17" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -9968,35 +11078,35 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="17" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B11" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -10028,29 +11138,29 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBCEBA5B-6A50-48EF-B74E-B76FA9984AEF}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="33.28515625" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" customWidth="1"/>
-    <col min="3" max="3" width="38.85546875" customWidth="1"/>
-    <col min="4" max="4" width="47.7109375" customWidth="1"/>
+    <col min="1" max="1" width="33.33203125" customWidth="1"/>
+    <col min="2" max="2" width="16.88671875" customWidth="1"/>
+    <col min="3" max="3" width="38.88671875" customWidth="1"/>
+    <col min="4" max="4" width="47.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="6" customFormat="1" ht="21">
       <c r="A1" s="8" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B1" s="8"/>
     </row>
     <row r="2" spans="1:4" s="7" customFormat="1" ht="21">
       <c r="A2" s="31" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B2" s="8"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="17" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="4"/>
@@ -10088,35 +11198,35 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
+        <v>259</v>
+      </c>
+      <c r="C9" t="s">
         <v>262</v>
       </c>
-      <c r="C9" t="s">
-        <v>265</v>
-      </c>
       <c r="D9" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C10" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D10" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
